--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C2" s="104" t="inlineStr">
         <is>
-          <t>Explain the fundamental concepts of database systems (data models, schemas, the three-schema architecture, data independence) and trace how they arose from the research literature.</t>
+          <t>Explain the fundamental concepts of database systems (data models, schemas and instances, the three-schema architecture, data independence, DBMS components) and relate them to the research contributions that introduced them.</t>
         </is>
       </c>
       <c r="D2" s="103" t="n"/>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="C3" s="104" t="inlineStr">
         <is>
-          <t>Design Entity-Relationship models from requirements, compare design alternatives, and identify constraints that the ER model cannot express.</t>
+          <t>Design a database from requirements: build an Entity-Relationship model, justify design alternatives, and map it to a relational schema whose keys and integrity constraints are specified precisely, including as logical statements.</t>
         </is>
       </c>
       <c r="D3" s="103" t="n"/>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="C4" s="104" t="inlineStr">
         <is>
-          <t>Map ER models to relational schemas and state keys, foreign keys and other integrity constraints precisely, including as logical statements.</t>
+          <t>Formulate queries in relational algebra and relational calculus, prove simple equivalences between expressions, and explain the limits of their expressive power.</t>
         </is>
       </c>
       <c r="D4" s="103" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C5" s="104" t="inlineStr">
         <is>
-          <t>Express queries in relational algebra and relational calculus, prove simple equivalences, and reason about the expressive power of query languages.</t>
+          <t>Use SQL to define, populate, modify and query relational databases (joins, aggregation, subqueries, views, access from Python) and explain query results through SQL semantics (bag semantics, three-valued logic).</t>
         </is>
       </c>
       <c r="D5" s="103" t="n"/>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C6" s="104" t="inlineStr">
         <is>
-          <t>Write SQL to define, modify and query databases (joins, aggregation, subqueries, views, access from Python) and explain its semantics (bags, three-valued logic) by translation to algebra.</t>
+          <t>Analyze and improve relational schemas with functional dependency theory: compute closures, candidate keys and minimal covers, prove basic properties, decompose to 3NF/BCNF with lossless-join and dependency-preservation guarantees, and implement these algorithms in Python.</t>
         </is>
       </c>
       <c r="D6" s="103" t="n"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="C7" s="104" t="inlineStr">
         <is>
-          <t>Apply functional dependency theory: compute closures, keys and minimal covers, prove properties, normalize to 3NF/BCNF, verify lossless-join and dependency preservation, and implement these algorithms in Python.</t>
+          <t>Evaluate physical design and query execution choices (storage organization, indexes, join algorithms, execution plans) using I/O cost models and controlled experiments.</t>
         </is>
       </c>
       <c r="D7" s="103" t="n"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C8" s="104" t="inlineStr">
         <is>
-          <t>Analyze storage, indexing, query processing and optimization with I/O cost models, and evaluate index and plan choices experimentally.</t>
+          <t>Analyze concurrent executions for conflict serializability and recoverability, and justify concurrency-control and recovery mechanisms (two-phase locking, isolation levels, write-ahead logging).</t>
         </is>
       </c>
       <c r="D8" s="103" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C9" s="104" t="inlineStr">
         <is>
-          <t>Analyze schedules for conflict serializability and recoverability, explain locking, isolation levels and logging-based recovery, and justify the correctness of two-phase locking.</t>
+          <t>Conduct a small, reproducible research study on a database topic: review primary literature, formulate a research question or hypothesis, design and carry out an experiment or implementation, and report the results in an academic paper and presentation.</t>
         </is>
       </c>
       <c r="D9" s="103" t="n"/>
@@ -2741,20 +2741,10 @@
       <c r="T9" s="103" t="n"/>
       <c r="U9" s="103" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="129" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="130" t="inlineStr">
-        <is>
-          <t>CLO9</t>
-        </is>
-      </c>
-      <c r="C10" s="104" t="inlineStr">
-        <is>
-          <t>Conduct a small research study in databases: read primary literature, formulate a question or hypothesis, design a reproducible experiment or implementation, and report the results in an academic format.</t>
-        </is>
-      </c>
+    <row r="10">
+      <c r="A10" s="103" t="n"/>
+      <c r="B10" s="103" t="n"/>
+      <c r="C10" s="103" t="n"/>
       <c r="D10" s="103" t="n"/>
       <c r="E10" s="103" t="n"/>
       <c r="F10" s="103" t="n"/>
@@ -3100,31 +3090,17 @@
       <c r="U21" s="113" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="131" t="inlineStr">
-        <is>
-          <t>CLO9</t>
-        </is>
-      </c>
-      <c r="B22" s="106" t="n"/>
-      <c r="C22" s="107" t="n"/>
-      <c r="D22" s="106" t="n"/>
+      <c r="A22" s="103" t="n"/>
+      <c r="B22" s="103" t="n"/>
+      <c r="C22" s="103" t="n"/>
+      <c r="D22" s="103" t="n"/>
       <c r="E22" s="103" t="n"/>
       <c r="F22" s="103" t="n"/>
       <c r="G22" s="103" t="n"/>
       <c r="H22" s="103" t="n"/>
       <c r="I22" s="103" t="n"/>
       <c r="J22" s="103" t="n"/>
-      <c r="K22" s="106" t="n"/>
-      <c r="L22" s="113" t="n"/>
-      <c r="M22" s="113" t="n"/>
-      <c r="N22" s="113" t="n"/>
-      <c r="O22" s="113" t="n"/>
-      <c r="P22" s="113" t="n"/>
-      <c r="Q22" s="113" t="n"/>
-      <c r="R22" s="113" t="n"/>
-      <c r="S22" s="113" t="n"/>
-      <c r="T22" s="113" t="n"/>
-      <c r="U22" s="113" t="n"/>
+      <c r="K22" s="103" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="103" t="n"/>
@@ -4846,7 +4822,7 @@
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
@@ -4897,7 +4873,7 @@
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
@@ -4951,7 +4927,7 @@
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
@@ -5002,7 +4978,7 @@
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
@@ -5057,7 +5033,7 @@
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO3</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E14" s="32" t="inlineStr">
@@ -5108,7 +5084,7 @@
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
@@ -5158,7 +5134,7 @@
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
@@ -5219,7 +5195,7 @@
       </c>
       <c r="D17" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
@@ -5271,7 +5247,7 @@
       </c>
       <c r="D18" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E18" s="32" t="inlineStr">
@@ -5321,7 +5297,7 @@
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
@@ -5370,7 +5346,7 @@
       </c>
       <c r="D20" s="32" t="inlineStr">
         <is>
-          <t>CLO1, CLO2, CLO3, CLO4</t>
+          <t>CLO1, CLO2, CLO3</t>
         </is>
       </c>
       <c r="E20" s="32" t="inlineStr">
@@ -5419,7 +5395,7 @@
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
@@ -5470,7 +5446,7 @@
       </c>
       <c r="D22" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E22" s="32" t="inlineStr">
@@ -5521,7 +5497,7 @@
       </c>
       <c r="D23" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
@@ -5571,7 +5547,7 @@
       </c>
       <c r="D24" s="32" t="inlineStr">
         <is>
-          <t>CLO3, CLO5</t>
+          <t>CLO2, CLO4</t>
         </is>
       </c>
       <c r="E24" s="32" t="inlineStr">
@@ -5619,7 +5595,7 @@
       </c>
       <c r="D25" s="32" t="inlineStr">
         <is>
-          <t>CLO3, CLO5</t>
+          <t>CLO2, CLO4</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
@@ -5667,7 +5643,7 @@
       </c>
       <c r="D26" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E26" s="32" t="inlineStr">
@@ -5718,7 +5694,7 @@
       </c>
       <c r="D27" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
@@ -5768,7 +5744,7 @@
       </c>
       <c r="D28" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E28" s="32" t="inlineStr">
@@ -5818,7 +5794,7 @@
       </c>
       <c r="D29" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
@@ -5865,7 +5841,7 @@
       </c>
       <c r="D30" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E30" s="32" t="inlineStr">
@@ -5915,7 +5891,7 @@
       </c>
       <c r="D31" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
@@ -5966,7 +5942,7 @@
       </c>
       <c r="D32" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E32" s="32" t="inlineStr">
@@ -6016,7 +5992,7 @@
       </c>
       <c r="D33" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
@@ -6063,7 +6039,7 @@
       </c>
       <c r="D34" s="32" t="inlineStr">
         <is>
-          <t>CLO4, CLO5</t>
+          <t>CLO3, CLO4</t>
         </is>
       </c>
       <c r="E34" s="32" t="inlineStr">
@@ -6110,7 +6086,7 @@
       </c>
       <c r="D35" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
@@ -6161,7 +6137,7 @@
       </c>
       <c r="D36" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E36" s="32" t="inlineStr">
@@ -6211,7 +6187,7 @@
       </c>
       <c r="D37" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
@@ -6261,7 +6237,7 @@
       </c>
       <c r="D38" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E38" s="32" t="inlineStr">
@@ -6308,7 +6284,7 @@
       </c>
       <c r="D39" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO3, CLO4, CLO9</t>
+          <t>CLO2, CLO3, CLO8</t>
         </is>
       </c>
       <c r="E39" s="32" t="inlineStr">
@@ -6356,7 +6332,7 @@
       </c>
       <c r="D40" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E40" s="32" t="inlineStr">
@@ -6406,7 +6382,7 @@
       </c>
       <c r="D41" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E41" s="32" t="inlineStr">
@@ -6457,7 +6433,7 @@
       </c>
       <c r="D42" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E42" s="32" t="inlineStr">
@@ -6507,7 +6483,7 @@
       </c>
       <c r="D43" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E43" s="32" t="inlineStr">
@@ -6557,7 +6533,7 @@
       </c>
       <c r="D44" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E44" s="32" t="inlineStr">
@@ -6609,7 +6585,7 @@
       </c>
       <c r="D45" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E45" s="32" t="inlineStr">
@@ -6659,7 +6635,7 @@
       </c>
       <c r="D46" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E46" s="32" t="inlineStr">
@@ -6708,7 +6684,7 @@
       </c>
       <c r="D47" s="32" t="inlineStr">
         <is>
-          <t>CLO5, CLO6</t>
+          <t>CLO4, CLO5</t>
         </is>
       </c>
       <c r="E47" s="32" t="inlineStr">
@@ -6756,7 +6732,7 @@
       </c>
       <c r="D48" s="32" t="inlineStr">
         <is>
-          <t>CLO7</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E48" s="32" t="inlineStr">
@@ -6806,7 +6782,7 @@
       </c>
       <c r="D49" s="32" t="inlineStr">
         <is>
-          <t>CLO7</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E49" s="32" t="inlineStr">
@@ -6857,7 +6833,7 @@
       </c>
       <c r="D50" s="32" t="inlineStr">
         <is>
-          <t>CLO7</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E50" s="32" t="inlineStr">
@@ -6909,7 +6885,7 @@
       </c>
       <c r="D51" s="32" t="inlineStr">
         <is>
-          <t>CLO7</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E51" s="32" t="inlineStr">
@@ -6960,7 +6936,7 @@
       </c>
       <c r="D52" s="32" t="inlineStr">
         <is>
-          <t>CLO7, CLO9</t>
+          <t>CLO6, CLO8</t>
         </is>
       </c>
       <c r="E52" s="32" t="inlineStr">
@@ -7011,7 +6987,7 @@
       </c>
       <c r="D53" s="32" t="inlineStr">
         <is>
-          <t>CLO8</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E53" s="32" t="inlineStr">
@@ -7062,7 +7038,7 @@
       </c>
       <c r="D54" s="32" t="inlineStr">
         <is>
-          <t>CLO8</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E54" s="32" t="inlineStr">
@@ -7114,7 +7090,7 @@
       </c>
       <c r="D55" s="32" t="inlineStr">
         <is>
-          <t>CLO8</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E55" s="32" t="inlineStr">
@@ -7166,7 +7142,7 @@
       </c>
       <c r="D56" s="32" t="inlineStr">
         <is>
-          <t>CLO8</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E56" s="32" t="inlineStr">
@@ -7216,7 +7192,7 @@
       </c>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t>CLO8</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
@@ -7264,7 +7240,7 @@
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>CLO9</t>
+          <t>CLO8</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
@@ -7311,7 +7287,7 @@
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>CLO7, CLO8, CLO9</t>
+          <t>CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
@@ -7358,7 +7334,7 @@
       </c>
       <c r="D60" s="32" t="inlineStr">
         <is>
-          <t>CLO7, CLO8, CLO9</t>
+          <t>CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E60" s="32" t="inlineStr">
@@ -7406,7 +7382,7 @@
       </c>
       <c r="D61" s="32" t="inlineStr">
         <is>
-          <t>CLO1–CLO9</t>
+          <t>CLO1–CLO8</t>
         </is>
       </c>
       <c r="E61" s="32" t="inlineStr">
@@ -7644,7 +7620,7 @@
       </c>
       <c r="H3" s="72" t="inlineStr">
         <is>
-          <t>CLO1, CLO2, CLO3, CLO4</t>
+          <t>CLO1, CLO2, CLO3</t>
         </is>
       </c>
       <c r="I3" s="25" t="inlineStr">
@@ -7711,7 +7687,7 @@
       </c>
       <c r="H4" s="72" t="inlineStr">
         <is>
-          <t>CLO5, CLO6</t>
+          <t>CLO4, CLO5</t>
         </is>
       </c>
       <c r="I4" s="25" t="inlineStr">
@@ -7778,7 +7754,7 @@
       </c>
       <c r="H5" s="72" t="inlineStr">
         <is>
-          <t>CLO2, CLO3, CLO4, CLO9</t>
+          <t>CLO2, CLO3, CLO8</t>
         </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
@@ -7841,7 +7817,7 @@
       </c>
       <c r="H6" s="72" t="inlineStr">
         <is>
-          <t>CLO6, CLO7, CLO8, CLO9</t>
+          <t>CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="I6" s="25" t="inlineStr">
@@ -7904,7 +7880,7 @@
       </c>
       <c r="H7" s="72" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="I7" s="25" t="inlineStr">
@@ -7967,7 +7943,7 @@
       </c>
       <c r="H8" s="72" t="inlineStr">
         <is>
-          <t>CLO1, CLO2, CLO3, CLO4, CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO1, CLO2, CLO3, CLO4, CLO5, CLO6, CLO7</t>
         </is>
       </c>
       <c r="I8" s="25" t="inlineStr">

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -583,7 +583,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -949,6 +949,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2767,7 +2773,7 @@
     <row r="11">
       <c r="A11" s="120" t="inlineStr">
         <is>
-          <t>Mapping of CLOs to PLOs of Curriculum BCS_AD (K22A) – to be completed when the program PLO list is confirmed</t>
+          <t>Mapping of CLOs to PLOs of Curriculum BCS_AD (K22A, 13 PLOs)</t>
         </is>
       </c>
     </row>
@@ -2849,26 +2855,10 @@
           <t>PLO13</t>
         </is>
       </c>
-      <c r="O13" s="105" t="inlineStr">
-        <is>
-          <t>PLO14</t>
-        </is>
-      </c>
-      <c r="P13" s="105" t="inlineStr">
-        <is>
-          <t>PLO15</t>
-        </is>
-      </c>
-      <c r="Q13" s="105" t="inlineStr">
-        <is>
-          <t>PLO16</t>
-        </is>
-      </c>
-      <c r="R13" s="105" t="inlineStr">
-        <is>
-          <t>PLO17</t>
-        </is>
-      </c>
+      <c r="O13" s="105" t="n"/>
+      <c r="P13" s="105" t="n"/>
+      <c r="Q13" s="105" t="n"/>
+      <c r="R13" s="105" t="n"/>
       <c r="S13" s="105" t="n"/>
       <c r="T13" s="105" t="n"/>
       <c r="U13" s="105" t="n"/>
@@ -2880,7 +2870,11 @@
         </is>
       </c>
       <c r="B14" s="106" t="n"/>
-      <c r="C14" s="107" t="n"/>
+      <c r="C14" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="D14" s="106" t="n"/>
       <c r="E14" s="103" t="n"/>
       <c r="F14" s="103" t="n"/>
@@ -2907,10 +2901,18 @@
         </is>
       </c>
       <c r="B15" s="106" t="n"/>
-      <c r="C15" s="107" t="n"/>
+      <c r="C15" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="D15" s="106" t="n"/>
       <c r="E15" s="103" t="n"/>
-      <c r="F15" s="103" t="n"/>
+      <c r="F15" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="G15" s="103" t="n"/>
       <c r="H15" s="103" t="n"/>
       <c r="I15" s="103" t="n"/>
@@ -2934,10 +2936,18 @@
         </is>
       </c>
       <c r="B16" s="106" t="n"/>
-      <c r="C16" s="107" t="n"/>
+      <c r="C16" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="D16" s="106" t="n"/>
       <c r="E16" s="103" t="n"/>
-      <c r="F16" s="103" t="n"/>
+      <c r="F16" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="G16" s="103" t="n"/>
       <c r="H16" s="103" t="n"/>
       <c r="I16" s="103" t="n"/>
@@ -2961,13 +2971,21 @@
         </is>
       </c>
       <c r="B17" s="106" t="n"/>
-      <c r="C17" s="107" t="n"/>
+      <c r="C17" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="D17" s="106" t="n"/>
       <c r="E17" s="103" t="n"/>
       <c r="F17" s="103" t="n"/>
       <c r="G17" s="103" t="n"/>
       <c r="H17" s="103" t="n"/>
-      <c r="I17" s="103" t="n"/>
+      <c r="I17" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="J17" s="103" t="n"/>
       <c r="K17" s="106" t="n"/>
       <c r="L17" s="113" t="n"/>
@@ -2988,13 +3006,25 @@
         </is>
       </c>
       <c r="B18" s="106" t="n"/>
-      <c r="C18" s="107" t="n"/>
+      <c r="C18" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="D18" s="106" t="n"/>
       <c r="E18" s="103" t="n"/>
-      <c r="F18" s="103" t="n"/>
+      <c r="F18" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="G18" s="103" t="n"/>
       <c r="H18" s="103" t="n"/>
-      <c r="I18" s="103" t="n"/>
+      <c r="I18" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="J18" s="103" t="n"/>
       <c r="K18" s="106" t="n"/>
       <c r="L18" s="113" t="n"/>
@@ -3015,14 +3045,26 @@
         </is>
       </c>
       <c r="B19" s="106" t="n"/>
-      <c r="C19" s="107" t="n"/>
+      <c r="C19" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="D19" s="106" t="n"/>
       <c r="E19" s="103" t="n"/>
-      <c r="F19" s="103" t="n"/>
+      <c r="F19" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="G19" s="103" t="n"/>
       <c r="H19" s="103" t="n"/>
       <c r="I19" s="103" t="n"/>
-      <c r="J19" s="103" t="n"/>
+      <c r="J19" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="K19" s="106" t="n"/>
       <c r="L19" s="113" t="n"/>
       <c r="M19" s="113" t="n"/>
@@ -3042,7 +3084,11 @@
         </is>
       </c>
       <c r="B20" s="106" t="n"/>
-      <c r="C20" s="107" t="n"/>
+      <c r="C20" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="D20" s="106" t="n"/>
       <c r="E20" s="103" t="n"/>
       <c r="F20" s="103" t="n"/>
@@ -3069,16 +3115,32 @@
         </is>
       </c>
       <c r="B21" s="106" t="n"/>
-      <c r="C21" s="107" t="n"/>
+      <c r="C21" s="132" t="n"/>
       <c r="D21" s="106" t="n"/>
       <c r="E21" s="103" t="n"/>
-      <c r="F21" s="103" t="n"/>
+      <c r="F21" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="G21" s="103" t="n"/>
-      <c r="H21" s="103" t="n"/>
+      <c r="H21" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="I21" s="103" t="n"/>
       <c r="J21" s="103" t="n"/>
-      <c r="K21" s="106" t="n"/>
-      <c r="L21" s="113" t="n"/>
+      <c r="K21" s="132" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
+      <c r="L21" s="133" t="inlineStr">
+        <is>
+          <t>ü</t>
+        </is>
+      </c>
       <c r="M21" s="113" t="n"/>
       <c r="N21" s="113" t="n"/>
       <c r="O21" s="113" t="n"/>
@@ -3222,594 +3284,594 @@
       </c>
     </row>
     <row r="2" ht="13.8" customHeight="1">
-      <c r="A2" s="132" t="n">
+      <c r="A2" s="134" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="133" t="n">
+      <c r="B2" s="135" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="134" t="inlineStr">
+      <c r="C2" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D2" s="135" t="inlineStr">
+      <c r="D2" s="137" t="inlineStr">
         <is>
           <t>Codd separated the logical view of data from its physical storage. What would be lost if applications had to know how and where each record is stored?</t>
         </is>
       </c>
     </row>
     <row r="3" ht="13.8" customHeight="1">
-      <c r="A3" s="132" t="n">
+      <c r="A3" s="134" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="133" t="n">
+      <c r="B3" s="135" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="134" t="inlineStr">
+      <c r="C3" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D3" s="135" t="inlineStr">
+      <c r="D3" s="137" t="inlineStr">
         <is>
           <t>Why do new data models (XML, document, graph, vector) keep appearing, and why do many of them end up adding SQL-like features?</t>
         </is>
       </c>
     </row>
     <row r="4" ht="13.8" customHeight="1">
-      <c r="A4" s="132" t="n">
+      <c r="A4" s="134" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="133" t="n">
+      <c r="B4" s="135" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="134" t="inlineStr">
+      <c r="C4" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D4" s="135" t="inlineStr">
+      <c r="D4" s="137" t="inlineStr">
         <is>
           <t>When is a database system NOT the right tool? Give a concrete example and justify it.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13.8" customHeight="1">
-      <c r="A5" s="132" t="n">
+      <c r="A5" s="134" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="133" t="n">
+      <c r="B5" s="135" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="134" t="inlineStr">
+      <c r="C5" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D5" s="135" t="inlineStr">
+      <c r="D5" s="137" t="inlineStr">
         <is>
           <t>Why is Grade an attribute of the enrollment relationship and not of STUDENT or SECTION? What goes wrong if it is placed on either entity?</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13.8" customHeight="1">
-      <c r="A6" s="132" t="n">
+      <c r="A6" s="134" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="133" t="n">
+      <c r="B6" s="135" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="134" t="inlineStr">
+      <c r="C6" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D6" s="135" t="inlineStr">
+      <c r="D6" s="137" t="inlineStr">
         <is>
           <t>Is a ternary relationship always equivalent to three binary relationships? Construct a counterexample.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="13.8" customHeight="1">
-      <c r="A7" s="132" t="n">
+      <c r="A7" s="134" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="133" t="n">
+      <c r="B7" s="135" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="134" t="inlineStr">
+      <c r="C7" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D7" s="135" t="inlineStr">
+      <c r="D7" s="137" t="inlineStr">
         <is>
           <t>Give a business rule of UniversityDB that cannot be drawn in an ER diagram. How should a designer record and enforce it?</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13.8" customHeight="1">
-      <c r="A8" s="132" t="n">
+      <c r="A8" s="134" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="133" t="n">
+      <c r="B8" s="135" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="134" t="inlineStr">
+      <c r="C8" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D8" s="135" t="inlineStr">
+      <c r="D8" s="137" t="inlineStr">
         <is>
           <t>What would break if relations were allowed to contain duplicate tuples? Consider keys, projection and the meaning of a fact.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="13.8" customHeight="1">
-      <c r="A9" s="132" t="n">
+      <c r="A9" s="134" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="133" t="n">
+      <c r="B9" s="135" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="134" t="inlineStr">
+      <c r="C9" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D9" s="135" t="inlineStr">
+      <c r="D9" s="137" t="inlineStr">
         <is>
           <t>Why is NULL allowed in a foreign key but not in a primary key? Argue from what each constraint means.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="13.8" customHeight="1">
-      <c r="A10" s="132" t="n">
+      <c r="A10" s="134" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="133" t="n">
+      <c r="B10" s="135" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="134" t="inlineStr">
+      <c r="C10" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D10" s="135" t="inlineStr">
+      <c r="D10" s="137" t="inlineStr">
         <is>
           <t>A 1:1 relationship can be mapped with a foreign key on either side, or by merging the two relations. How would you decide, and what evidence would you use?</t>
         </is>
       </c>
     </row>
     <row r="11" ht="13.8" customHeight="1">
-      <c r="A11" s="132" t="n">
+      <c r="A11" s="134" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="133" t="n">
+      <c r="B11" s="135" t="n">
         <v>17</v>
       </c>
-      <c r="C11" s="134" t="inlineStr">
+      <c r="C11" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D11" s="135" t="inlineStr">
+      <c r="D11" s="137" t="inlineStr">
         <is>
           <t>Why does projection remove duplicates in relational algebra while SELECT in SQL does not? What are the costs and benefits of each choice?</t>
         </is>
       </c>
     </row>
     <row r="12" ht="13.8" customHeight="1">
-      <c r="A12" s="132" t="n">
+      <c r="A12" s="134" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="133" t="n">
+      <c r="B12" s="135" t="n">
         <v>17</v>
       </c>
-      <c r="C12" s="134" t="inlineStr">
+      <c r="C12" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D12" s="135" t="inlineStr">
+      <c r="D12" s="137" t="inlineStr">
         <is>
           <t>Division expresses 'for all' queries. Why is there no basic 'for all' operator, and how does calculus express the same idea?</t>
         </is>
       </c>
     </row>
     <row r="13" ht="13.8" customHeight="1">
-      <c r="A13" s="132" t="n">
+      <c r="A13" s="134" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="133" t="n">
+      <c r="B13" s="135" t="n">
         <v>17</v>
       </c>
-      <c r="C13" s="134" t="inlineStr">
+      <c r="C13" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D13" s="135" t="inlineStr">
+      <c r="D13" s="137" t="inlineStr">
         <is>
           <t>Relational algebra cannot compute the transitive closure of a relation. Why does a fixed-size expression limit what a language can express?</t>
         </is>
       </c>
     </row>
     <row r="14" ht="13.8" customHeight="1">
-      <c r="A14" s="132" t="n">
+      <c r="A14" s="134" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="133" t="n">
+      <c r="B14" s="135" t="n">
         <v>22</v>
       </c>
-      <c r="C14" s="134" t="inlineStr">
+      <c r="C14" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D14" s="135" t="inlineStr">
+      <c r="D14" s="137" t="inlineStr">
         <is>
           <t>Why should integrity rules be declared in the database rather than checked in application code? When is the opposite true?</t>
         </is>
       </c>
     </row>
     <row r="15" ht="13.8" customHeight="1">
-      <c r="A15" s="132" t="n">
+      <c r="A15" s="134" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="133" t="n">
+      <c r="B15" s="135" t="n">
         <v>22</v>
       </c>
-      <c r="C15" s="134" t="inlineStr">
+      <c r="C15" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D15" s="135" t="inlineStr">
+      <c r="D15" s="137" t="inlineStr">
         <is>
           <t>Why do almost no DBMSs implement CREATE ASSERTION, although it is in the SQL standard?</t>
         </is>
       </c>
     </row>
     <row r="16" ht="13.8" customHeight="1">
-      <c r="A16" s="132" t="n">
+      <c r="A16" s="134" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="133" t="n">
+      <c r="B16" s="135" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="134" t="inlineStr">
+      <c r="C16" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D16" s="135" t="inlineStr">
+      <c r="D16" s="137" t="inlineStr">
         <is>
           <t>ON DELETE CASCADE is convenient. What risks does it create, and how could a cascade chain surprise a user?</t>
         </is>
       </c>
     </row>
     <row r="17" ht="13.8" customHeight="1">
-      <c r="A17" s="132" t="n">
+      <c r="A17" s="134" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="133" t="n">
+      <c r="B17" s="135" t="n">
         <v>26</v>
       </c>
-      <c r="C17" s="134" t="inlineStr">
+      <c r="C17" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D17" s="135" t="inlineStr">
+      <c r="D17" s="137" t="inlineStr">
         <is>
           <t>Under three-valued logic, 'p OR NOT p' is not always true. Which everyday query mistakes follow from this?</t>
         </is>
       </c>
     </row>
     <row r="18" ht="13.8" customHeight="1">
-      <c r="A18" s="132" t="n">
+      <c r="A18" s="134" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="133" t="n">
+      <c r="B18" s="135" t="n">
         <v>26</v>
       </c>
-      <c r="C18" s="134" t="inlineStr">
+      <c r="C18" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D18" s="135" t="inlineStr">
+      <c r="D18" s="137" t="inlineStr">
         <is>
           <t>Why does 'x NOT IN (subquery)' return no rows when the subquery contains NULL, while NOT EXISTS behaves differently?</t>
         </is>
       </c>
     </row>
     <row r="19" ht="13.8" customHeight="1">
-      <c r="A19" s="132" t="n">
+      <c r="A19" s="134" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="133" t="n">
+      <c r="B19" s="135" t="n">
         <v>26</v>
       </c>
-      <c r="C19" s="134" t="inlineStr">
+      <c r="C19" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D19" s="135" t="inlineStr">
+      <c r="D19" s="137" t="inlineStr">
         <is>
           <t>Which algebraic laws that hold for sets fail for bags? Why did SQL choose bag semantics anyway?</t>
         </is>
       </c>
     </row>
     <row r="20" ht="13.8" customHeight="1">
-      <c r="A20" s="132" t="n">
+      <c r="A20" s="134" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="133" t="n">
+      <c r="B20" s="135" t="n">
         <v>31</v>
       </c>
-      <c r="C20" s="134" t="inlineStr">
+      <c r="C20" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D20" s="135" t="inlineStr">
+      <c r="D20" s="137" t="inlineStr">
         <is>
           <t>A correlated subquery is evaluated 'once per outer row' in the textbook model. How could a DBMS evaluate it more efficiently?</t>
         </is>
       </c>
     </row>
     <row r="21" ht="13.8" customHeight="1">
-      <c r="A21" s="132" t="n">
+      <c r="A21" s="134" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="133" t="n">
+      <c r="B21" s="135" t="n">
         <v>31</v>
       </c>
-      <c r="C21" s="134" t="inlineStr">
+      <c r="C21" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D21" s="135" t="inlineStr">
+      <c r="D21" s="137" t="inlineStr">
         <is>
           <t>The same query can often be written with a join, a subquery or a set operation. Should the choice affect performance? Why or why not?</t>
         </is>
       </c>
     </row>
     <row r="22" ht="13.8" customHeight="1">
-      <c r="A22" s="132" t="n">
+      <c r="A22" s="134" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="133" t="n">
+      <c r="B22" s="135" t="n">
         <v>31</v>
       </c>
-      <c r="C22" s="134" t="inlineStr">
+      <c r="C22" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D22" s="135" t="inlineStr">
+      <c r="D22" s="137" t="inlineStr">
         <is>
           <t>Why did it take until 2017 to give SQL a complete formal semantics?</t>
         </is>
       </c>
     </row>
     <row r="23" ht="13.8" customHeight="1">
-      <c r="A23" s="132" t="n">
+      <c r="A23" s="134" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="133" t="n">
+      <c r="B23" s="135" t="n">
         <v>35</v>
       </c>
-      <c r="C23" s="134" t="inlineStr">
+      <c r="C23" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D23" s="135" t="inlineStr">
+      <c r="D23" s="137" t="inlineStr">
         <is>
           <t>Deleting a row through a join view can be translated in more than one way. Which translation should the DBMS choose, and why?</t>
         </is>
       </c>
     </row>
     <row r="24" ht="13.8" customHeight="1">
-      <c r="A24" s="132" t="n">
+      <c r="A24" s="134" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="133" t="n">
+      <c r="B24" s="135" t="n">
         <v>35</v>
       </c>
-      <c r="C24" s="134" t="inlineStr">
+      <c r="C24" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D24" s="135" t="inlineStr">
+      <c r="D24" s="137" t="inlineStr">
         <is>
           <t>A view costs nothing extra at run time. How is that possible?</t>
         </is>
       </c>
     </row>
     <row r="25" ht="13.8" customHeight="1">
-      <c r="A25" s="132" t="n">
+      <c r="A25" s="134" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="133" t="n">
+      <c r="B25" s="135" t="n">
         <v>35</v>
       </c>
-      <c r="C25" s="134" t="inlineStr">
+      <c r="C25" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D25" s="135" t="inlineStr">
+      <c r="D25" s="137" t="inlineStr">
         <is>
           <t>Why do parameterized queries prevent SQL injection, while escaping user input is considered fragile?</t>
         </is>
       </c>
     </row>
     <row r="26" ht="13.8" customHeight="1">
-      <c r="A26" s="132" t="n">
+      <c r="A26" s="134" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="133" t="n">
+      <c r="B26" s="135" t="n">
         <v>44</v>
       </c>
-      <c r="C26" s="134" t="inlineStr">
+      <c r="C26" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D26" s="135" t="inlineStr">
+      <c r="D26" s="137" t="inlineStr">
         <is>
           <t>Every normal form can be seen as removing one kind of redundancy. What single idea unifies them?</t>
         </is>
       </c>
     </row>
     <row r="27" ht="13.8" customHeight="1">
-      <c r="A27" s="132" t="n">
+      <c r="A27" s="134" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="133" t="n">
+      <c r="B27" s="135" t="n">
         <v>44</v>
       </c>
-      <c r="C27" s="134" t="inlineStr">
+      <c r="C27" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D27" s="135" t="inlineStr">
+      <c r="D27" s="137" t="inlineStr">
         <is>
           <t>BCNF decomposition may lose a dependency. When would you accept 3NF instead, and what do you gain?</t>
         </is>
       </c>
     </row>
     <row r="28" ht="13.8" customHeight="1">
-      <c r="A28" s="132" t="n">
+      <c r="A28" s="134" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="133" t="n">
+      <c r="B28" s="135" t="n">
         <v>44</v>
       </c>
-      <c r="C28" s="134" t="inlineStr">
+      <c r="C28" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D28" s="135" t="inlineStr">
+      <c r="D28" s="137" t="inlineStr">
         <is>
           <t>Testing whether an attribute is prime is NP-complete. What does this mean for automatic schema design tools?</t>
         </is>
       </c>
     </row>
     <row r="29" ht="13.8" customHeight="1">
-      <c r="A29" s="132" t="n">
+      <c r="A29" s="134" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="133" t="n">
+      <c r="B29" s="135" t="n">
         <v>50</v>
       </c>
-      <c r="C29" s="134" t="inlineStr">
+      <c r="C29" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D29" s="135" t="inlineStr">
+      <c r="D29" s="137" t="inlineStr">
         <is>
           <t>Why is a B-tree node the size of a disk page instead of holding a single key as in a binary search tree?</t>
         </is>
       </c>
     </row>
     <row r="30" ht="13.8" customHeight="1">
-      <c r="A30" s="132" t="n">
+      <c r="A30" s="134" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="133" t="n">
+      <c r="B30" s="135" t="n">
         <v>50</v>
       </c>
-      <c r="C30" s="134" t="inlineStr">
+      <c r="C30" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D30" s="135" t="inlineStr">
+      <c r="D30" s="137" t="inlineStr">
         <is>
           <t>The optimizer relies on estimates. What happens when the estimates are wrong, and where do the errors come from?</t>
         </is>
       </c>
     </row>
     <row r="31" ht="13.8" customHeight="1">
-      <c r="A31" s="132" t="n">
+      <c r="A31" s="134" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="133" t="n">
+      <c r="B31" s="135" t="n">
         <v>50</v>
       </c>
-      <c r="C31" s="134" t="inlineStr">
+      <c r="C31" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D31" s="135" t="inlineStr">
+      <c r="D31" s="137" t="inlineStr">
         <is>
           <t>Could a machine-learning model replace an index? What would you need to measure to decide?</t>
         </is>
       </c>
     </row>
     <row r="32" ht="13.8" customHeight="1">
-      <c r="A32" s="132" t="n">
+      <c r="A32" s="134" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="133" t="n">
+      <c r="B32" s="135" t="n">
         <v>55</v>
       </c>
-      <c r="C32" s="134" t="inlineStr">
+      <c r="C32" s="136" t="inlineStr">
         <is>
           <t>CQ1</t>
         </is>
       </c>
-      <c r="D32" s="135" t="inlineStr">
+      <c r="D32" s="137" t="inlineStr">
         <is>
           <t>Why is serializability the accepted correctness criterion for concurrent transactions? What weaker criteria do real systems use, and why?</t>
         </is>
       </c>
     </row>
     <row r="33" ht="13.8" customHeight="1">
-      <c r="A33" s="132" t="n">
+      <c r="A33" s="134" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="133" t="n">
+      <c r="B33" s="135" t="n">
         <v>55</v>
       </c>
-      <c r="C33" s="134" t="inlineStr">
+      <c r="C33" s="136" t="inlineStr">
         <is>
           <t>CQ2</t>
         </is>
       </c>
-      <c r="D33" s="135" t="inlineStr">
+      <c r="D33" s="137" t="inlineStr">
         <is>
           <t>Why does two-phase locking guarantee serializability? Explain the idea of the lock point.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13.8" customHeight="1">
-      <c r="A34" s="132" t="n">
+      <c r="A34" s="134" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="133" t="n">
+      <c r="B34" s="135" t="n">
         <v>55</v>
       </c>
-      <c r="C34" s="134" t="inlineStr">
+      <c r="C34" s="136" t="inlineStr">
         <is>
           <t>CQ3</t>
         </is>
       </c>
-      <c r="D34" s="135" t="inlineStr">
+      <c r="D34" s="137" t="inlineStr">
         <is>
           <t>Snapshot isolation prevents dirty reads, non-repeatable reads and phantoms. Why is it still not serializable?</t>
         </is>
@@ -7977,7 +8039,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="136" t="inlineStr">
+      <c r="B9" s="138" t="inlineStr">
         <is>
           <t>Total</t>
         </is>

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -1583,7 +1583,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="190" customFormat="1" customHeight="1" s="10">
+    <row r="12" ht="125" customFormat="1" customHeight="1" s="10">
       <c r="A12" s="78" t="n">
         <v>11</v>
       </c>
@@ -1595,7 +1595,14 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>This course gives a rigorous, research-oriented introduction to database systems for talented first-year Computer Science students. Students model data with the Entity-Relationship model and map it to the relational model, which is studied as a mathematical structure. They express queries in relational algebra, relational calculus and SQL, and reason about the semantics and expressive power of these languages. Functional dependency theory is developed with proofs and algorithms and applied to normalization. The course then opens the DBMS: storage and indexing under an I/O cost model, query processing and optimization, and the theory of transactions, concurrency control and recovery. Every chapter includes a 'Research Corner' built around a seminal paper, and students implement core algorithms in Python and carry out reproducible experiments. At the end of the course, students can design normalized schemas, query databases proficiently in SQL, explain the internal mechanisms of storage and transaction control, and conduct and report a small research study in the database field.</t>
+          <t>This course aims to help students:
+- understand the basic concepts of database systems and the relational model;
+- design databases with the Entity-Relationship model and convert them into relational schemas;
+- write queries in relational algebra, relational calculus and SQL;
+- use functional dependencies to evaluate and normalize a database design;
+- explain how a DBMS stores data, uses indexes and processes queries;
+- explain how transactions, concurrency control and recovery keep data correct;
+- read research papers and carry out small experiments on database topics.</t>
         </is>
       </c>
     </row>

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -1620,8 +1620,9 @@
         <is>
           <t>- Students must attend at least 80% of contact slots in order to be accepted to the final examination.
 - Read the assigned textbook sections and the Research Corner paper BEFORE each theory session, and prepare answers to the constructivist questions.
-- Complete all 8 research labs, including the 'Investigate' part and the Python implementation tasks, and submit them on time.
+- Complete all 9 research labs, including the 'Investigate' part and the Python implementation tasks, and submit them on time.
 - Complete Assignment 1 (individual technical report) and Assignment 2 (group mini research project: short paper, reproducible code and presentation).
+- Complete the guided self-study readings listed in the schedule (abstract topics such as relational calculus, statistics estimation and recovery algorithms); they are assessed in the progress tests and the final exam.
 - Keep all code, scripts and measurements in a version-controlled repository so that results are reproducible.
 - Disclose any use of generative AI tools in submitted work; undisclosed use is treated as a breach of academic integrity.
 - Use laptop in class only for learning purpose.
@@ -1662,7 +1663,7 @@
       <c r="C15" s="21" t="inlineStr">
         <is>
           <t>1) On-going Assessment
-- 8 Research labs:                        10%
+- 9 Research labs:                        10%
 - 2 Progress tests:                        20%
 - Assignment 1 (technical report):   10%
 - Assignment 2 (research project):  20%
@@ -1843,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.2"/>
   <cols>
     <col width="3.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1932,7 +1933,7 @@
       </c>
       <c r="F2" s="127" t="inlineStr">
         <is>
-          <t>[DSC] Main textbook</t>
+          <t>[DSC] Main textbook. The schedule follows its chapters and cites sections and pages; Ch. 27 (online) is used for self-study</t>
         </is>
       </c>
       <c r="G2" s="127" t="inlineStr">
@@ -1967,7 +1968,7 @@
       </c>
       <c r="C3" s="128" t="inlineStr">
         <is>
-          <t>textbook</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="D3" s="128" t="inlineStr">
@@ -1982,7 +1983,7 @@
       </c>
       <c r="F3" s="127" t="inlineStr">
         <is>
-          <t>[DMS] Main textbook</t>
+          <t>[DMS] Secondary textbook for alternative explanations and extra exercises</t>
         </is>
       </c>
       <c r="G3" s="127" t="inlineStr">
@@ -2012,7 +2013,7 @@
       </c>
       <c r="B4" s="127" t="inlineStr">
         <is>
-          <t>A Relational Model of Data for Large Shared Data Banks</t>
+          <t>What Goes Around Comes Around… And Around…</t>
         </is>
       </c>
       <c r="C4" s="128" t="inlineStr">
@@ -2028,12 +2029,12 @@
       </c>
       <c r="F4" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 3. Communications of the ACM 13(6):377–387</t>
+          <t>Research Corner, Chapter 1. ACM SIGMOD Record 53(2)</t>
         </is>
       </c>
       <c r="G4" s="127" t="inlineStr">
         <is>
-          <t>E. F. Codd</t>
+          <t>Michael Stonebraker, Andrew Pavlo</t>
         </is>
       </c>
       <c r="H4" s="127" t="inlineStr">
@@ -2043,7 +2044,7 @@
       </c>
       <c r="I4" s="127" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J4" s="127" t="inlineStr"/>
@@ -2054,7 +2055,7 @@
       </c>
       <c r="B5" s="127" t="inlineStr">
         <is>
-          <t>The Entity-Relationship Model—Toward a Unified View of Data</t>
+          <t>A Relational Model of Data for Large Shared Data Banks</t>
         </is>
       </c>
       <c r="C5" s="128" t="inlineStr">
@@ -2070,12 +2071,12 @@
       </c>
       <c r="F5" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 2. ACM TODS 1(1):9–36</t>
+          <t>Research Corner, Chapter 2. Communications of the ACM 13(6):377–387</t>
         </is>
       </c>
       <c r="G5" s="127" t="inlineStr">
         <is>
-          <t>Peter P. Chen</t>
+          <t>E. F. Codd</t>
         </is>
       </c>
       <c r="H5" s="127" t="inlineStr">
@@ -2085,7 +2086,7 @@
       </c>
       <c r="I5" s="127" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="J5" s="127" t="inlineStr"/>
@@ -2096,7 +2097,7 @@
       </c>
       <c r="B6" s="127" t="inlineStr">
         <is>
-          <t>Relational Completeness of Data Base Sublanguages</t>
+          <t>SEQUEL: A Structured English Query Language</t>
         </is>
       </c>
       <c r="C6" s="128" t="inlineStr">
@@ -2112,22 +2113,22 @@
       </c>
       <c r="F6" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 4. In R. Rustin (ed.), Data Base Systems, pp. 65–98</t>
+          <t>Research Corner, Chapter 3. Proc. ACM SIGFIDET Workshop</t>
         </is>
       </c>
       <c r="G6" s="127" t="inlineStr">
         <is>
-          <t>E. F. Codd</t>
+          <t>Donald D. Chamberlin, Raymond F. Boyce</t>
         </is>
       </c>
       <c r="H6" s="127" t="inlineStr">
         <is>
-          <t>Prentice-Hall</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="I6" s="127" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="J6" s="127" t="inlineStr"/>
@@ -2138,7 +2139,7 @@
       </c>
       <c r="B7" s="127" t="inlineStr">
         <is>
-          <t>A Simple Guide to Five Normal Forms in Relational Database Theory</t>
+          <t>The Entity-Relationship Model—Toward a Unified View of Data</t>
         </is>
       </c>
       <c r="C7" s="128" t="inlineStr">
@@ -2154,12 +2155,12 @@
       </c>
       <c r="F7" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 8. Communications of the ACM 26(2):120–125</t>
+          <t>Research Corner, Chapter 5. ACM TODS 1(1):9–36</t>
         </is>
       </c>
       <c r="G7" s="127" t="inlineStr">
         <is>
-          <t>William Kent</t>
+          <t>Peter P. Chen</t>
         </is>
       </c>
       <c r="H7" s="127" t="inlineStr">
@@ -2169,7 +2170,7 @@
       </c>
       <c r="I7" s="127" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="J7" s="127" t="inlineStr"/>
@@ -2180,7 +2181,7 @@
       </c>
       <c r="B8" s="127" t="inlineStr">
         <is>
-          <t>Access Path Selection in a Relational Database Management System</t>
+          <t>A Simple Guide to Five Normal Forms in Relational Database Theory</t>
         </is>
       </c>
       <c r="C8" s="128" t="inlineStr">
@@ -2196,12 +2197,12 @@
       </c>
       <c r="F8" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 9. Proc. ACM SIGMOD</t>
+          <t>Research Corner, Chapter 6. Communications of the ACM 26(2):120–125</t>
         </is>
       </c>
       <c r="G8" s="127" t="inlineStr">
         <is>
-          <t>P. G. Selinger et al.</t>
+          <t>William Kent</t>
         </is>
       </c>
       <c r="H8" s="127" t="inlineStr">
@@ -2211,7 +2212,7 @@
       </c>
       <c r="I8" s="127" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="J8" s="127" t="inlineStr"/>
@@ -2222,7 +2223,7 @@
       </c>
       <c r="B9" s="127" t="inlineStr">
         <is>
-          <t>The Case for Learned Index Structures</t>
+          <t>Organization and Maintenance of Large Ordered Indexes</t>
         </is>
       </c>
       <c r="C9" s="128" t="inlineStr">
@@ -2238,22 +2239,22 @@
       </c>
       <c r="F9" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 9. Proc. ACM SIGMOD</t>
+          <t>Research Corner, Chapter 7. Acta Informatica 1:173–189</t>
         </is>
       </c>
       <c r="G9" s="127" t="inlineStr">
         <is>
-          <t>T. Kraska, A. Beutel, E. H. Chi, J. Dean, N. Polyzotis</t>
+          <t>Rudolf Bayer, Edward McCreight</t>
         </is>
       </c>
       <c r="H9" s="127" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>Springer</t>
         </is>
       </c>
       <c r="I9" s="127" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="J9" s="127" t="inlineStr"/>
@@ -2264,7 +2265,7 @@
       </c>
       <c r="B10" s="127" t="inlineStr">
         <is>
-          <t>A Critique of ANSI SQL Isolation Levels</t>
+          <t>The Case for Learned Index Structures</t>
         </is>
       </c>
       <c r="C10" s="128" t="inlineStr">
@@ -2280,12 +2281,12 @@
       </c>
       <c r="F10" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 10. Proc. ACM SIGMOD</t>
+          <t>Research Corner, Chapter 7. Proc. ACM SIGMOD</t>
         </is>
       </c>
       <c r="G10" s="127" t="inlineStr">
         <is>
-          <t>H. Berenson et al.</t>
+          <t>T. Kraska, A. Beutel, E. H. Chi, J. Dean, N. Polyzotis</t>
         </is>
       </c>
       <c r="H10" s="127" t="inlineStr">
@@ -2295,7 +2296,7 @@
       </c>
       <c r="I10" s="127" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="J10" s="127" t="inlineStr"/>
@@ -2306,7 +2307,7 @@
       </c>
       <c r="B11" s="127" t="inlineStr">
         <is>
-          <t>What Goes Around Comes Around… And Around…</t>
+          <t>Access Path Selection in a Relational Database Management System</t>
         </is>
       </c>
       <c r="C11" s="128" t="inlineStr">
@@ -2322,12 +2323,12 @@
       </c>
       <c r="F11" s="127" t="inlineStr">
         <is>
-          <t>Research Corner Ch. 1. ACM SIGMOD Record 53(2)</t>
+          <t>Research Corner, Chapter 8. Proc. ACM SIGMOD</t>
         </is>
       </c>
       <c r="G11" s="127" t="inlineStr">
         <is>
-          <t>Michael Stonebraker, Andrew Pavlo</t>
+          <t>P. G. Selinger et al.</t>
         </is>
       </c>
       <c r="H11" s="127" t="inlineStr">
@@ -2337,7 +2338,7 @@
       </c>
       <c r="I11" s="127" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="J11" s="127" t="inlineStr"/>
@@ -2348,7 +2349,7 @@
       </c>
       <c r="B12" s="127" t="inlineStr">
         <is>
-          <t>Transact-SQL reference</t>
+          <t>A Critique of ANSI SQL Isolation Levels</t>
         </is>
       </c>
       <c r="C12" s="128" t="inlineStr">
@@ -2364,70 +2365,109 @@
       </c>
       <c r="F12" s="127" t="inlineStr">
         <is>
+          <t>Research Corner, Chapter 9. Proc. ACM SIGMOD</t>
+        </is>
+      </c>
+      <c r="G12" s="127" t="inlineStr">
+        <is>
+          <t>H. Berenson et al.</t>
+        </is>
+      </c>
+      <c r="H12" s="127" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="I12" s="127" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="J12" s="127" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="127" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="127" t="inlineStr">
+        <is>
+          <t>Transact-SQL reference</t>
+        </is>
+      </c>
+      <c r="C13" s="128" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D13" s="128" t="inlineStr"/>
+      <c r="E13" s="127" t="inlineStr">
+        <is>
+          <t>online</t>
+        </is>
+      </c>
+      <c r="F13" s="127" t="inlineStr">
+        <is>
           <t>https://learn.microsoft.com/sql/t-sql/</t>
         </is>
       </c>
-      <c r="G12" s="127" t="inlineStr">
+      <c r="G13" s="127" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="H12" s="127" t="inlineStr">
+      <c r="H13" s="127" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="I12" s="127" t="inlineStr"/>
-      <c r="J12" s="127" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="116" t="n"/>
+      <c r="I13" s="127" t="inlineStr"/>
+      <c r="J13" s="127" t="inlineStr"/>
     </row>
     <row r="14" ht="26.4" customHeight="1">
       <c r="B14" s="117" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="119" t="inlineStr">
+      <c r="B15" s="116" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="119" t="inlineStr">
         <is>
           <t>Ghi rõ ISBN với sách hardcopy</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="116" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="114" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="114" t="inlineStr">
         <is>
           <t>Purpose: textbook or reference
 Type: hardcopy or online</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="116" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="116" t="inlineStr">
         <is>
           <t>Đối với các môn "m" hoặc "c"</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="117" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="117" t="inlineStr">
         <is>
           <t>MaterialDescription: Tên MOOC, 
                                   Eg. MOOC 1: Architecting Solutions on AWS</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="116" t="inlineStr">
-        <is>
-          <t>Author: Tên Trường/Côngty/Tổ chức biên soạn MOOC</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="B22" s="116" t="inlineStr">
+        <is>
+          <t>Author: Tên Trường/Côngty/Tổ chức biên soạn MOOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="116" t="inlineStr">
         <is>
           <t>Publisher: Coursera</t>
         </is>
@@ -3349,7 +3389,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="136" t="inlineStr">
         <is>
@@ -3358,7 +3398,7 @@
       </c>
       <c r="D5" s="137" t="inlineStr">
         <is>
-          <t>Why is Grade an attribute of the enrollment relationship and not of STUDENT or SECTION? What goes wrong if it is placed on either entity?</t>
+          <t>What would break if relations were allowed to contain duplicate tuples? Consider keys, projection and the meaning of a fact.</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3407,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="136" t="inlineStr">
         <is>
@@ -3376,7 +3416,7 @@
       </c>
       <c r="D6" s="137" t="inlineStr">
         <is>
-          <t>Is a ternary relationship always equivalent to three binary relationships? Construct a counterexample.</t>
+          <t>Division expresses 'for all' queries. Why is there no basic 'for all' operator, and how does relational calculus express the same idea?</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3425,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="135" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="136" t="inlineStr">
         <is>
@@ -3394,7 +3434,7 @@
       </c>
       <c r="D7" s="137" t="inlineStr">
         <is>
-          <t>Give a business rule of UniversityDB that cannot be drawn in an ER diagram. How should a designer record and enforce it?</t>
+          <t>Relational algebra cannot compute the transitive closure of a relation. Why does a fixed-size expression limit what a language can express?</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3452,7 @@
       </c>
       <c r="D8" s="137" t="inlineStr">
         <is>
-          <t>What would break if relations were allowed to contain duplicate tuples? Consider keys, projection and the meaning of a fact.</t>
+          <t>Under three-valued logic, 'p OR NOT p' is not always true. Which everyday query mistakes follow from this?</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3470,7 @@
       </c>
       <c r="D9" s="137" t="inlineStr">
         <is>
-          <t>Why is NULL allowed in a foreign key but not in a primary key? Argue from what each constraint means.</t>
+          <t>Why does 'x NOT IN (subquery)' return no rows when the subquery contains NULL, while NOT EXISTS behaves differently?</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3488,7 @@
       </c>
       <c r="D10" s="137" t="inlineStr">
         <is>
-          <t>A 1:1 relationship can be mapped with a foreign key on either side, or by merging the two relations. How would you decide, and what evidence would you use?</t>
+          <t>Which algebraic laws that hold for sets fail for bags? Why did SQL choose bag semantics anyway?</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3497,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="136" t="inlineStr">
         <is>
@@ -3466,7 +3506,7 @@
       </c>
       <c r="D11" s="137" t="inlineStr">
         <is>
-          <t>Why does projection remove duplicates in relational algebra while SELECT in SQL does not? What are the costs and benefits of each choice?</t>
+          <t>Why should integrity rules be declared in the database rather than checked in application code? When is the opposite true?</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3515,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" s="136" t="inlineStr">
         <is>
@@ -3484,7 +3524,7 @@
       </c>
       <c r="D12" s="137" t="inlineStr">
         <is>
-          <t>Division expresses 'for all' queries. Why is there no basic 'for all' operator, and how does calculus express the same idea?</t>
+          <t>A view costs nothing extra at run time. How is that possible, and when would a materialized view be better?</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3533,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="135" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="136" t="inlineStr">
         <is>
@@ -3502,7 +3542,7 @@
       </c>
       <c r="D13" s="137" t="inlineStr">
         <is>
-          <t>Relational algebra cannot compute the transitive closure of a relation. Why does a fixed-size expression limit what a language can express?</t>
+          <t>Why do parameterized queries prevent SQL injection, while escaping user input is considered fragile?</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3551,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="135" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="136" t="inlineStr">
         <is>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="D14" s="137" t="inlineStr">
         <is>
-          <t>Why should integrity rules be declared in the database rather than checked in application code? When is the opposite true?</t>
+          <t>Why is a grade an attribute of the enrollment relationship and not of STUDENT or SECTION? What goes wrong if it is placed on either entity?</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3569,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="135" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" s="136" t="inlineStr">
         <is>
@@ -3538,7 +3578,7 @@
       </c>
       <c r="D15" s="137" t="inlineStr">
         <is>
-          <t>Why do almost no DBMSs implement CREATE ASSERTION, although it is in the SQL standard?</t>
+          <t>Is a ternary relationship always equivalent to three binary relationships? Construct a counterexample.</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3587,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="135" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" s="136" t="inlineStr">
         <is>
@@ -3556,7 +3596,7 @@
       </c>
       <c r="D16" s="137" t="inlineStr">
         <is>
-          <t>ON DELETE CASCADE is convenient. What risks does it create, and how could a cascade chain surprise a user?</t>
+          <t>Give a business rule of the university database that cannot be drawn in an E-R diagram. How should a designer record and enforce it?</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="135" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C17" s="136" t="inlineStr">
         <is>
@@ -3574,7 +3614,7 @@
       </c>
       <c r="D17" s="137" t="inlineStr">
         <is>
-          <t>Under three-valued logic, 'p OR NOT p' is not always true. Which everyday query mistakes follow from this?</t>
+          <t>Every normal form can be seen as removing one kind of redundancy. What single idea unifies them?</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3623,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="135" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C18" s="136" t="inlineStr">
         <is>
@@ -3592,7 +3632,7 @@
       </c>
       <c r="D18" s="137" t="inlineStr">
         <is>
-          <t>Why does 'x NOT IN (subquery)' return no rows when the subquery contains NULL, while NOT EXISTS behaves differently?</t>
+          <t>BCNF decomposition may lose a dependency. When would you accept 3NF instead, and what do you gain?</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3641,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="135" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C19" s="136" t="inlineStr">
         <is>
@@ -3610,7 +3650,7 @@
       </c>
       <c r="D19" s="137" t="inlineStr">
         <is>
-          <t>Which algebraic laws that hold for sets fail for bags? Why did SQL choose bag semantics anyway?</t>
+          <t>Testing whether an attribute is prime is NP-complete. What does this mean for automatic schema design tools?</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3659,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="135" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C20" s="136" t="inlineStr">
         <is>
@@ -3628,7 +3668,7 @@
       </c>
       <c r="D20" s="137" t="inlineStr">
         <is>
-          <t>A correlated subquery is evaluated 'once per outer row' in the textbook model. How could a DBMS evaluate it more efficiently?</t>
+          <t>Why is a B+-tree node the size of a disk block instead of holding a single key as in a binary search tree?</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3677,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="135" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C21" s="136" t="inlineStr">
         <is>
@@ -3646,7 +3686,7 @@
       </c>
       <c r="D21" s="137" t="inlineStr">
         <is>
-          <t>The same query can often be written with a join, a subquery or a set operation. Should the choice affect performance? Why or why not?</t>
+          <t>When can a full table scan be cheaper than using an index? Design an experiment that shows it.</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3695,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="135" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C22" s="136" t="inlineStr">
         <is>
@@ -3664,7 +3704,7 @@
       </c>
       <c r="D22" s="137" t="inlineStr">
         <is>
-          <t>Why did it take until 2017 to give SQL a complete formal semantics?</t>
+          <t>Could a machine-learning model replace an index? What would you need to measure to decide?</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3713,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="135" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C23" s="136" t="inlineStr">
         <is>
@@ -3682,7 +3722,7 @@
       </c>
       <c r="D23" s="137" t="inlineStr">
         <is>
-          <t>Deleting a row through a join view can be translated in more than one way. Which translation should the DBMS choose, and why?</t>
+          <t>The optimizer relies on estimates. What happens when the estimates are wrong, and where do the errors come from?</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3731,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="135" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C24" s="136" t="inlineStr">
         <is>
@@ -3700,7 +3740,7 @@
       </c>
       <c r="D24" s="137" t="inlineStr">
         <is>
-          <t>A view costs nothing extra at run time. How is that possible?</t>
+          <t>The same query can often be written with a join, a subquery or a set operation. Should the choice affect performance? Why or why not?</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3749,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="135" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C25" s="136" t="inlineStr">
         <is>
@@ -3718,7 +3758,7 @@
       </c>
       <c r="D25" s="137" t="inlineStr">
         <is>
-          <t>Why do parameterized queries prevent SQL injection, while escaping user input is considered fragile?</t>
+          <t>Why does the number of possible join orders grow so quickly, and how does dynamic programming keep the search manageable?</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3767,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="135" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C26" s="136" t="inlineStr">
         <is>
@@ -3736,7 +3776,7 @@
       </c>
       <c r="D26" s="137" t="inlineStr">
         <is>
-          <t>Every normal form can be seen as removing one kind of redundancy. What single idea unifies them?</t>
+          <t>Why is serializability the accepted correctness criterion for concurrent transactions? What weaker criteria do real systems use, and why?</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3785,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="135" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C27" s="136" t="inlineStr">
         <is>
@@ -3754,7 +3794,7 @@
       </c>
       <c r="D27" s="137" t="inlineStr">
         <is>
-          <t>BCNF decomposition may lose a dependency. When would you accept 3NF instead, and what do you gain?</t>
+          <t>Why does two-phase locking guarantee serializability? Explain the idea of the lock point.</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3803,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="135" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C28" s="136" t="inlineStr">
         <is>
@@ -3772,7 +3812,7 @@
       </c>
       <c r="D28" s="137" t="inlineStr">
         <is>
-          <t>Testing whether an attribute is prime is NP-complete. What does this mean for automatic schema design tools?</t>
+          <t>Snapshot isolation prevents dirty reads, non-repeatable reads and phantoms. Why is it still not serializable?</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3821,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="135" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C29" s="136" t="inlineStr">
         <is>
@@ -3790,7 +3830,7 @@
       </c>
       <c r="D29" s="137" t="inlineStr">
         <is>
-          <t>Why is a B-tree node the size of a disk page instead of holding a single key as in a binary search tree?</t>
+          <t>Why must a log record reach stable storage before the data page it describes (write-ahead logging)?</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3839,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="135" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C30" s="136" t="inlineStr">
         <is>
@@ -3808,7 +3848,7 @@
       </c>
       <c r="D30" s="137" t="inlineStr">
         <is>
-          <t>The optimizer relies on estimates. What happens when the estimates are wrong, and where do the errors come from?</t>
+          <t>What would a DBMS lose, in performance and in safety, if it forced every modified page to disk at commit?</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3857,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="135" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C31" s="136" t="inlineStr">
         <is>
@@ -3826,63 +3866,24 @@
       </c>
       <c r="D31" s="137" t="inlineStr">
         <is>
-          <t>Could a machine-learning model replace an index? What would you need to measure to decide?</t>
+          <t>Why is recovery hard to test in a lab, and how could you still gain evidence that a recovery algorithm is correct?</t>
         </is>
       </c>
     </row>
     <row r="32" ht="13.8" customHeight="1">
-      <c r="A32" s="134" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="135" t="n">
-        <v>55</v>
-      </c>
-      <c r="C32" s="136" t="inlineStr">
-        <is>
-          <t>CQ1</t>
-        </is>
-      </c>
-      <c r="D32" s="137" t="inlineStr">
-        <is>
-          <t>Why is serializability the accepted correctness criterion for concurrent transactions? What weaker criteria do real systems use, and why?</t>
-        </is>
-      </c>
+      <c r="B32" s="96" t="n"/>
+      <c r="C32" s="96" t="n"/>
+      <c r="D32" s="97" t="n"/>
     </row>
     <row r="33" ht="13.8" customHeight="1">
-      <c r="A33" s="134" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="135" t="n">
-        <v>55</v>
-      </c>
-      <c r="C33" s="136" t="inlineStr">
-        <is>
-          <t>CQ2</t>
-        </is>
-      </c>
-      <c r="D33" s="137" t="inlineStr">
-        <is>
-          <t>Why does two-phase locking guarantee serializability? Explain the idea of the lock point.</t>
-        </is>
-      </c>
+      <c r="B33" s="96" t="n"/>
+      <c r="C33" s="96" t="n"/>
+      <c r="D33" s="97" t="n"/>
     </row>
     <row r="34" ht="13.8" customHeight="1">
-      <c r="A34" s="134" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="135" t="n">
-        <v>55</v>
-      </c>
-      <c r="C34" s="136" t="inlineStr">
-        <is>
-          <t>CQ3</t>
-        </is>
-      </c>
-      <c r="D34" s="137" t="inlineStr">
-        <is>
-          <t>Snapshot isolation prevents dirty reads, non-repeatable reads and phantoms. Why is it still not serializable?</t>
-        </is>
-      </c>
+      <c r="B34" s="96" t="n"/>
+      <c r="C34" s="96" t="n"/>
+      <c r="D34" s="97" t="n"/>
     </row>
     <row r="35" ht="13.8" customHeight="1">
       <c r="B35" s="96" t="n"/>
@@ -4447,15 +4448,16 @@
       </c>
       <c r="L1" s="41" t="n"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="42" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="32" t="inlineStr">
         <is>
-          <t>Course introduction (syllabus, assessment, research orientation)
-1.1 Basic definitions
-1.2 The file-based approach and its problems</t>
+          <t>Course introduction: syllabus, assessment, research orientation
+1.1 Database-system applications
+1.2 Purpose of database systems
+1.3 View of data</t>
         </is>
       </c>
       <c r="C2" s="32" t="inlineStr">
@@ -4475,20 +4477,20 @@
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 1
-- Textbook: [DSC] Ch. 1; [DMS] Ch. 1</t>
+          <t>- Slides: Chapter 1
+- Textbook: DSC Ch. 1, §1.1–1.3, pp. 1–12</t>
         </is>
       </c>
       <c r="G2" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 1
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 1 ([DSC] Ch. 1; [DMS] Ch. 1) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 1, §1.1–1.3, pp. 1–12 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I2" s="74" t="inlineStr">
@@ -4513,10 +4515,10 @@
       </c>
       <c r="B3" s="32" t="inlineStr">
         <is>
-          <t>1.3 Characteristics of the database approach
-1.4 Data models; schema vs. instance
-1.5 Three-schema architecture; data independence
-1.6 Database languages</t>
+          <t>1.4 Database languages
+1.5 Database design
+1.6 Database engine
+1.7 Database and application architecture</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
@@ -4536,20 +4538,21 @@
       </c>
       <c r="F3" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 1
-- Textbook: [DSC] Ch. 1; [DMS] Ch. 1</t>
+          <t>- Slides: Chapter 1
+- Textbook: DSC Ch. 1, §1.4–1.7, pp. 13–23</t>
         </is>
       </c>
       <c r="G3" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 1
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 1 ([DSC] Ch. 1; [DMS] Ch. 1) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 1, §1.4–1.7, pp. 13–23 before class; prepare the constructivist questions
+Self-study: DSC §1.8–1.9 (users and administrators; history of database systems), pp. 24–28</t>
         </is>
       </c>
       <c r="I3" s="74" t="inlineStr">
@@ -4560,15 +4563,14 @@
       <c r="J3" s="115" t="n"/>
       <c r="K3" s="115" t="n"/>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="42" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>1.7–1.10 Users, DBMS components, architectures
-Research Corner: Stonebraker &amp; Pavlo (2024)
-Lab 1: Install SQL Server, load UniversityDB</t>
+          <t>Research Corner: history of data models (Stonebraker &amp; Pavlo, 2024)
+Lab 1: install SQL Server; load the sample university database</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
@@ -4591,7 +4593,8 @@
         <is>
           <t>- Slides: Chapter 1
 - Paper: Stonebraker &amp; Pavlo (2024)
-- Lab 1 handout</t>
+- Lab 1 handout
+- Textbook: DSC Appendix A, pp. 1287–1298</t>
         </is>
       </c>
       <c r="G4" s="33" t="inlineStr">
@@ -4613,14 +4616,17 @@
       <c r="J4" s="115" t="n"/>
       <c r="K4" s="115" t="n"/>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="42" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>2.1 The database design process
-2.2 Entities and attributes (simple, composite, multivalued, derived, key)</t>
+          <t>2.1 Structure of relational databases
+2.2 Database schema
+2.3 Keys
+2.4 Schema diagrams
+The relational model as mathematics: relations as sets, keys and constraints as logic</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -4630,7 +4636,7 @@
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO2, CLO3</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr">
@@ -4640,20 +4646,20 @@
       </c>
       <c r="F5" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 2
-- Textbook: [DSC] 6.1–6.3; [DMS] 2.1–2.3</t>
+          <t>- Slides: Chapter 2
+- Textbook: DSC Ch. 2, §2.1–2.4, pp. 37–46</t>
         </is>
       </c>
       <c r="G5" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 2
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H5" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 2 ([DSC] 6.1–6.3; [DMS] 2.1–2.3) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 2, §2.1–2.4, pp. 37–46 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I5" s="74" t="inlineStr">
@@ -4670,7 +4676,8 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>2.3 Relationships: degree, cardinality ratio, participation, (min, max) notation, relationship attributes, recursive relationships</t>
+          <t>2.5 Relational query languages
+2.6 The relational algebra: select, project, union, set difference, Cartesian product, rename</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -4680,7 +4687,7 @@
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
@@ -4690,20 +4697,20 @@
       </c>
       <c r="F6" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 2
-- Textbook: [DSC] 6.2–6.4; [DMS] 2.4–2.5</t>
+          <t>- Slides: Chapter 2
+- Textbook: DSC Ch. 2, §2.5–2.6, pp. 47–57</t>
         </is>
       </c>
       <c r="G6" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 2
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 2 ([DSC] 6.2–6.4; [DMS] 2.4–2.5) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 2, §2.5–2.6, pp. 47–57 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I6" s="74" t="inlineStr">
@@ -4720,8 +4727,8 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>2.4 Weak entity types
-2.5 Design guidelines and choices (binary vs. ternary)</t>
+          <t>2.6 The relational algebra (cont.): joins, intersection, assignment, equivalent queries; division and aggregation as extended operators
+Research Corner: Codd (1970)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -4731,7 +4738,7 @@
       </c>
       <c r="D7" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr">
@@ -4741,20 +4748,21 @@
       </c>
       <c r="F7" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 2
-- Textbook: [DSC] 6.5–6.6, 6.8; [DMS] 2.4–2.5</t>
+          <t>- Slides: Chapter 2
+- Textbook: DSC Ch. 2, §2.6, pp. 48–57; Codd (1970)</t>
         </is>
       </c>
       <c r="G7" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 2
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H7" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 2 ([DSC] 6.5–6.6, 6.8; [DMS] 2.4–2.5) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 2, §2.6, pp. 48–57; Codd (1970) before class; prepare the constructivist questions
+Self-study: Relational calculus (tuple and domain) and Codd's theorem, DSC online Ch. 27 – guided reading with worksheet</t>
         </is>
       </c>
       <c r="I7" s="74" t="inlineStr">
@@ -4765,16 +4773,13 @@
       <c r="J7" s="115" t="n"/>
       <c r="K7" s="115" t="n"/>
     </row>
-    <row r="8" ht="75" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="42" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>2.6 Worked example: UniversityDB
-2.7 Crow's-foot notation
-2.8 Limits of the ER model
-Research Corner: Chen (1976)</t>
+          <t>Lab 2: relational algebra exercises; Python mini relational-algebra evaluator</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -4784,36 +4789,34 @@
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>T
-U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F8" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 2
-- Textbook: [DSC] 6.1–6.8; [DMS] Ch. 2; Chen (1976)</t>
+          <t>- Lab 2 handout
+- Python starter code (ra.py)
+- Textbook: DSC §2.6, pp. 48–57; Exercises, pp. 60–62</t>
         </is>
       </c>
       <c r="G8" s="31" t="inlineStr">
         <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 2
-- Textbooks [DSC], [DMS]</t>
+          <t>- Lab 2 handout and sample solution</t>
         </is>
       </c>
       <c r="H8" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 2 ([DSC] 6.1–6.8; [DMS] Ch. 2; Chen (1976)) before class; prepare the constructivist questions</t>
+          <t>Do Lab 2; submit before the end of the session</t>
         </is>
       </c>
       <c r="I8" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 2; lead the discussion of the constructivist questions</t>
+          <t>Guide Lab 2; review and grade submissions</t>
         </is>
       </c>
       <c r="J8" s="115" t="n"/>
@@ -4825,7 +4828,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>Lab 2 (part A): ER design – bookstore, hospital, design critique</t>
+          <t>Guided exercises: algebra and calculus proofs; review of the relational-calculus self-study worksheet</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -4835,7 +4838,7 @@
       </c>
       <c r="D9" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO3</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
@@ -4845,22 +4848,23 @@
       </c>
       <c r="F9" s="33" t="inlineStr">
         <is>
-          <t>- Lab 2 handout</t>
+          <t>- Slides: Chapter 2
+- Relational-calculus worksheet (DSC online Ch. 27)</t>
         </is>
       </c>
       <c r="G9" s="33" t="inlineStr">
         <is>
-          <t>- Lab 2 handout and sample solution</t>
+          <t>- Worksheet solutions</t>
         </is>
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 2; submit before the end of the session</t>
+          <t>Submit the self-study worksheet; solve the proof exercises</t>
         </is>
       </c>
       <c r="I9" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 2; review and grade submissions</t>
+          <t>Check the worksheet; discuss common mistakes</t>
         </is>
       </c>
       <c r="J9" s="115" t="inlineStr">
@@ -4874,14 +4878,15 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="42" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>3.1 Relational model concepts
-3.2 Keys: superkey, candidate key, primary key, foreign key</t>
+          <t>3.1 Overview of SQL
+3.2 SQL data definition
+3.3 Basic structure of SQL queries</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -4891,7 +4896,7 @@
       </c>
       <c r="D10" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
@@ -4901,20 +4906,20 @@
       </c>
       <c r="F10" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 3
-- Textbook: [DSC] 2.1–2.3; [DMS] 3.1</t>
+          <t>- Slides: Chapter 3
+- Textbook: DSC Ch. 3, §3.1–3.3, pp. 65–78</t>
         </is>
       </c>
       <c r="G10" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 3
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 3 ([DSC] 2.1–2.3; [DMS] 3.1) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.1–3.3, pp. 65–78 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I10" s="74" t="inlineStr">
@@ -4925,14 +4930,15 @@
       <c r="J10" s="115" t="n"/>
       <c r="K10" s="115" t="n"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="42" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>3.3 Integrity constraints and their violations
-3.6 The relational model as mathematics (relations as sets, constraints as logic)</t>
+          <t>3.4 Additional basic operations
+3.5 Set operations
+3.6 Null values and three-valued logic</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -4942,7 +4948,7 @@
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
@@ -4952,20 +4958,20 @@
       </c>
       <c r="F11" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 3
-- Textbook: [DSC] 2.3–2.4; [DMS] 3.2–3.3</t>
+          <t>- Slides: Chapter 3
+- Textbook: DSC Ch. 3, §3.4–3.6, pp. 79–90</t>
         </is>
       </c>
       <c r="G11" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 3
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 3 ([DSC] 2.3–2.4; [DMS] 3.2–3.3) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.4–3.6, pp. 79–90 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I11" s="74" t="inlineStr">
@@ -4986,7 +4992,8 @@
       </c>
       <c r="B12" s="32" t="inlineStr">
         <is>
-          <t>3.4 ER-to-relational mapping, steps 1–4 (strong and weak entities, 1:1, 1:N)</t>
+          <t>3.7 Aggregate functions
+3.8 Nested subqueries</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -4996,7 +5003,7 @@
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
@@ -5006,20 +5013,20 @@
       </c>
       <c r="F12" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 3
-- Textbook: [DSC] 6.7; [DMS] 3.5</t>
+          <t>- Slides: Chapter 3
+- Textbook: DSC Ch. 3, §3.7–3.8, pp. 91–107</t>
         </is>
       </c>
       <c r="G12" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 3
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H12" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 3 ([DSC] 6.7; [DMS] 3.5) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.7–3.8, pp. 91–107 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I12" s="74" t="inlineStr">
@@ -5030,14 +5037,15 @@
       <c r="J12" s="115" t="n"/>
       <c r="K12" s="115" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="42" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>3.4 Mapping steps 5–7 (M:N, multivalued, n-ary); 3.5 Worked example
-Research Corner: Codd (1970)</t>
+          <t>3.9 Modification of the database
+Semantics of SQL: bag semantics and translation to relational algebra
+Research Corner: Chamberlin &amp; Boyce (1974)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -5047,7 +5055,7 @@
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO3, CLO4</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
@@ -5057,20 +5065,20 @@
       </c>
       <c r="F13" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 3
-- Textbook: [DSC] 6.7; [DMS] 3.5; Codd (1970)</t>
+          <t>- Slides: Chapter 3
+- Textbook: DSC Ch. 3, §3.9, pp. 108–113; Chamberlin &amp; Boyce (1974)</t>
         </is>
       </c>
       <c r="G13" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 3
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H13" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 3 ([DSC] 6.7; [DMS] 3.5; Codd (1970)) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.9, pp. 108–113; Chamberlin &amp; Boyce (1974) before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I13" s="74" t="inlineStr">
@@ -5091,8 +5099,7 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>Lab 2 (part B): ER-to-relational mapping; reverse engineering UniversityDB
-Assignment 1 released</t>
+          <t>Lab 3 (part 1): single-table queries, joins, NULL behaviour</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -5102,7 +5109,7 @@
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>CLO2</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E14" s="32" t="inlineStr">
@@ -5112,38 +5119,35 @@
       </c>
       <c r="F14" s="33" t="inlineStr">
         <is>
-          <t>- Lab 2 handout
-- Assignment 1 brief</t>
+          <t>- Lab 3 handout
+- Textbook: DSC Ch. 3 Exercises, pp. 115–123</t>
         </is>
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>- Lab 2 sample solution
-- Assignment 1 brief and rubric</t>
+          <t>- Lab 3 handout and sample solution</t>
         </is>
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 2 (part B); read the Assignment 1 brief</t>
+          <t>Do Lab 3; submit before the end of the session</t>
         </is>
       </c>
       <c r="I14" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 2; present Assignment 1</t>
+          <t>Guide Lab 3; review and grade submissions</t>
         </is>
       </c>
       <c r="J14" s="115" t="n"/>
       <c r="K14" s="115" t="n"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="42" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>4.1 Relational algebra overview
-4.2 Selection, projection, rename
-4.3 Set operations and Cartesian product</t>
+          <t>Lab 3 (part 2): aggregation, subqueries, set operations; equivalent formulations of the same query</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -5153,35 +5157,33 @@
       </c>
       <c r="D15" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO3, CLO4</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F15" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 4
-- Textbook: [DSC] 2.5–2.6; [DMS] 4.1–4.2</t>
+          <t>- Lab 3 handout
+- Textbook: DSC Ch. 3 Exercises, pp. 115–123</t>
         </is>
       </c>
       <c r="G15" s="31" t="inlineStr">
         <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 4
-- Textbooks [DSC], [DMS]</t>
+          <t>- Lab 3 handout and sample solution</t>
         </is>
       </c>
       <c r="H15" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 4 ([DSC] 2.5–2.6; [DMS] 4.1–4.2) before class; prepare the constructivist questions</t>
+          <t>Do Lab 3; submit before the end of the session</t>
         </is>
       </c>
       <c r="I15" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 4; lead the discussion of the constructivist questions</t>
+          <t>Guide Lab 3; review and grade submissions</t>
         </is>
       </c>
       <c r="J15" s="115" t="n"/>
@@ -5193,7 +5195,8 @@
       </c>
       <c r="B16" s="32" t="inlineStr">
         <is>
-          <t>4.4 Joins: theta, equi, natural, outer, semi-join</t>
+          <t>4.1 Join expressions
+4.2 Views</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -5203,7 +5206,7 @@
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
@@ -5213,20 +5216,20 @@
       </c>
       <c r="F16" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 4
-- Textbook: [DSC] 2.6; [DMS] 4.2</t>
+          <t>- Slides: Chapter 4
+- Textbook: DSC Ch. 4, §4.1–4.2, pp. 125–142</t>
         </is>
       </c>
       <c r="G16" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 4
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H16" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 4 ([DSC] 2.6; [DMS] 4.2) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 4, §4.1–4.2, pp. 125–142 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I16" s="74" t="inlineStr">
@@ -5245,16 +5248,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="75" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="42" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>4.5 Division
-4.6 Aggregation
-4.7 Complete set of operators
-4.8–4.9 Translation to SQL; worked examples</t>
+          <t>4.3 Transactions (preview)
+4.4 Integrity constraints
+4.5 SQL data types and schemas</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -5264,7 +5266,7 @@
       </c>
       <c r="D17" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO2, CLO4</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
@@ -5274,20 +5276,21 @@
       </c>
       <c r="F17" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 4
-- Textbook: [DSC] 2.6; [DMS] 4.2</t>
+          <t>- Slides: Chapter 4
+- Textbook: DSC Ch. 4, §4.3–4.5, pp. 143–163</t>
         </is>
       </c>
       <c r="G17" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 4
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H17" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 4 ([DSC] 2.6; [DMS] 4.2) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 4, §4.3–4.5, pp. 143–163 before class; prepare the constructivist questions
+Self-study: DSC §4.7 Authorization, pp. 165–172</t>
         </is>
       </c>
       <c r="I17" s="74" t="inlineStr">
@@ -5298,15 +5301,14 @@
       <c r="J17" s="115" t="n"/>
       <c r="K17" s="115" t="n"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="42" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>4.10 Relational calculus (TRC, DRC), safety, Codd's theorem
-4.11 Limits of expressive power (transitive closure)
-Research Corner: Codd (1972)</t>
+          <t>4.6 Index definition in SQL
+5.4 Recursive queries: transitive closure and the limits of relational algebra</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -5316,7 +5318,7 @@
       </c>
       <c r="D18" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO3, CLO4</t>
         </is>
       </c>
       <c r="E18" s="32" t="inlineStr">
@@ -5326,20 +5328,21 @@
       </c>
       <c r="F18" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 4
-- Textbook: [DMS] 4.3–4.4; Codd (1972)</t>
+          <t>- Slides: Chapter 4
+- Textbook: DSC §4.6, p. 164; §5.4, pp. 213–218</t>
         </is>
       </c>
       <c r="G18" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 4
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H18" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 4 ([DMS] 4.3–4.4; Codd (1972)) before class; prepare the constructivist questions</t>
+          <t>Read DSC §4.6, p. 164; §5.4, pp. 213–218 before class; prepare the constructivist questions
+Self-study: DSC §5.5 Advanced aggregation features (ranking, windowing), pp. 219–230</t>
         </is>
       </c>
       <c r="I18" s="74" t="inlineStr">
@@ -5356,7 +5359,8 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>Lab 3: Relational algebra and calculus; Python mini relational-algebra evaluator</t>
+          <t>5.1 Accessing SQL from a programming language (Python)
+SQL injection and parameterized queries</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -5366,33 +5370,36 @@
       </c>
       <c r="D19" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F19" s="33" t="inlineStr">
         <is>
-          <t>- Lab 3 handout
-- Python starter code labs/python (ra.py)</t>
+          <t>- Slides: Chapter 4
+- Textbook: DSC §5.1, pp. 183–197</t>
         </is>
       </c>
       <c r="G19" s="31" t="inlineStr">
         <is>
-          <t>- Lab 3 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 4
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H19" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 3; submit before the end of the session</t>
+          <t>Read DSC §5.1, pp. 183–197 before class; prepare the constructivist questions
+Self-study: DSC §9.8 Application security, pp. 437–446; optional: §5.2–5.3 functions, procedures, triggers, pp. 198–212</t>
         </is>
       </c>
       <c r="I19" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 3; review and grade submissions</t>
+          <t>Teach Chapter 4; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J19" s="115" t="n"/>
@@ -5404,192 +5411,191 @@
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
+          <t>Lab 4: DDL, integrity constraints, views, and SQL from Python</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>CLO2, CLO4</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>- Lab 4 handout
+- Textbook: DSC Ch. 4 Exercises, pp. 176–179; §5.1</t>
+        </is>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>- Lab 4 handout and sample solution</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr">
+        <is>
+          <t>Do Lab 4; submit before the end of the session</t>
+        </is>
+      </c>
+      <c r="I20" s="74" t="inlineStr">
+        <is>
+          <t>Guide Lab 4; review and grade submissions</t>
+        </is>
+      </c>
+      <c r="J20" s="115" t="n"/>
+      <c r="K20" s="115" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="42" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
           <t>Progress test 1 (Chapters 1–4)
 Review exercises</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
-        <is>
-          <t>CLO1, CLO2, CLO3</t>
-        </is>
-      </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>CLO1, CLO2, CLO3, CLO4</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
-        <is>
-          <t>- Slides: Chapters 1–4</t>
-        </is>
-      </c>
-      <c r="G20" s="33" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapters 1–4
+- DSC Ch. 1–4</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
         <is>
           <t>- Progress test 1</t>
         </is>
       </c>
-      <c r="H20" s="31" t="inlineStr">
+      <c r="H21" s="31" t="inlineStr">
         <is>
           <t>Review Chapters 1–4; take Progress test 1</t>
         </is>
       </c>
-      <c r="I20" s="74" t="inlineStr">
+      <c r="I21" s="74" t="inlineStr">
         <is>
           <t>Run and grade Progress test 1; review the answers</t>
         </is>
       </c>
-      <c r="J20" s="115" t="n"/>
-      <c r="K20" s="115" t="n"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="42" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>5.1 SQL overview
-5.2 Databases and schemas
-5.3 SQL Server data types</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="J21" s="115" t="n"/>
+      <c r="K21" s="115" t="n"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="42" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>6.1 Overview of the design process
+6.2 The Entity-Relationship model
+6.3 Complex attributes</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
-        <is>
-          <t>CLO4</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>CLO2</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F21" s="33" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 5
-- Textbook: [DSC] 3.1–3.2; [DMS] 5.1</t>
-        </is>
-      </c>
-      <c r="G21" s="31" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 5
+- Textbook: DSC Ch. 6, §6.1–6.3, pp. 241–251</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 5
-- Textbooks [DSC], [DMS]</t>
-        </is>
-      </c>
-      <c r="H21" s="31" t="inlineStr">
-        <is>
-          <t>Read Chapter 5 ([DSC] 3.1–3.2; [DMS] 5.1) before class; prepare the constructivist questions</t>
-        </is>
-      </c>
-      <c r="I21" s="74" t="inlineStr">
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 6, §6.1–6.3, pp. 241–251 before class; prepare the constructivist questions</t>
+        </is>
+      </c>
+      <c r="I22" s="74" t="inlineStr">
         <is>
           <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
         </is>
       </c>
-      <c r="J21" s="115" t="n"/>
-      <c r="K21" s="115" t="n"/>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="42" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>5.4 CREATE TABLE
-5.5 Constraints and referential actions; IDENTITY</t>
-        </is>
-      </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="J22" s="115" t="n"/>
+      <c r="K22" s="115" t="n"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>6.4 Mapping cardinalities
+6.5 Primary key
+6.6 Removing redundant attributes in entity sets</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
-        <is>
-          <t>CLO4</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>CLO2</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 5
-- Textbook: [DSC] 4.4–4.5; [DMS] 3.2–3.3</t>
-        </is>
-      </c>
-      <c r="G22" s="33" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 5
+- Textbook: DSC Ch. 6, §6.4–6.6, pp. 252–263</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 5
-- Textbooks [DSC], [DMS]</t>
-        </is>
-      </c>
-      <c r="H22" s="31" t="inlineStr">
-        <is>
-          <t>Read Chapter 5 ([DSC] 4.4–4.5; [DMS] 3.2–3.3) before class; prepare the constructivist questions</t>
-        </is>
-      </c>
-      <c r="I22" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
-        </is>
-      </c>
-      <c r="J22" s="115" t="n"/>
-      <c r="K22" s="115" t="n"/>
-    </row>
-    <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="42" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>5.6–5.9 ALTER/DROP, creation order, catalog, DCL
-5.10 Assertions and the cost of integrity checking</t>
-        </is>
-      </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
-        <is>
-          <t>CLO4</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F23" s="33" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 5
-- Textbook: [DSC] 4.4–4.7; [DMS] 3.3, 5.7</t>
-        </is>
-      </c>
-      <c r="G23" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 5
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H23" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 5 ([DSC] 4.4–4.7; [DMS] 3.3, 5.7) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 6, §6.4–6.6, pp. 252–263 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I23" s="74" t="inlineStr">
@@ -5606,7 +5612,7 @@
       </c>
       <c r="B24" s="32" t="inlineStr">
         <is>
-          <t>Lab 4 (part 1): LibraryDB – tables and constraints</t>
+          <t>6.7 Reducing E-R diagrams to relational schemas</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -5616,32 +5622,36 @@
       </c>
       <c r="D24" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO4</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F24" s="33" t="inlineStr">
         <is>
-          <t>- Lab 4 handout</t>
+          <t>- Slides: Chapter 5
+- Textbook: DSC Ch. 6, §6.7, pp. 264–270</t>
         </is>
       </c>
       <c r="G24" s="33" t="inlineStr">
         <is>
-          <t>- Lab 4 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 5
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H24" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 4; submit before the end of the session</t>
+          <t>Read DSC Ch. 6, §6.7, pp. 264–270 before class; prepare the constructivist questions
+Self-study: DSC §6.8 Extended E-R features, pp. 271–278</t>
         </is>
       </c>
       <c r="I24" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 4; review and grade submissions</t>
+          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J24" s="115" t="n"/>
@@ -5653,8 +5663,8 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>Lab 4 (part 2): testing constraints, ALTER TABLE, reflection
-Assignment 1 consultation</t>
+          <t>6.9 Entity-relationship design issues; limits of the E-R model
+Research Corner: Chen (1976)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -5664,32 +5674,36 @@
       </c>
       <c r="D25" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO4</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F25" s="33" t="inlineStr">
         <is>
-          <t>- Lab 4 handout</t>
+          <t>- Slides: Chapter 5
+- Textbook: DSC Ch. 6, §6.9, pp. 279–284; Chen (1976)</t>
         </is>
       </c>
       <c r="G25" s="31" t="inlineStr">
         <is>
-          <t>- Lab 4 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 5
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H25" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 4; submit before the end of the session</t>
+          <t>Read DSC Ch. 6, §6.9, pp. 279–284; Chen (1976) before class; prepare the constructivist questions
+Self-study: DSC §6.10–6.11 Alternative notations (crow's foot, UML) and other aspects of design, pp. 285–291</t>
         </is>
       </c>
       <c r="I25" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 4; review and grade submissions</t>
+          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J25" s="115" t="n"/>
@@ -5701,8 +5715,8 @@
       </c>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t>6.1 The SELECT statement and logical processing order
-6.2 Single-table queries, predicates, built-in functions</t>
+          <t>Lab 5: E-R design and reduction to relational schemas
+Assignment 1 released</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -5712,35 +5726,35 @@
       </c>
       <c r="D26" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO2</t>
         </is>
       </c>
       <c r="E26" s="32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F26" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 6
-- Textbook: [DSC] 3.3–3.4; [DMS] 5.2</t>
+          <t>- Lab 5 handout
+- Assignment 1 brief
+- Textbook: DSC Ch. 6 Exercises, pp. 294–299</t>
         </is>
       </c>
       <c r="G26" s="33" t="inlineStr">
         <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 6
-- Textbooks [DSC], [DMS]</t>
+          <t>- Lab 5 sample solution
+- Assignment 1 brief and rubric</t>
         </is>
       </c>
       <c r="H26" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 6 ([DSC] 3.3–3.4; [DMS] 5.2) before class; prepare the constructivist questions</t>
+          <t>Do Lab 5; read the Assignment 1 brief</t>
         </is>
       </c>
       <c r="I26" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
+          <t>Guide Lab 5; present Assignment 1</t>
         </is>
       </c>
       <c r="J26" s="115" t="n"/>
@@ -5752,8 +5766,8 @@
       </c>
       <c r="B27" s="32" t="inlineStr">
         <is>
-          <t>6.3 NULL and three-valued logic
-6.9 Semantics of SQL: translation to algebra, bag semantics</t>
+          <t>7.1 Features of good relational designs: redundancy and anomalies
+7.2 Decomposition using functional dependencies</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -5763,7 +5777,7 @@
       </c>
       <c r="D27" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
@@ -5773,20 +5787,20 @@
       </c>
       <c r="F27" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 6
-- Textbook: [DSC] 3.6; [DMS] 5.6</t>
+          <t>- Slides: Chapter 6
+- Textbook: DSC Ch. 7, §7.1–7.2, pp. 303–312</t>
         </is>
       </c>
       <c r="G27" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 6
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H27" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 6 ([DSC] 3.6; [DMS] 5.6) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.1–7.2, pp. 303–312 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I27" s="74" t="inlineStr">
@@ -5803,7 +5817,7 @@
       </c>
       <c r="B28" s="32" t="inlineStr">
         <is>
-          <t>6.4 Joins: inner, outer, self, anti-join</t>
+          <t>7.3 Normal forms: BCNF and 3NF</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -5813,7 +5827,7 @@
       </c>
       <c r="D28" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E28" s="32" t="inlineStr">
@@ -5823,20 +5837,20 @@
       </c>
       <c r="F28" s="33" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 6
-- Textbook: [DSC] 4.1; [DMS] 5.6</t>
+          <t>- Slides: Chapter 6
+- Textbook: DSC Ch. 7, §7.3, pp. 313–319</t>
         </is>
       </c>
       <c r="G28" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 6
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H28" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 6 ([DSC] 4.1; [DMS] 5.6) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.3, pp. 313–319 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I28" s="74" t="inlineStr">
@@ -5853,7 +5867,7 @@
       </c>
       <c r="B29" s="32" t="inlineStr">
         <is>
-          <t>Lab 5 (part A): single-table queries and joins</t>
+          <t>7.4 Functional-dependency theory: closure of a set of FDs, Armstrong's axioms, attribute closure</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -5863,32 +5877,35 @@
       </c>
       <c r="D29" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F29" s="31" t="inlineStr">
         <is>
-          <t>- Lab 5 handout</t>
+          <t>- Slides: Chapter 6
+- Textbook: DSC Ch. 7, §7.4, pp. 320–329</t>
         </is>
       </c>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>- Lab 5 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 6
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H29" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 5; submit before the end of the session</t>
+          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I29" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 5; review and grade submissions</t>
+          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J29" s="115" t="n"/>
@@ -5900,7 +5917,7 @@
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>6.5 Aggregation: GROUP BY, HAVING</t>
+          <t>7.4 Functional-dependency theory (cont.): canonical cover, lossless decomposition, dependency preservation; proofs of soundness</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -5910,7 +5927,7 @@
       </c>
       <c r="D30" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E30" s="32" t="inlineStr">
@@ -5920,20 +5937,20 @@
       </c>
       <c r="F30" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 6
-- Textbook: [DSC] 3.7; [DMS] 5.5</t>
+          <t>- Slides: Chapter 6
+- Textbook: DSC Ch. 7, §7.4, pp. 320–329</t>
         </is>
       </c>
       <c r="G30" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 6
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 6 ([DSC] 3.7; [DMS] 5.5) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I30" s="74" t="inlineStr">
@@ -5950,7 +5967,7 @@
       </c>
       <c r="B31" s="32" t="inlineStr">
         <is>
-          <t>6.6 Subqueries: scalar, IN/ANY/ALL, correlated, EXISTS, division in SQL</t>
+          <t>7.5 Algorithms for decomposition: BCNF decomposition and 3NF synthesis</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -5960,7 +5977,7 @@
       </c>
       <c r="D31" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
@@ -5970,20 +5987,20 @@
       </c>
       <c r="F31" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 6
-- Textbook: [DSC] 3.8; [DMS] 5.4</t>
+          <t>- Slides: Chapter 6
+- Textbook: DSC Ch. 7, §7.5, pp. 330–335</t>
         </is>
       </c>
       <c r="G31" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 6
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H31" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 6 ([DSC] 3.8; [DMS] 5.4) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.5, pp. 330–335 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I31" s="74" t="inlineStr">
@@ -5994,14 +6011,15 @@
       <c r="J31" s="115" t="n"/>
       <c r="K31" s="115" t="n"/>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="42" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>6.6–6.8 CTEs, set operations, window functions
-Research Corner: Chamberlin &amp; Boyce (1974); Guagliardo &amp; Libkin (2017)</t>
+          <t>7.6 Decomposition using multivalued dependencies (4NF, overview)
+7.8 Atomic domains and first normal form
+Research Corner: Kent (1983)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -6011,7 +6029,7 @@
       </c>
       <c r="D32" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E32" s="32" t="inlineStr">
@@ -6021,20 +6039,21 @@
       </c>
       <c r="F32" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 6
-- Textbook: [DSC] 3.5, 3.8, 5.5; [DMS] 5.3</t>
+          <t>- Slides: Chapter 6
+- Textbook: DSC Ch. 7, §7.6, §7.8, pp. 336–340, 342</t>
         </is>
       </c>
       <c r="G32" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 6
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 6 ([DSC] 3.5, 3.8, 5.5; [DMS] 5.3) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.6, §7.8, pp. 336–340, 342 before class; prepare the constructivist questions
+Self-study: DSC §7.7 More normal forms, p. 341; §7.9 Database-design process, pp. 343–346</t>
         </is>
       </c>
       <c r="I32" s="74" t="inlineStr">
@@ -6051,7 +6070,7 @@
       </c>
       <c r="B33" s="32" t="inlineStr">
         <is>
-          <t>Lab 5 (part B): aggregation, subqueries, set operations</t>
+          <t>Lab 6: FD theory on paper; Python FD toolkit (closure, keys, canonical cover, BCNF, lossless-join test)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -6061,7 +6080,7 @@
       </c>
       <c r="D33" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
@@ -6071,22 +6090,24 @@
       </c>
       <c r="F33" s="31" t="inlineStr">
         <is>
-          <t>- Lab 5 handout</t>
+          <t>- Lab 6 handout
+- Python starter code (fd.py)
+- Textbook: DSC Ch. 7 Exercises, pp. 353–359</t>
         </is>
       </c>
       <c r="G33" s="31" t="inlineStr">
         <is>
-          <t>- Lab 5 handout and sample solution</t>
+          <t>- Lab 6 handout and sample solution</t>
         </is>
       </c>
       <c r="H33" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 5; submit before the end of the session</t>
+          <t>Do Lab 6; submit before the end of the session</t>
         </is>
       </c>
       <c r="I33" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 5; review and grade submissions</t>
+          <t>Guide Lab 6; review and grade submissions</t>
         </is>
       </c>
       <c r="J33" s="115" t="n"/>
@@ -6098,7 +6119,7 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Lab 5 (part B, challenge): recursive CTE and expressive power</t>
+          <t>Assignment 1: submission and oral defense</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -6108,7 +6129,7 @@
       </c>
       <c r="D34" s="32" t="inlineStr">
         <is>
-          <t>CLO3, CLO4</t>
+          <t>CLO2, CLO3, CLO8</t>
         </is>
       </c>
       <c r="E34" s="32" t="inlineStr">
@@ -6118,22 +6139,22 @@
       </c>
       <c r="F34" s="31" t="inlineStr">
         <is>
-          <t>- Lab 5 handout</t>
+          <t>- Assignment 1 brief and rubric</t>
         </is>
       </c>
       <c r="G34" s="31" t="inlineStr">
         <is>
-          <t>- Lab 5 handout and sample solution</t>
+          <t>- Assignment 1 rubric</t>
         </is>
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 5; submit before the end of the session</t>
+          <t>Submit the report; defend it orally (5 minutes)</t>
         </is>
       </c>
       <c r="I34" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 5; review and grade submissions</t>
+          <t>Assess reports and oral defenses</t>
         </is>
       </c>
       <c r="J34" s="115" t="n"/>
@@ -6145,7 +6166,8 @@
       </c>
       <c r="B35" s="32" t="inlineStr">
         <is>
-          <t>7.1–7.5 INSERT, UPDATE, DELETE, TRUNCATE, MERGE, OUTPUT</t>
+          <t>Progress test 2 (Chapters 5–6)
+Review exercises</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -6155,131 +6177,134 @@
       </c>
       <c r="D35" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO2, CLO5</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapters 5–6
+- DSC Ch. 6–7</t>
+        </is>
+      </c>
+      <c r="G35" s="31" t="inlineStr">
+        <is>
+          <t>- Progress test 2</t>
+        </is>
+      </c>
+      <c r="H35" s="31" t="inlineStr">
+        <is>
+          <t>Review Chapters 5–6; take Progress test 2</t>
+        </is>
+      </c>
+      <c r="I35" s="74" t="inlineStr">
+        <is>
+          <t>Run and grade Progress test 2; review the answers</t>
+        </is>
+      </c>
+      <c r="J35" s="115" t="n"/>
+      <c r="K35" s="115" t="n"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>13.1 Database storage architecture
+13.2 File organization
+13.3 Organization of records in files</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>CLO6</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 7
-- Textbook: [DSC] 3.9; [DMS] 3.6</t>
-        </is>
-      </c>
-      <c r="G35" s="31" t="inlineStr">
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 13, §13.1–13.3, pp. 587–601</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 7
-- Textbooks [DSC], [DMS]</t>
-        </is>
-      </c>
-      <c r="H35" s="31" t="inlineStr">
-        <is>
-          <t>Read Chapter 7 ([DSC] 3.9; [DMS] 3.6) before class; prepare the constructivist questions</t>
-        </is>
-      </c>
-      <c r="I35" s="74" t="inlineStr">
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H36" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 13, §13.1–13.3, pp. 587–601 before class; prepare the constructivist questions
+Self-study: DSC §12.1 Physical storage media, pp. 559–561; §12.6 Disk-block access, pp. 577–579</t>
+        </is>
+      </c>
+      <c r="I36" s="74" t="inlineStr">
         <is>
           <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
         </is>
       </c>
-      <c r="J35" s="115" t="n"/>
-      <c r="K35" s="115" t="n"/>
-    </row>
-    <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="42" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="32" t="inlineStr">
-        <is>
-          <t>7.6 Views: definition, updatability, WITH CHECK OPTION
-7.9 View expansion and the view-update problem</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="J36" s="115" t="n"/>
+      <c r="K36" s="115" t="n"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="42" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>13.5 Database buffer
+14.1 Indexing: basic concepts
+14.2 Ordered indices</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D36" s="32" t="inlineStr">
-        <is>
-          <t>CLO4</t>
-        </is>
-      </c>
-      <c r="E36" s="32" t="inlineStr">
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>CLO6</t>
+        </is>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F36" s="31" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 7
-- Textbook: [DSC] 4.2; [DMS] 3.6; Bancilhon &amp; Spyratos (1981)</t>
-        </is>
-      </c>
-      <c r="G36" s="31" t="inlineStr">
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
+- Textbook: DSC §13.5, pp. 604–610; Ch. 14, §14.1–14.2, pp. 623–633</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 7
-- Textbooks [DSC], [DMS]</t>
-        </is>
-      </c>
-      <c r="H36" s="31" t="inlineStr">
-        <is>
-          <t>Read Chapter 7 ([DSC] 4.2; [DMS] 3.6; Bancilhon &amp; Spyratos (1981)) before class; prepare the constructivist questions</t>
-        </is>
-      </c>
-      <c r="I36" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
-        </is>
-      </c>
-      <c r="J36" s="115" t="n"/>
-      <c r="K36" s="115" t="n"/>
-    </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="42" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="32" t="inlineStr">
-        <is>
-          <t>7.7 Using the database from Python (pyodbc, pandas); SQL injection</t>
-        </is>
-      </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="inlineStr">
-        <is>
-          <t>CLO4</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 7
-- Textbook: [DSC] 5.1; [DMS] 6.1–6.2</t>
-        </is>
-      </c>
-      <c r="G37" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 7
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H37" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 7 ([DSC] 5.1; [DMS] 6.1–6.2) before class; prepare the constructivist questions</t>
+          <t>Read DSC §13.5, pp. 604–610; Ch. 14, §14.1–14.2, pp. 623–633 before class; prepare the constructivist questions
+Self-study: DSC §13.4 Data-dictionary storage, pp. 602–603</t>
         </is>
       </c>
       <c r="I37" s="74" t="inlineStr">
@@ -6296,7 +6321,7 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Lab 6: data modification, views, and SQL from Python</t>
+          <t>14.3 B+-tree index files: structure, search, insertion, deletion; height analysis</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -6306,44 +6331,51 @@
       </c>
       <c r="D38" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E38" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F38" s="31" t="inlineStr">
         <is>
-          <t>- Lab 6 handout</t>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 14, §14.3, pp. 634–649</t>
         </is>
       </c>
       <c r="G38" s="31" t="inlineStr">
         <is>
-          <t>- Lab 6 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 7
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 6; submit before the end of the session</t>
+          <t>Read DSC Ch. 14, §14.3, pp. 634–649 before class; prepare the constructivist questions
+Self-study: DSC §14.4 B+-tree extensions, pp. 650–657</t>
         </is>
       </c>
       <c r="I38" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 6; review and grade submissions</t>
+          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J38" s="115" t="n"/>
       <c r="K38" s="115" t="n"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="42" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="32" t="inlineStr">
         <is>
-          <t>Assignment 1: submission and oral defense</t>
+          <t>14.5 Hash indices
+14.6 Multiple-key access
+14.7 Creation of indices
+Research Corner: Bayer &amp; McCreight (1972); Kraska et al. (2018)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -6353,32 +6385,36 @@
       </c>
       <c r="D39" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO3, CLO8</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F39" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 1 brief and rubric</t>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 14, §14.5–14.7, pp. 658–664</t>
         </is>
       </c>
       <c r="G39" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 1 rubric</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 7
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H39" s="31" t="inlineStr">
         <is>
-          <t>Submit the report; defend it orally (5 minutes)</t>
+          <t>Read DSC Ch. 14, §14.5–14.7, pp. 658–664 before class; prepare the constructivist questions
+Self-study: Optional: §13.6 Column-oriented storage, pp. 611–614; §14.8 Write-optimized index structures (LSM), pp. 665–669</t>
         </is>
       </c>
       <c r="I39" s="74" t="inlineStr">
         <is>
-          <t>Assess reports and oral defenses</t>
+          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J39" s="115" t="n"/>
@@ -6390,8 +6426,7 @@
       </c>
       <c r="B40" s="32" t="inlineStr">
         <is>
-          <t>8.1 Anomalies
-8.2 Functional dependencies; Armstrong's axioms</t>
+          <t>Guided exercises: B+-tree insertion and deletion by hand; hashing; I/O cost of index lookups versus table scans</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -6401,35 +6436,33 @@
       </c>
       <c r="D40" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F40" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 8
-- Textbook: [DSC] 7.1–7.2; [DMS] 19.1–19.3</t>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 14 Exercises, pp. 679–682</t>
         </is>
       </c>
       <c r="G40" s="31" t="inlineStr">
         <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 8
-- Textbooks [DSC], [DMS]</t>
+          <t>- Exercise solutions</t>
         </is>
       </c>
       <c r="H40" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 8 ([DSC] 7.1–7.2; [DMS] 19.1–19.3) before class; prepare the constructivist questions</t>
+          <t>Solve the exercises; compare hand-computed costs with the formulas</t>
         </is>
       </c>
       <c r="I40" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
+          <t>Guide the exercises; discuss solutions</t>
         </is>
       </c>
       <c r="J40" s="115" t="n"/>
@@ -6441,7 +6474,7 @@
       </c>
       <c r="B41" s="32" t="inlineStr">
         <is>
-          <t>8.3 Attribute closure; finding candidate keys</t>
+          <t>Lab 7: indexing experiments on a large table; execution plans and logical reads (Investigate)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -6451,81 +6484,80 @@
       </c>
       <c r="D41" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO6, CLO8</t>
         </is>
       </c>
       <c r="E41" s="32" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 7 handout
+- Textbook: DSC Ch. 14 Exercises, pp. 679–682</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 7 handout and sample solution</t>
+        </is>
+      </c>
+      <c r="H41" s="31" t="inlineStr">
+        <is>
+          <t>Do Lab 7; submit before the end of the session</t>
+        </is>
+      </c>
+      <c r="I41" s="74" t="inlineStr">
+        <is>
+          <t>Guide Lab 7; review and grade submissions</t>
+        </is>
+      </c>
+      <c r="J41" s="115" t="n"/>
+      <c r="K41" s="115" t="n"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>15.1 Overview of query processing
+15.2 Measures of query cost
+15.3 Selection operation</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
+        <is>
+          <t>CLO6</t>
+        </is>
+      </c>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F41" s="31" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 8
-- Textbook: [DSC] 7.4; [DMS] 19.3</t>
-        </is>
-      </c>
-      <c r="G41" s="31" t="inlineStr">
+      <c r="F42" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 8
+- Textbook: DSC Ch. 15, §15.1–15.3, pp. 689–700</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 8
-- Textbooks [DSC], [DMS]</t>
-        </is>
-      </c>
-      <c r="H41" s="31" t="inlineStr">
-        <is>
-          <t>Read Chapter 8 ([DSC] 7.4; [DMS] 19.3) before class; prepare the constructivist questions</t>
-        </is>
-      </c>
-      <c r="I41" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
-        </is>
-      </c>
-      <c r="J41" s="115" t="n"/>
-      <c r="K41" s="115" t="n"/>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="32" t="inlineStr">
-        <is>
-          <t>8.4 Minimal cover
-8.10 Proofs: soundness, correctness of the closure algorithm</t>
-        </is>
-      </c>
-      <c r="C42" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="inlineStr">
-        <is>
-          <t>CLO5</t>
-        </is>
-      </c>
-      <c r="E42" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F42" s="31" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 8
-- Textbook: [DSC] 7.4; [DMS] 19.3</t>
-        </is>
-      </c>
-      <c r="G42" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 8
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H42" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 8 ([DSC] 7.4; [DMS] 19.3) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 15, §15.1–15.3, pp. 689–700 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I42" s="74" t="inlineStr">
@@ -6542,7 +6574,8 @@
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>8.5 Normal forms: 1NF, 2NF, 3NF, BCNF</t>
+          <t>15.4 Sorting (external merge sort)
+15.5 Join operation: nested-loop and block nested-loop joins</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -6552,7 +6585,7 @@
       </c>
       <c r="D43" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E43" s="32" t="inlineStr">
@@ -6562,20 +6595,20 @@
       </c>
       <c r="F43" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 8
-- Textbook: [DSC] 7.3; [DMS] 19.4</t>
+          <t>- Slides: Chapter 8
+- Textbook: DSC Ch. 15, §15.4, pp. 701–703; §15.5, pp. 704–718</t>
         </is>
       </c>
       <c r="G43" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 8
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H43" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 8 ([DSC] 7.3; [DMS] 19.4) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 15, §15.4, pp. 701–703; §15.5, pp. 704–718 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I43" s="74" t="inlineStr">
@@ -6592,7 +6625,7 @@
       </c>
       <c r="B44" s="32" t="inlineStr">
         <is>
-          <t>8.6–8.8 Lossless join and dependency preservation; 3NF synthesis and BCNF decomposition; worked example</t>
+          <t>15.5 Join operation (cont.): indexed nested-loop, merge join, hash join; cost comparison</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -6602,7 +6635,7 @@
       </c>
       <c r="D44" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E44" s="32" t="inlineStr">
@@ -6612,20 +6645,21 @@
       </c>
       <c r="F44" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 8
-- Textbook: [DSC] 7.5; [DMS] 19.5–19.6</t>
+          <t>- Slides: Chapter 8
+- Textbook: DSC Ch. 15, §15.5, pp. 704–718</t>
         </is>
       </c>
       <c r="G44" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 8
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 8 ([DSC] 7.5; [DMS] 19.5–19.6) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 15, §15.5, pp. 704–718 before class; prepare the constructivist questions
+Self-study: DSC §15.6 Other operations, pp. 719–723; §15.7 Evaluation of expressions (pipelining), pp. 724–730</t>
         </is>
       </c>
       <c r="I44" s="74" t="inlineStr">
@@ -6636,15 +6670,14 @@
       <c r="J44" s="115" t="n"/>
       <c r="K44" s="115" t="n"/>
     </row>
-    <row r="45" ht="60" customHeight="1">
+    <row r="45" ht="45" customHeight="1">
       <c r="A45" s="42" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="32" t="inlineStr">
         <is>
-          <t>8.11 Computational complexity of normalization
-8.12 MVDs and 4NF
-Research Corner: Kent (1983); Armstrong (1974)</t>
+          <t>16.1 Overview of query optimization
+16.2 Transformation of relational expressions: equivalence rules</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -6654,7 +6687,7 @@
       </c>
       <c r="D45" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E45" s="32" t="inlineStr">
@@ -6664,20 +6697,20 @@
       </c>
       <c r="F45" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 8
-- Textbook: [DSC] 7.6; [DMS] 19.8; Kent (1983)</t>
+          <t>- Slides: Chapter 8
+- Textbook: DSC Ch. 16, §16.1–16.2, pp. 743–756</t>
         </is>
       </c>
       <c r="G45" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 8
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H45" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 8 ([DSC] 7.6; [DMS] 19.8; Kent (1983)) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 16, §16.1–16.2, pp. 743–756 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I45" s="74" t="inlineStr">
@@ -6694,7 +6727,8 @@
       </c>
       <c r="B46" s="32" t="inlineStr">
         <is>
-          <t>Lab 7: FD theory on paper; Python FD toolkit (closure, keys, minimal cover, BCNF, chase)</t>
+          <t>16.4 Choice of evaluation plans: cost-based join ordering (dynamic programming)
+Research Corner: Selinger et al. (1979)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -6704,33 +6738,36 @@
       </c>
       <c r="D46" s="32" t="inlineStr">
         <is>
-          <t>CLO5</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F46" s="31" t="inlineStr">
         <is>
-          <t>- Lab 7 handout
-- Python starter code labs/python (fd.py)</t>
+          <t>- Slides: Chapter 8
+- Textbook: DSC Ch. 16, §16.4, pp. 766–777</t>
         </is>
       </c>
       <c r="G46" s="31" t="inlineStr">
         <is>
-          <t>- Lab 7 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 8
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 7; submit before the end of the session</t>
+          <t>Read DSC Ch. 16, §16.4, pp. 766–777 before class; prepare the constructivist questions
+Self-study: DSC §16.3 Estimating statistics of expression results, pp. 757–765</t>
         </is>
       </c>
       <c r="I46" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 7; review and grade submissions</t>
+          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J46" s="115" t="n"/>
@@ -6742,8 +6779,8 @@
       </c>
       <c r="B47" s="32" t="inlineStr">
         <is>
-          <t>Progress test 2 (Chapters 5–8)
-Review exercises</t>
+          <t>Lab 8: reading execution plans; comparing join algorithms and equivalent queries (Investigate)
+Assignment 2 released (research topics)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -6753,7 +6790,7 @@
       </c>
       <c r="D47" s="32" t="inlineStr">
         <is>
-          <t>CLO4, CLO5</t>
+          <t>CLO6, CLO8</t>
         </is>
       </c>
       <c r="E47" s="32" t="inlineStr">
@@ -6763,35 +6800,39 @@
       </c>
       <c r="F47" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapters 5–8</t>
+          <t>- Lab 8 handout
+- Assignment 2 brief
+- Textbook: DSC Ch. 15–16 Exercises, pp. 736–739, 789–793</t>
         </is>
       </c>
       <c r="G47" s="31" t="inlineStr">
         <is>
-          <t>- Progress test 2</t>
+          <t>- Lab 8 handout and sample solution</t>
         </is>
       </c>
       <c r="H47" s="31" t="inlineStr">
         <is>
-          <t>Review Chapters 5–8; take Progress test 2</t>
+          <t>Do Lab 8; submit before the end of the session</t>
         </is>
       </c>
       <c r="I47" s="74" t="inlineStr">
         <is>
-          <t>Run and grade Progress test 2; review the answers</t>
+          <t>Guide Lab 8; review and grade submissions</t>
         </is>
       </c>
       <c r="J47" s="115" t="n"/>
       <c r="K47" s="115" t="n"/>
     </row>
-    <row r="48" ht="45" customHeight="1">
+    <row r="48" ht="75" customHeight="1">
       <c r="A48" s="42" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="32" t="inlineStr">
         <is>
-          <t>9.1 Why storage matters
-9.2 Pages, records, file organizations, the buffer pool</t>
+          <t>17.1 Transaction concept
+17.2 A simple transaction model
+17.3 Storage structure
+17.4 Transaction atomicity and durability</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -6801,7 +6842,7 @@
       </c>
       <c r="D48" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E48" s="32" t="inlineStr">
@@ -6811,20 +6852,20 @@
       </c>
       <c r="F48" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 9
-- Textbook: [DSC] 13.1–13.3; [DMS] 8.1–8.2, 9.1–9.4</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 17, §17.1–17.4, pp. 799–806</t>
         </is>
       </c>
       <c r="G48" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 9
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H48" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 9 ([DSC] 13.1–13.3; [DMS] 8.1–8.2, 9.1–9.4) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 17, §17.1–17.4, pp. 799–806 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I48" s="74" t="inlineStr">
@@ -6841,7 +6882,8 @@
       </c>
       <c r="B49" s="32" t="inlineStr">
         <is>
-          <t>9.3 Indexes: B+-trees, hash indexes, clustered vs. non-clustered, choosing indexes</t>
+          <t>17.5 Transaction isolation
+17.6 Serializability: conflict serializability and precedence graphs</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -6851,7 +6893,7 @@
       </c>
       <c r="D49" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E49" s="32" t="inlineStr">
@@ -6861,20 +6903,20 @@
       </c>
       <c r="F49" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 9
-- Textbook: [DSC] 14.1–14.5; [DMS] 8.3–8.5, 10.1–10.3</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 17, §17.5–17.6, pp. 807–818</t>
         </is>
       </c>
       <c r="G49" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 9
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H49" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 9 ([DSC] 14.1–14.5; [DMS] 8.3–8.5, 10.1–10.3) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 17, §17.5–17.6, pp. 807–818 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I49" s="74" t="inlineStr">
@@ -6885,14 +6927,16 @@
       <c r="J49" s="115" t="n"/>
       <c r="K49" s="115" t="n"/>
     </row>
-    <row r="50" ht="45" customHeight="1">
+    <row r="50" ht="75" customHeight="1">
       <c r="A50" s="42" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="32" t="inlineStr">
         <is>
-          <t>9.4 Query processing; selection and join algorithms
-9.6 Cost formulas</t>
+          <t>17.7 Transaction isolation and atomicity: recoverable and cascadeless schedules
+17.8 Transaction isolation levels
+17.9 Implementation of isolation levels
+17.10 Transactions as SQL statements</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -6902,7 +6946,7 @@
       </c>
       <c r="D50" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E50" s="32" t="inlineStr">
@@ -6912,20 +6956,20 @@
       </c>
       <c r="F50" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 9
-- Textbook: [DSC] 15.1–15.5; [DMS] 12.1–12.4, 14.4</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 17, §17.7–17.10, pp. 819–827</t>
         </is>
       </c>
       <c r="G50" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 9
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 9 ([DSC] 15.1–15.5; [DMS] 12.1–12.4, 14.4) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 17, §17.7–17.10, pp. 819–827 before class; prepare the constructivist questions</t>
         </is>
       </c>
       <c r="I50" s="74" t="inlineStr">
@@ -6936,15 +6980,13 @@
       <c r="J50" s="115" t="n"/>
       <c r="K50" s="115" t="n"/>
     </row>
-    <row r="51" ht="60" customHeight="1">
+    <row r="51" ht="45" customHeight="1">
       <c r="A51" s="42" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="32" t="inlineStr">
         <is>
-          <t>9.5 Reading execution plans
-9.7 Query optimization and join ordering
-Research Corner: Selinger et al. (1979); Leis et al. (2015); Kraska et al. (2018)</t>
+          <t>18.1 Lock-based protocols: two-phase locking and why it guarantees serializability</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -6954,7 +6996,7 @@
       </c>
       <c r="D51" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E51" s="32" t="inlineStr">
@@ -6964,20 +7006,21 @@
       </c>
       <c r="F51" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 9
-- Textbook: [DSC] 16.1–16.4; [DMS] 12.1–12.4, 15.1–15.4</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 18, §18.1, pp. 835–848</t>
         </is>
       </c>
       <c r="G51" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 9
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H51" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 9 ([DSC] 16.1–16.4; [DMS] 12.1–12.4, 15.1–15.4) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 18, §18.1, pp. 835–848 before class; prepare the constructivist questions
+Self-study: DSC §18.3 Multiple granularity, pp. 853–856</t>
         </is>
       </c>
       <c r="I51" s="74" t="inlineStr">
@@ -6994,8 +7037,8 @@
       </c>
       <c r="B52" s="32" t="inlineStr">
         <is>
-          <t>Lab 8 (part A): indexing experiments and execution plans
-Assignment 2 released (research topics)</t>
+          <t>18.2 Deadlock handling
+18.4 Insert operations, delete operations and predicate reads (phantoms)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -7005,48 +7048,49 @@
       </c>
       <c r="D52" s="32" t="inlineStr">
         <is>
-          <t>CLO6, CLO8</t>
+          <t>CLO7</t>
         </is>
       </c>
       <c r="E52" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F52" s="31" t="inlineStr">
         <is>
-          <t>- Lab 8 handout
-- Assignment 2 brief</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860</t>
         </is>
       </c>
       <c r="G52" s="31" t="inlineStr">
         <is>
-          <t>- Lab 8 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 9
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 8; submit before the end of the session</t>
+          <t>Read DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860 before class; prepare the constructivist questions
+Self-study: DSC §18.5 Timestamp-based protocols, pp. 861–865; §18.7 Multiversion schemes, pp. 869–871</t>
         </is>
       </c>
       <c r="I52" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 8; review and grade submissions</t>
+          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J52" s="115" t="n"/>
       <c r="K52" s="115" t="n"/>
     </row>
-    <row r="53" ht="75" customHeight="1">
+    <row r="53" ht="45" customHeight="1">
       <c r="A53" s="42" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="32" t="inlineStr">
         <is>
-          <t>10.1 Transactions
-10.2 ACID properties
-10.3 Transactions in T-SQL
-10.4 Transaction states</t>
+          <t>18.8 Snapshot isolation and write skew
+Research Corner: Berenson et al. (1995)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -7066,25 +7110,26 @@
       </c>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 10
-- Textbook: [DSC] 17.1–17.4; [DMS] 16.1–16.3</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 18, §18.8, pp. 872–879; Berenson et al. (1995)</t>
         </is>
       </c>
       <c r="G53" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 10
-- Textbooks [DSC], [DMS]</t>
+- Slides: Chapter 9
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H53" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 10 ([DSC] 17.1–17.4; [DMS] 16.1–16.3) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 18, §18.8, pp. 872–879; Berenson et al. (1995) before class; prepare the constructivist questions
+Self-study: DSC §18.9 Weak levels of consistency in practice, pp. 880–882</t>
         </is>
       </c>
       <c r="I53" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 10; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J53" s="115" t="n"/>
@@ -7096,8 +7141,7 @@
       </c>
       <c r="B54" s="32" t="inlineStr">
         <is>
-          <t>10.5 Concurrency anomalies
-10.6 Schedules and conflict serializability; precedence graphs</t>
+          <t>Lab 9: concurrency experiments with two sessions (isolation levels, deadlocks); Python serializability tester</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -7112,77 +7156,76 @@
       </c>
       <c r="E54" s="32" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F54" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 9 handout
+- Python starter code (schedule.py)
+- Textbook: DSC Ch. 17–18 Exercises, pp. 831–833, 899–903</t>
+        </is>
+      </c>
+      <c r="G54" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 9 handout and sample solution</t>
+        </is>
+      </c>
+      <c r="H54" s="31" t="inlineStr">
+        <is>
+          <t>Do Lab 9; submit before the end of the session</t>
+        </is>
+      </c>
+      <c r="I54" s="74" t="inlineStr">
+        <is>
+          <t>Guide Lab 9; review and grade submissions</t>
+        </is>
+      </c>
+      <c r="J54" s="115" t="n"/>
+      <c r="K54" s="115" t="n"/>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="42" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>Recovery system (overview): 19.1 Failure classification, 19.3 Recovery and atomicity (write-ahead logging), 19.4 Recovery algorithm (main ideas)
+Briefing for the self-study of Chapter 19</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t>CLO7</t>
+        </is>
+      </c>
+      <c r="E55" s="32" t="inlineStr">
+        <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F54" s="31" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 10
-- Textbook: [DSC] 17.5–17.6; [DMS] 16.3</t>
-        </is>
-      </c>
-      <c r="G54" s="31" t="inlineStr">
+      <c r="F55" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 10
+- Textbook: DSC Ch. 19, §19.1, §19.3, pp. 907, 912–921</t>
+        </is>
+      </c>
+      <c r="G55" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
 - Slides: Chapter 10
-- Textbooks [DSC], [DMS]</t>
-        </is>
-      </c>
-      <c r="H54" s="31" t="inlineStr">
-        <is>
-          <t>Read Chapter 10 ([DSC] 17.5–17.6; [DMS] 16.3) before class; prepare the constructivist questions</t>
-        </is>
-      </c>
-      <c r="I54" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 10; lead the discussion of the constructivist questions</t>
-        </is>
-      </c>
-      <c r="J54" s="115" t="n"/>
-      <c r="K54" s="115" t="n"/>
-    </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="42" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="32" t="inlineStr">
-        <is>
-          <t>10.7 Locking, two-phase locking, deadlocks
-10.8 Isolation levels
-10.9 Fixing a race condition</t>
-        </is>
-      </c>
-      <c r="C55" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="inlineStr">
-        <is>
-          <t>CLO7</t>
-        </is>
-      </c>
-      <c r="E55" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F55" s="31" t="inlineStr">
-        <is>
-          <t>- Lecture notes &amp; slides: Chapter 10
-- Textbook: [DSC] 18.1–18.2, 17.8; [DMS] 16.4–16.6, 17.1–17.2</t>
-        </is>
-      </c>
-      <c r="G55" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 10
-- Textbooks [DSC], [DMS]</t>
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H55" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 10 ([DSC] 18.1–18.2, 17.8; [DMS] 16.4–16.6, 17.1–17.2) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 19, §19.1, §19.3, pp. 907, 912–921 before class; prepare the constructivist questions
+Self-study: DSC §19.2 Storage, pp. 908–911; §19.4 Recovery algorithm, pp. 922–925; §19.5–19.6, pp. 926–930; optional §19.9 ARIES, pp. 941–946</t>
         </is>
       </c>
       <c r="I55" s="74" t="inlineStr">
@@ -7193,15 +7236,13 @@
       <c r="J55" s="115" t="n"/>
       <c r="K55" s="115" t="n"/>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="45" customHeight="1">
       <c r="A56" s="42" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="32" t="inlineStr">
         <is>
-          <t>10.10 Recovery (WAL, ARIES overview)
-10.11 Recoverability, view serializability, proof that 2PL is correct, snapshot isolation and write skew
-Research Corner: Eswaran et al. (1976); Berenson et al. (1995)</t>
+          <t>Assignment 2: research progress meeting (question, method, preliminary results)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -7211,35 +7252,32 @@
       </c>
       <c r="D56" s="32" t="inlineStr">
         <is>
-          <t>CLO7</t>
+          <t>CLO8</t>
         </is>
       </c>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F56" s="31" t="inlineStr">
         <is>
-          <t>- Lecture notes &amp; slides: Chapter 10
-- Textbook: [DSC] 17.7, 18.8, 19.1–19.4; [DMS] 16.7, 18.1</t>
+          <t>- Assignment 2 brief and rubric</t>
         </is>
       </c>
       <c r="G56" s="31" t="inlineStr">
         <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 10
-- Textbooks [DSC], [DMS]</t>
+          <t>- Assignment 2 rubric</t>
         </is>
       </c>
       <c r="H56" s="31" t="inlineStr">
         <is>
-          <t>Read Chapter 10 ([DSC] 17.7, 18.8, 19.1–19.4; [DMS] 16.7, 18.1) before class; prepare the constructivist questions</t>
+          <t>Present progress; revise the method</t>
         </is>
       </c>
       <c r="I56" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 10; lead the discussion of the constructivist questions</t>
+          <t>Give feedback on each group's method</t>
         </is>
       </c>
       <c r="J56" s="115" t="n"/>
@@ -7251,7 +7289,7 @@
       </c>
       <c r="B57" s="32" t="inlineStr">
         <is>
-          <t>Lab 8 (part B): concurrency experiments with two sessions; Python serializability tester</t>
+          <t>Assignment 2: paper presentations (part 1)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -7261,7 +7299,7 @@
       </c>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t>CLO7</t>
+          <t>CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
@@ -7271,23 +7309,22 @@
       </c>
       <c r="F57" s="31" t="inlineStr">
         <is>
-          <t>- Lab 8 handout
-- Python starter code labs/python (schedule.py)</t>
+          <t>- Assignment 2 brief</t>
         </is>
       </c>
       <c r="G57" s="31" t="inlineStr">
         <is>
-          <t>- Lab 8 handout and sample solution</t>
+          <t>- Assignment 2 rubric</t>
         </is>
       </c>
       <c r="H57" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 8; submit before the end of the session</t>
+          <t>Present the paper (10 minutes + 5 minutes Q&amp;A)</t>
         </is>
       </c>
       <c r="I57" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 8; review and grade submissions</t>
+          <t>Assess presentations and papers</t>
         </is>
       </c>
       <c r="J57" s="115" t="n"/>
@@ -7299,7 +7336,7 @@
       </c>
       <c r="B58" s="32" t="inlineStr">
         <is>
-          <t>Assignment 2: research progress meeting (question, method, preliminary results)</t>
+          <t>Assignment 2: paper presentations (part 2)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -7309,7 +7346,7 @@
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>CLO8</t>
+          <t>CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
@@ -7319,7 +7356,7 @@
       </c>
       <c r="F58" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 brief and rubric</t>
+          <t>- Assignment 2 brief</t>
         </is>
       </c>
       <c r="G58" s="31" t="inlineStr">
@@ -7329,12 +7366,12 @@
       </c>
       <c r="H58" s="31" t="inlineStr">
         <is>
-          <t>Present progress; revise the method</t>
+          <t>Present the paper; submit the final paper and code</t>
         </is>
       </c>
       <c r="I58" s="74" t="inlineStr">
         <is>
-          <t>Give feedback on each group's method</t>
+          <t>Assess presentations and papers</t>
         </is>
       </c>
       <c r="J58" s="115" t="n"/>
@@ -7346,7 +7383,7 @@
       </c>
       <c r="B59" s="32" t="inlineStr">
         <is>
-          <t>Assignment 2: paper presentations (part 1)</t>
+          <t>Course review (part 1): Chapters 1–6, including the self-study readings</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -7356,7 +7393,7 @@
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>CLO6, CLO7, CLO8</t>
+          <t>CLO1, CLO2, CLO3, CLO4, CLO5</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
@@ -7366,22 +7403,23 @@
       </c>
       <c r="F59" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 brief</t>
+          <t>- Slides: Chapters 1–6
+- Self-study reading list</t>
         </is>
       </c>
       <c r="G59" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 rubric</t>
+          <t>- Review questions</t>
         </is>
       </c>
       <c r="H59" s="31" t="inlineStr">
         <is>
-          <t>Present the paper (10 minutes + 5 minutes Q&amp;A)</t>
+          <t>Review Chapters 1–6 and the self-study readings</t>
         </is>
       </c>
       <c r="I59" s="74" t="inlineStr">
         <is>
-          <t>Assess presentations and papers</t>
+          <t>Answer questions; review key results</t>
         </is>
       </c>
       <c r="J59" s="115" t="n"/>
@@ -7393,7 +7431,7 @@
       </c>
       <c r="B60" s="32" t="inlineStr">
         <is>
-          <t>Assignment 2: paper presentations (part 2)</t>
+          <t>Course review (part 2): Chapters 7–10, including the self-study of recovery</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -7403,7 +7441,7 @@
       </c>
       <c r="D60" s="32" t="inlineStr">
         <is>
-          <t>CLO6, CLO7, CLO8</t>
+          <t>CLO6, CLO7</t>
         </is>
       </c>
       <c r="E60" s="32" t="inlineStr">
@@ -7413,22 +7451,23 @@
       </c>
       <c r="F60" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 brief</t>
+          <t>- Slides: Chapters 7–10
+- Self-study reading list</t>
         </is>
       </c>
       <c r="G60" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 rubric</t>
+          <t>- Review questions</t>
         </is>
       </c>
       <c r="H60" s="31" t="inlineStr">
         <is>
-          <t>Present the paper; submit the final paper and code</t>
+          <t>Review Chapters 7–10 and the self-study readings</t>
         </is>
       </c>
       <c r="I60" s="74" t="inlineStr">
         <is>
-          <t>Assess presentations and papers</t>
+          <t>Answer questions; review key results</t>
         </is>
       </c>
       <c r="J60" s="115" t="n"/>
@@ -7440,8 +7479,7 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>Course review: key results and open research questions
-Practical exam preparation</t>
+          <t>Practical exam preparation: SQL practice on the computer</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -7451,7 +7489,7 @@
       </c>
       <c r="D61" s="32" t="inlineStr">
         <is>
-          <t>CLO1–CLO8</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E61" s="32" t="inlineStr">
@@ -7461,24 +7499,22 @@
       </c>
       <c r="F61" s="31" t="inlineStr">
         <is>
-          <t>- Slides: all chapters
-- Question bank</t>
+          <t>- Practice problems (DDL and queries)</t>
         </is>
       </c>
       <c r="G61" s="31" t="inlineStr">
         <is>
-          <t>- Slides: all chapters
-- Question bank</t>
+          <t>- Practice problems and solutions</t>
         </is>
       </c>
       <c r="H61" s="31" t="inlineStr">
         <is>
-          <t>Review all chapters; practice SQL</t>
+          <t>Practise SQL under exam conditions</t>
         </is>
       </c>
       <c r="I61" s="74" t="inlineStr">
         <is>
-          <t>Review; answer questions</t>
+          <t>Guide the practice; clarify the exam rules</t>
         </is>
       </c>
       <c r="J61" s="115" t="n"/>
@@ -7615,7 +7651,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="69" t="n">
         <v>0.0001</v>
@@ -7636,11 +7672,11 @@
         </is>
       </c>
       <c r="J2" s="27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="28" t="inlineStr">
         <is>
-          <t>Labs 1–8 (Chapters 1–10)</t>
+          <t>Labs 1–9 (Chapters 1–9)</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
@@ -7650,7 +7686,7 @@
       </c>
       <c r="M2" s="25" t="inlineStr">
         <is>
-          <t>Each lab is worth 1.25%. The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark. Python tasks are graded by the provided unit tests and by code review.</t>
+          <t>Each lab is worth about 1.1% (10% / 9). The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark. Python tasks are graded by the provided unit tests and by code review.</t>
         </is>
       </c>
       <c r="N2" s="71" t="inlineStr">
@@ -7689,7 +7725,7 @@
       </c>
       <c r="H3" s="72" t="inlineStr">
         <is>
-          <t>CLO1, CLO2, CLO3</t>
+          <t>CLO1, CLO2, CLO3, CLO4</t>
         </is>
       </c>
       <c r="I3" s="25" t="inlineStr">
@@ -7704,8 +7740,8 @@
       </c>
       <c r="K3" s="28" t="inlineStr">
         <is>
-          <t>- cover content 1, 2, 3, 4
-- written items: one ER design or mapping task, one relational algebra/calculus proof or query</t>
+          <t>- cover Chapters 1–4 (DSC Ch. 1–4, §5.1, §5.4) and the self-study of relational calculus (DSC online Ch. 27)
+- written items: one relational algebra/calculus proof or query, one SQL semantics question (NULL, bags)</t>
         </is>
       </c>
       <c r="L3" s="19" t="inlineStr">
@@ -7756,7 +7792,7 @@
       </c>
       <c r="H4" s="72" t="inlineStr">
         <is>
-          <t>CLO4, CLO5</t>
+          <t>CLO2, CLO5</t>
         </is>
       </c>
       <c r="I4" s="25" t="inlineStr">
@@ -7771,8 +7807,8 @@
       </c>
       <c r="K4" s="28" t="inlineStr">
         <is>
-          <t>- cover content 5, 6, 7, 8
-- written items: one SQL semantics question (NULL/bags), one FD proof or normalization task</t>
+          <t>- cover Chapters 5–6 (DSC Ch. 6–7) and their self-study sections
+- written items: one E-R design and reduction task, one FD proof or normalization task</t>
         </is>
       </c>
       <c r="L4" s="19" t="inlineStr">
@@ -7836,13 +7872,13 @@
       </c>
       <c r="K5" s="28" t="inlineStr">
         <is>
-          <t>- cover content 2, 3, 4, 5, 6
+          <t>- cover Chapters 2–6 (DSC Ch. 2–4, 6–7)
 - design and theory report: ER model with justified alternatives, formal relational schema, constraints as logic, algebra/calculus/SQL queries with correctness arguments, one guided experiment</t>
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>take-home, submitted in session 38, graded by instructor with rubric</t>
+          <t>take-home; released in session 25, submitted and defended in session 33; graded by instructor with rubric</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
@@ -7899,13 +7935,13 @@
       </c>
       <c r="K6" s="28" t="inlineStr">
         <is>
-          <t>- cover content 6–10 and the Research Corner papers
+          <t>- cover Chapters 6–10 (DSC Ch. 7, 12–19) and the Research Corner papers
 - topics: empirical studies (indexes, join algorithms, isolation levels), algorithm implementation and evaluation (FD algorithms, serializability, relational algebra), or reproducing a result from a paper</t>
         </is>
       </c>
       <c r="L6" s="19" t="inlineStr">
         <is>
-          <t>take-home; progress meeting in session 57; presentations in sessions 58–59; graded by instructor with rubric</t>
+          <t>take-home; released in session 46; progress meeting in session 55; presentations in sessions 56–57; graded by instructor with rubric</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
@@ -7962,7 +7998,7 @@
       </c>
       <c r="K7" s="25" t="inlineStr">
         <is>
-          <t>- cover content 5, 6, 7
+          <t>- cover Chapters 3–5 (DSC Ch. 3, 4, 6)
 - create a schema with constraints from a specification; write SQL queries (joins, aggregation, subqueries, views)</t>
         </is>
       </c>
@@ -8026,7 +8062,7 @@
       </c>
       <c r="K8" s="25" t="inlineStr">
         <is>
-          <t>concepts, proofs, algorithms and analysis; all studied chapters; at least 30% of items at the Analyze level or above</t>
+          <t>concepts, proofs, algorithms and analysis; all chapters, including the self-study readings (about 20% of items); at least 30% of items at the Analyze level or above</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -1602,7 +1602,7 @@
 - use functional dependencies to evaluate and normalize a database design;
 - explain how a DBMS stores data, uses indexes and processes queries;
 - explain how transactions, concurrency control and recovery keep data correct;
-- read research papers and carry out small experiments on database topics.</t>
+- answer research-style questions and carry out small experiments on database topics.</t>
         </is>
       </c>
     </row>
@@ -1619,8 +1619,9 @@
       <c r="C13" s="18" t="inlineStr">
         <is>
           <t>- Students must attend at least 80% of contact slots in order to be accepted to the final examination.
-- Read the assigned textbook sections and the Research Corner paper BEFORE each theory session, and prepare answers to the constructivist questions.
-- Complete all 9 research labs, including the 'Investigate' part and the Python implementation tasks, and submit them on time.
+- Read the assigned textbook sections BEFORE each theory session.
+- For each chapter, choose ONE of its three constructivist questions and submit a short written answer (150–200 words) on the LMS within one week of the discussion session. The answers are graded as part of the research score (4% in total).
+- Complete all 9 labs, including the 'Investigate' part and the Python implementation tasks, and submit them on time.
 - Complete Assignment 1 (individual technical report) and Assignment 2 (group mini research project: short paper, reproducible code and presentation).
 - Complete the guided self-study readings listed in the schedule (abstract topics such as relational calculus, statistics estimation and recovery algorithms); they are assessed in the progress tests and the final exam.
 - Keep all code, scripts and measurements in a version-controlled repository so that results are reproducible.
@@ -1663,7 +1664,7 @@
       <c r="C15" s="21" t="inlineStr">
         <is>
           <t>1) On-going Assessment
-- 9 Research labs:                        10%
+- 9 labs + 10 CQ answers:              10%
 - 2 Progress tests:                        20%
 - Assignment 1 (technical report):   10%
 - Assignment 2 (research project):  20%
@@ -1674,7 +1675,7 @@
 1) Every on-going assessment component &gt; 0
 2) Practical Exam &gt; 0
 3) Final Exam Score &gt;= 4 &amp; Final Result &gt;= 5
-Rationale: the course serves talented students on an academic track, so 40% of the grade rewards research work (labs, report, research project), 60% rewards individual mastery of theory and skills (progress tests, practical exam, final exam), and the final exam includes at least 30% analysis-level items.</t>
+Rationale: the course serves talented students on an academic track, so 40% of the grade rewards research work (labs, constructivist questions, report, research project), 60% rewards individual mastery of theory and skills (progress tests, practical exam, final exam), and the final exam includes at least 30% analysis-level items.</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.2"/>
   <cols>
     <col width="3.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2013,7 +2014,7 @@
       </c>
       <c r="B4" s="127" t="inlineStr">
         <is>
-          <t>What Goes Around Comes Around… And Around…</t>
+          <t>Transact-SQL reference</t>
         </is>
       </c>
       <c r="C4" s="128" t="inlineStr">
@@ -2029,445 +2030,66 @@
       </c>
       <c r="F4" s="127" t="inlineStr">
         <is>
-          <t>Research Corner, Chapter 1. ACM SIGMOD Record 53(2)</t>
+          <t>https://learn.microsoft.com/sql/t-sql/</t>
         </is>
       </c>
       <c r="G4" s="127" t="inlineStr">
         <is>
-          <t>Michael Stonebraker, Andrew Pavlo</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="H4" s="127" t="inlineStr">
         <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I4" s="127" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="I4" s="127" t="inlineStr"/>
       <c r="J4" s="127" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="127" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="127" t="inlineStr">
-        <is>
-          <t>A Relational Model of Data for Large Shared Data Banks</t>
-        </is>
-      </c>
-      <c r="C5" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D5" s="128" t="inlineStr"/>
-      <c r="E5" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F5" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 2. Communications of the ACM 13(6):377–387</t>
-        </is>
-      </c>
-      <c r="G5" s="127" t="inlineStr">
-        <is>
-          <t>E. F. Codd</t>
-        </is>
-      </c>
-      <c r="H5" s="127" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I5" s="127" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="J5" s="127" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="127" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="127" t="inlineStr">
-        <is>
-          <t>SEQUEL: A Structured English Query Language</t>
-        </is>
-      </c>
-      <c r="C6" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D6" s="128" t="inlineStr"/>
-      <c r="E6" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F6" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 3. Proc. ACM SIGFIDET Workshop</t>
-        </is>
-      </c>
-      <c r="G6" s="127" t="inlineStr">
-        <is>
-          <t>Donald D. Chamberlin, Raymond F. Boyce</t>
-        </is>
-      </c>
-      <c r="H6" s="127" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I6" s="127" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="J6" s="127" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="127" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="127" t="inlineStr">
-        <is>
-          <t>The Entity-Relationship Model—Toward a Unified View of Data</t>
-        </is>
-      </c>
-      <c r="C7" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D7" s="128" t="inlineStr"/>
-      <c r="E7" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F7" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 5. ACM TODS 1(1):9–36</t>
-        </is>
-      </c>
-      <c r="G7" s="127" t="inlineStr">
-        <is>
-          <t>Peter P. Chen</t>
-        </is>
-      </c>
-      <c r="H7" s="127" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I7" s="127" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="J7" s="127" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="127" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="127" t="inlineStr">
-        <is>
-          <t>A Simple Guide to Five Normal Forms in Relational Database Theory</t>
-        </is>
-      </c>
-      <c r="C8" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D8" s="128" t="inlineStr"/>
-      <c r="E8" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F8" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 6. Communications of the ACM 26(2):120–125</t>
-        </is>
-      </c>
-      <c r="G8" s="127" t="inlineStr">
-        <is>
-          <t>William Kent</t>
-        </is>
-      </c>
-      <c r="H8" s="127" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I8" s="127" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="J8" s="127" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="127" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="127" t="inlineStr">
-        <is>
-          <t>Organization and Maintenance of Large Ordered Indexes</t>
-        </is>
-      </c>
-      <c r="C9" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D9" s="128" t="inlineStr"/>
-      <c r="E9" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F9" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 7. Acta Informatica 1:173–189</t>
-        </is>
-      </c>
-      <c r="G9" s="127" t="inlineStr">
-        <is>
-          <t>Rudolf Bayer, Edward McCreight</t>
-        </is>
-      </c>
-      <c r="H9" s="127" t="inlineStr">
-        <is>
-          <t>Springer</t>
-        </is>
-      </c>
-      <c r="I9" s="127" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="J9" s="127" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="127" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="127" t="inlineStr">
-        <is>
-          <t>The Case for Learned Index Structures</t>
-        </is>
-      </c>
-      <c r="C10" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D10" s="128" t="inlineStr"/>
-      <c r="E10" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F10" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 7. Proc. ACM SIGMOD</t>
-        </is>
-      </c>
-      <c r="G10" s="127" t="inlineStr">
-        <is>
-          <t>T. Kraska, A. Beutel, E. H. Chi, J. Dean, N. Polyzotis</t>
-        </is>
-      </c>
-      <c r="H10" s="127" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I10" s="127" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="J10" s="127" t="inlineStr"/>
-    </row>
+      <c r="B9" s="119" t="inlineStr">
+        <is>
+          <t>Ghi rõ ISBN với sách hardcopy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11" ht="26.4" customHeight="1">
-      <c r="A11" s="127" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="127" t="inlineStr">
-        <is>
-          <t>Access Path Selection in a Relational Database Management System</t>
-        </is>
-      </c>
-      <c r="C11" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D11" s="128" t="inlineStr"/>
-      <c r="E11" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F11" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 8. Proc. ACM SIGMOD</t>
-        </is>
-      </c>
-      <c r="G11" s="127" t="inlineStr">
-        <is>
-          <t>P. G. Selinger et al.</t>
-        </is>
-      </c>
-      <c r="H11" s="127" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I11" s="127" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="J11" s="127" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="127" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="127" t="inlineStr">
-        <is>
-          <t>A Critique of ANSI SQL Isolation Levels</t>
-        </is>
-      </c>
-      <c r="C12" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D12" s="128" t="inlineStr"/>
-      <c r="E12" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F12" s="127" t="inlineStr">
-        <is>
-          <t>Research Corner, Chapter 9. Proc. ACM SIGMOD</t>
-        </is>
-      </c>
-      <c r="G12" s="127" t="inlineStr">
-        <is>
-          <t>H. Berenson et al.</t>
-        </is>
-      </c>
-      <c r="H12" s="127" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="I12" s="127" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="J12" s="127" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="127" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="127" t="inlineStr">
-        <is>
-          <t>Transact-SQL reference</t>
-        </is>
-      </c>
-      <c r="C13" s="128" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="D13" s="128" t="inlineStr"/>
-      <c r="E13" s="127" t="inlineStr">
-        <is>
-          <t>online</t>
-        </is>
-      </c>
-      <c r="F13" s="127" t="inlineStr">
-        <is>
-          <t>https://learn.microsoft.com/sql/t-sql/</t>
-        </is>
-      </c>
-      <c r="G13" s="127" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="H13" s="127" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="I13" s="127" t="inlineStr"/>
-      <c r="J13" s="127" t="inlineStr"/>
-    </row>
-    <row r="14" ht="26.4" customHeight="1">
-      <c r="B14" s="117" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="116" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="119" t="inlineStr">
-        <is>
-          <t>Ghi rõ ISBN với sách hardcopy</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="114" t="inlineStr">
+      <c r="B11" s="114" t="inlineStr">
         <is>
           <t>Purpose: textbook or reference
 Type: hardcopy or online</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="116" t="inlineStr">
+      <c r="C11" s="118" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="113" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="116" t="inlineStr">
         <is>
           <t>Đối với các môn "m" hoặc "c"</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="117" t="inlineStr">
+    <row r="14" ht="26.4" customHeight="1">
+      <c r="B14" s="117" t="inlineStr">
         <is>
           <t>MaterialDescription: Tên MOOC, 
                                   Eg. MOOC 1: Architecting Solutions on AWS</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="116" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="116" t="inlineStr">
         <is>
           <t>Author: Tên Trường/Côngty/Tổ chức biên soạn MOOC</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="116" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="116" t="inlineStr">
         <is>
           <t>Publisher: Coursera</t>
         </is>
@@ -4490,12 +4112,12 @@
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 1, §1.1–1.3, pp. 1–12 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 1, §1.1–1.3, pp. 1–12 before class</t>
         </is>
       </c>
       <c r="I2" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 1; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 1</t>
         </is>
       </c>
       <c r="J2" s="115" t="inlineStr">
@@ -4551,13 +4173,13 @@
       </c>
       <c r="H3" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 1, §1.4–1.7, pp. 13–23 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 1, §1.4–1.7, pp. 13–23 before class
 Self-study: DSC §1.8–1.9 (users and administrators; history of database systems), pp. 24–28</t>
         </is>
       </c>
       <c r="I3" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 1; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 1</t>
         </is>
       </c>
       <c r="J3" s="115" t="n"/>
@@ -4569,7 +4191,7 @@
       </c>
       <c r="B4" s="32" t="inlineStr">
         <is>
-          <t>Research Corner: history of data models (Stonebraker &amp; Pavlo, 2024)
+          <t>Discussion of the Chapter 1 constructivist questions
 Lab 1: install SQL Server; load the sample university database</t>
         </is>
       </c>
@@ -4592,7 +4214,6 @@
       <c r="F4" s="33" t="inlineStr">
         <is>
           <t>- Slides: Chapter 1
-- Paper: Stonebraker &amp; Pavlo (2024)
 - Lab 1 handout
 - Textbook: DSC Appendix A, pp. 1287–1298</t>
         </is>
@@ -4605,12 +4226,13 @@
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>Read the paper with the guiding questions; do Lab 1</t>
+          <t>Discuss the Chapter 1 constructivist questions; choose one and submit a 150–200-word answer within one week
+Do Lab 1</t>
         </is>
       </c>
       <c r="I4" s="74" t="inlineStr">
         <is>
-          <t>Lead the paper discussion; guide Lab 1</t>
+          <t>Lead the discussion; guide Lab 1</t>
         </is>
       </c>
       <c r="J4" s="115" t="n"/>
@@ -4659,12 +4281,12 @@
       </c>
       <c r="H5" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 2, §2.1–2.4, pp. 37–46 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 2, §2.1–2.4, pp. 37–46 before class</t>
         </is>
       </c>
       <c r="I5" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 2; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 2</t>
         </is>
       </c>
       <c r="J5" s="115" t="n"/>
@@ -4710,12 +4332,12 @@
       </c>
       <c r="H6" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 2, §2.5–2.6, pp. 47–57 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 2, §2.5–2.6, pp. 47–57 before class</t>
         </is>
       </c>
       <c r="I6" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 2; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 2</t>
         </is>
       </c>
       <c r="J6" s="115" t="n"/>
@@ -4727,8 +4349,7 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>2.6 The relational algebra (cont.): joins, intersection, assignment, equivalent queries; division and aggregation as extended operators
-Research Corner: Codd (1970)</t>
+          <t>2.6 The relational algebra (cont.): joins, intersection, assignment, equivalent queries; division and aggregation as extended operators</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -4749,7 +4370,7 @@
       <c r="F7" s="33" t="inlineStr">
         <is>
           <t>- Slides: Chapter 2
-- Textbook: DSC Ch. 2, §2.6, pp. 48–57; Codd (1970)</t>
+- Textbook: DSC Ch. 2, §2.6, pp. 48–57</t>
         </is>
       </c>
       <c r="G7" s="33" t="inlineStr">
@@ -4761,13 +4382,13 @@
       </c>
       <c r="H7" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 2, §2.6, pp. 48–57; Codd (1970) before class; prepare the constructivist questions
+          <t>Read DSC Ch. 2, §2.6, pp. 48–57 before class
 Self-study: Relational calculus (tuple and domain) and Codd's theorem, DSC online Ch. 27 – guided reading with worksheet</t>
         </is>
       </c>
       <c r="I7" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 2; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 2</t>
         </is>
       </c>
       <c r="J7" s="115" t="n"/>
@@ -4859,12 +4480,13 @@
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>Submit the self-study worksheet; solve the proof exercises</t>
+          <t>Submit the self-study worksheet; solve the proof exercises
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I9" s="74" t="inlineStr">
         <is>
-          <t>Check the worksheet; discuss common mistakes</t>
+          <t>Check the worksheet; discuss common mistakes; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J9" s="115" t="inlineStr">
@@ -4919,12 +4541,12 @@
       </c>
       <c r="H10" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 3, §3.1–3.3, pp. 65–78 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.1–3.3, pp. 65–78 before class</t>
         </is>
       </c>
       <c r="I10" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 3; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 3</t>
         </is>
       </c>
       <c r="J10" s="115" t="n"/>
@@ -4971,12 +4593,12 @@
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 3, §3.4–3.6, pp. 79–90 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.4–3.6, pp. 79–90 before class</t>
         </is>
       </c>
       <c r="I11" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 3; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 3</t>
         </is>
       </c>
       <c r="J11" s="115" t="n"/>
@@ -5026,26 +4648,25 @@
       </c>
       <c r="H12" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 3, §3.7–3.8, pp. 91–107 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.7–3.8, pp. 91–107 before class</t>
         </is>
       </c>
       <c r="I12" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 3; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 3</t>
         </is>
       </c>
       <c r="J12" s="115" t="n"/>
       <c r="K12" s="115" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="42" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
           <t>3.9 Modification of the database
-Semantics of SQL: bag semantics and translation to relational algebra
-Research Corner: Chamberlin &amp; Boyce (1974)</t>
+Semantics of SQL: bag semantics and translation to relational algebra</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -5066,7 +4687,7 @@
       <c r="F13" s="33" t="inlineStr">
         <is>
           <t>- Slides: Chapter 3
-- Textbook: DSC Ch. 3, §3.9, pp. 108–113; Chamberlin &amp; Boyce (1974)</t>
+- Textbook: DSC Ch. 3, §3.9, pp. 108–113</t>
         </is>
       </c>
       <c r="G13" s="33" t="inlineStr">
@@ -5078,7 +4699,8 @@
       </c>
       <c r="H13" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 3, §3.9, pp. 108–113; Chamberlin &amp; Boyce (1974) before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 3, §3.9, pp. 108–113 before class
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I13" s="74" t="inlineStr">
@@ -5229,12 +4851,12 @@
       </c>
       <c r="H16" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 4, §4.1–4.2, pp. 125–142 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 4, §4.1–4.2, pp. 125–142 before class</t>
         </is>
       </c>
       <c r="I16" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 4; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 4</t>
         </is>
       </c>
       <c r="J16" s="115" t="inlineStr">
@@ -5289,13 +4911,13 @@
       </c>
       <c r="H17" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 4, §4.3–4.5, pp. 143–163 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 4, §4.3–4.5, pp. 143–163 before class
 Self-study: DSC §4.7 Authorization, pp. 165–172</t>
         </is>
       </c>
       <c r="I17" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 4; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 4</t>
         </is>
       </c>
       <c r="J17" s="115" t="n"/>
@@ -5341,13 +4963,13 @@
       </c>
       <c r="H18" s="31" t="inlineStr">
         <is>
-          <t>Read DSC §4.6, p. 164; §5.4, pp. 213–218 before class; prepare the constructivist questions
+          <t>Read DSC §4.6, p. 164; §5.4, pp. 213–218 before class
 Self-study: DSC §5.5 Advanced aggregation features (ranking, windowing), pp. 219–230</t>
         </is>
       </c>
       <c r="I18" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 4; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 4</t>
         </is>
       </c>
       <c r="J18" s="115" t="n"/>
@@ -5393,8 +5015,9 @@
       </c>
       <c r="H19" s="31" t="inlineStr">
         <is>
-          <t>Read DSC §5.1, pp. 183–197 before class; prepare the constructivist questions
-Self-study: DSC §9.8 Application security, pp. 437–446; optional: §5.2–5.3 functions, procedures, triggers, pp. 198–212</t>
+          <t>Read DSC §5.1, pp. 183–197 before class
+Self-study: DSC §9.8 Application security, pp. 437–446; optional: §5.2–5.3 functions, procedures, triggers, pp. 198–212
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I19" s="74" t="inlineStr">
@@ -5543,12 +5166,12 @@
       </c>
       <c r="H22" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 6, §6.1–6.3, pp. 241–251 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 6, §6.1–6.3, pp. 241–251 before class</t>
         </is>
       </c>
       <c r="I22" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 5</t>
         </is>
       </c>
       <c r="J22" s="115" t="n"/>
@@ -5595,12 +5218,12 @@
       </c>
       <c r="H23" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 6, §6.4–6.6, pp. 252–263 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 6, §6.4–6.6, pp. 252–263 before class</t>
         </is>
       </c>
       <c r="I23" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 5</t>
         </is>
       </c>
       <c r="J23" s="115" t="n"/>
@@ -5645,13 +5268,13 @@
       </c>
       <c r="H24" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 6, §6.7, pp. 264–270 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 6, §6.7, pp. 264–270 before class
 Self-study: DSC §6.8 Extended E-R features, pp. 271–278</t>
         </is>
       </c>
       <c r="I24" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 5</t>
         </is>
       </c>
       <c r="J24" s="115" t="n"/>
@@ -5663,8 +5286,7 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>6.9 Entity-relationship design issues; limits of the E-R model
-Research Corner: Chen (1976)</t>
+          <t>6.9 Entity-relationship design issues; limits of the E-R model</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -5685,7 +5307,7 @@
       <c r="F25" s="33" t="inlineStr">
         <is>
           <t>- Slides: Chapter 5
-- Textbook: DSC Ch. 6, §6.9, pp. 279–284; Chen (1976)</t>
+- Textbook: DSC Ch. 6, §6.9, pp. 279–284</t>
         </is>
       </c>
       <c r="G25" s="31" t="inlineStr">
@@ -5697,8 +5319,9 @@
       </c>
       <c r="H25" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 6, §6.9, pp. 279–284; Chen (1976) before class; prepare the constructivist questions
-Self-study: DSC §6.10–6.11 Alternative notations (crow's foot, UML) and other aspects of design, pp. 285–291</t>
+          <t>Read DSC Ch. 6, §6.9, pp. 279–284 before class
+Self-study: DSC §6.10–6.11 Alternative notations (crow's foot, UML) and other aspects of design, pp. 285–291
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I25" s="74" t="inlineStr">
@@ -5800,12 +5423,12 @@
       </c>
       <c r="H27" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 7, §7.1–7.2, pp. 303–312 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.1–7.2, pp. 303–312 before class</t>
         </is>
       </c>
       <c r="I27" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 6</t>
         </is>
       </c>
       <c r="J27" s="115" t="n"/>
@@ -5850,12 +5473,12 @@
       </c>
       <c r="H28" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 7, §7.3, pp. 313–319 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.3, pp. 313–319 before class</t>
         </is>
       </c>
       <c r="I28" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 6</t>
         </is>
       </c>
       <c r="J28" s="115" t="n"/>
@@ -5900,12 +5523,12 @@
       </c>
       <c r="H29" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class</t>
         </is>
       </c>
       <c r="I29" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 6</t>
         </is>
       </c>
       <c r="J29" s="115" t="n"/>
@@ -5950,12 +5573,12 @@
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class</t>
         </is>
       </c>
       <c r="I30" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 6</t>
         </is>
       </c>
       <c r="J30" s="115" t="n"/>
@@ -6000,26 +5623,25 @@
       </c>
       <c r="H31" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 7, §7.5, pp. 330–335 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 7, §7.5, pp. 330–335 before class</t>
         </is>
       </c>
       <c r="I31" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 6</t>
         </is>
       </c>
       <c r="J31" s="115" t="n"/>
       <c r="K31" s="115" t="n"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="42" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
           <t>7.6 Decomposition using multivalued dependencies (4NF, overview)
-7.8 Atomic domains and first normal form
-Research Corner: Kent (1983)</t>
+7.8 Atomic domains and first normal form</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -6052,8 +5674,9 @@
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 7, §7.6, §7.8, pp. 336–340, 342 before class; prepare the constructivist questions
-Self-study: DSC §7.7 More normal forms, p. 341; §7.9 Database-design process, pp. 343–346</t>
+          <t>Read DSC Ch. 7, §7.6, §7.8, pp. 336–340, 342 before class
+Self-study: DSC §7.7 More normal forms, p. 341; §7.9 Database-design process, pp. 343–346
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I32" s="74" t="inlineStr">
@@ -6250,13 +5873,13 @@
       </c>
       <c r="H36" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 13, §13.1–13.3, pp. 587–601 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 13, §13.1–13.3, pp. 587–601 before class
 Self-study: DSC §12.1 Physical storage media, pp. 559–561; §12.6 Disk-block access, pp. 577–579</t>
         </is>
       </c>
       <c r="I36" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 7</t>
         </is>
       </c>
       <c r="J36" s="115" t="n"/>
@@ -6303,13 +5926,13 @@
       </c>
       <c r="H37" s="31" t="inlineStr">
         <is>
-          <t>Read DSC §13.5, pp. 604–610; Ch. 14, §14.1–14.2, pp. 623–633 before class; prepare the constructivist questions
+          <t>Read DSC §13.5, pp. 604–610; Ch. 14, §14.1–14.2, pp. 623–633 before class
 Self-study: DSC §13.4 Data-dictionary storage, pp. 602–603</t>
         </is>
       </c>
       <c r="I37" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 7</t>
         </is>
       </c>
       <c r="J37" s="115" t="n"/>
@@ -6354,19 +5977,19 @@
       </c>
       <c r="H38" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 14, §14.3, pp. 634–649 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 14, §14.3, pp. 634–649 before class
 Self-study: DSC §14.4 B+-tree extensions, pp. 650–657</t>
         </is>
       </c>
       <c r="I38" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 7</t>
         </is>
       </c>
       <c r="J38" s="115" t="n"/>
       <c r="K38" s="115" t="n"/>
     </row>
-    <row r="39" ht="75" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="42" t="n">
         <v>38</v>
       </c>
@@ -6374,8 +5997,7 @@
         <is>
           <t>14.5 Hash indices
 14.6 Multiple-key access
-14.7 Creation of indices
-Research Corner: Bayer &amp; McCreight (1972); Kraska et al. (2018)</t>
+14.7 Creation of indices</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -6408,13 +6030,13 @@
       </c>
       <c r="H39" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 14, §14.5–14.7, pp. 658–664 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 14, §14.5–14.7, pp. 658–664 before class
 Self-study: Optional: §13.6 Column-oriented storage, pp. 611–614; §14.8 Write-optimized index structures (LSM), pp. 665–669</t>
         </is>
       </c>
       <c r="I39" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 7</t>
         </is>
       </c>
       <c r="J39" s="115" t="n"/>
@@ -6457,12 +6079,13 @@
       </c>
       <c r="H40" s="31" t="inlineStr">
         <is>
-          <t>Solve the exercises; compare hand-computed costs with the formulas</t>
+          <t>Solve the exercises; compare hand-computed costs with the formulas
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I40" s="74" t="inlineStr">
         <is>
-          <t>Guide the exercises; discuss solutions</t>
+          <t>Guide the exercises; discuss solutions; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J40" s="115" t="n"/>
@@ -6557,12 +6180,12 @@
       </c>
       <c r="H42" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 15, §15.1–15.3, pp. 689–700 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 15, §15.1–15.3, pp. 689–700 before class</t>
         </is>
       </c>
       <c r="I42" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 8</t>
         </is>
       </c>
       <c r="J42" s="115" t="n"/>
@@ -6608,12 +6231,12 @@
       </c>
       <c r="H43" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 15, §15.4, pp. 701–703; §15.5, pp. 704–718 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 15, §15.4, pp. 701–703; §15.5, pp. 704–718 before class</t>
         </is>
       </c>
       <c r="I43" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 8</t>
         </is>
       </c>
       <c r="J43" s="115" t="n"/>
@@ -6658,13 +6281,13 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 15, §15.5, pp. 704–718 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 15, §15.5, pp. 704–718 before class
 Self-study: DSC §15.6 Other operations, pp. 719–723; §15.7 Evaluation of expressions (pipelining), pp. 724–730</t>
         </is>
       </c>
       <c r="I44" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 8</t>
         </is>
       </c>
       <c r="J44" s="115" t="n"/>
@@ -6710,12 +6333,12 @@
       </c>
       <c r="H45" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 16, §16.1–16.2, pp. 743–756 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 16, §16.1–16.2, pp. 743–756 before class</t>
         </is>
       </c>
       <c r="I45" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 8</t>
         </is>
       </c>
       <c r="J45" s="115" t="n"/>
@@ -6727,8 +6350,7 @@
       </c>
       <c r="B46" s="32" t="inlineStr">
         <is>
-          <t>16.4 Choice of evaluation plans: cost-based join ordering (dynamic programming)
-Research Corner: Selinger et al. (1979)</t>
+          <t>16.4 Choice of evaluation plans: cost-based join ordering (dynamic programming)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -6761,8 +6383,9 @@
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 16, §16.4, pp. 766–777 before class; prepare the constructivist questions
-Self-study: DSC §16.3 Estimating statistics of expression results, pp. 757–765</t>
+          <t>Read DSC Ch. 16, §16.4, pp. 766–777 before class
+Self-study: DSC §16.3 Estimating statistics of expression results, pp. 757–765
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I46" s="74" t="inlineStr">
@@ -6865,12 +6488,12 @@
       </c>
       <c r="H48" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 17, §17.1–17.4, pp. 799–806 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 17, §17.1–17.4, pp. 799–806 before class</t>
         </is>
       </c>
       <c r="I48" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 9</t>
         </is>
       </c>
       <c r="J48" s="115" t="n"/>
@@ -6916,12 +6539,12 @@
       </c>
       <c r="H49" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 17, §17.5–17.6, pp. 807–818 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 17, §17.5–17.6, pp. 807–818 before class</t>
         </is>
       </c>
       <c r="I49" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 9</t>
         </is>
       </c>
       <c r="J49" s="115" t="n"/>
@@ -6969,12 +6592,12 @@
       </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 17, §17.7–17.10, pp. 819–827 before class; prepare the constructivist questions</t>
+          <t>Read DSC Ch. 17, §17.7–17.10, pp. 819–827 before class</t>
         </is>
       </c>
       <c r="I50" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 9</t>
         </is>
       </c>
       <c r="J50" s="115" t="n"/>
@@ -7019,13 +6642,13 @@
       </c>
       <c r="H51" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 18, §18.1, pp. 835–848 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 18, §18.1, pp. 835–848 before class
 Self-study: DSC §18.3 Multiple granularity, pp. 853–856</t>
         </is>
       </c>
       <c r="I51" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 9</t>
         </is>
       </c>
       <c r="J51" s="115" t="n"/>
@@ -7071,13 +6694,13 @@
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860 before class; prepare the constructivist questions
+          <t>Read DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860 before class
 Self-study: DSC §18.5 Timestamp-based protocols, pp. 861–865; §18.7 Multiversion schemes, pp. 869–871</t>
         </is>
       </c>
       <c r="I52" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 9</t>
         </is>
       </c>
       <c r="J52" s="115" t="n"/>
@@ -7089,8 +6712,7 @@
       </c>
       <c r="B53" s="32" t="inlineStr">
         <is>
-          <t>18.8 Snapshot isolation and write skew
-Research Corner: Berenson et al. (1995)</t>
+          <t>18.8 Snapshot isolation and write skew</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -7111,7 +6733,7 @@
       <c r="F53" s="31" t="inlineStr">
         <is>
           <t>- Slides: Chapter 9
-- Textbook: DSC Ch. 18, §18.8, pp. 872–879; Berenson et al. (1995)</t>
+- Textbook: DSC Ch. 18, §18.8, pp. 872–879</t>
         </is>
       </c>
       <c r="G53" s="31" t="inlineStr">
@@ -7123,8 +6745,9 @@
       </c>
       <c r="H53" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 18, §18.8, pp. 872–879; Berenson et al. (1995) before class; prepare the constructivist questions
-Self-study: DSC §18.9 Weak levels of consistency in practice, pp. 880–882</t>
+          <t>Read DSC Ch. 18, §18.8, pp. 872–879 before class
+Self-study: DSC §18.9 Weak levels of consistency in practice, pp. 880–882
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I53" s="74" t="inlineStr">
@@ -7224,8 +6847,9 @@
       </c>
       <c r="H55" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 19, §19.1, §19.3, pp. 907, 912–921 before class; prepare the constructivist questions
-Self-study: DSC §19.2 Storage, pp. 908–911; §19.4 Recovery algorithm, pp. 922–925; §19.5–19.6, pp. 926–930; optional §19.9 ARIES, pp. 941–946</t>
+          <t>Read DSC Ch. 19, §19.1, §19.3, pp. 907, 912–921 before class
+Self-study: DSC §19.2 Storage, pp. 908–911; §19.4 Recovery algorithm, pp. 922–925; §19.5–19.6, pp. 926–930; optional §19.9 ARIES, pp. 941–946
+Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
         </is>
       </c>
       <c r="I55" s="74" t="inlineStr">
@@ -7639,7 +7263,7 @@
       </c>
       <c r="B2" s="71" t="inlineStr">
         <is>
-          <t>Research labs</t>
+          <t>Labs and constructivist questions</t>
         </is>
       </c>
       <c r="C2" s="69" t="inlineStr">
@@ -7651,42 +7275,44 @@
         <v>10</v>
       </c>
       <c r="E2" s="69" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F2" s="69" t="n">
         <v>0.0001</v>
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>In lab sessions</t>
+          <t>Labs: in lab sessions; CQ answers: 1 week after each discussion</t>
         </is>
       </c>
       <c r="H2" s="72" t="inlineStr">
         <is>
-          <t>CLO2, CLO3, CLO4, CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO1, CLO2, CLO3, CLO4, CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>Lab exercises, Python implementations with tests, 'Investigate' mini-reports</t>
-        </is>
-      </c>
-      <c r="J2" s="27" t="n">
-        <v>9</v>
+          <t>Lab exercises, Python implementations with tests, 'Investigate' mini-reports; short written answers to constructivist questions</t>
+        </is>
+      </c>
+      <c r="J2" s="27" t="inlineStr">
+        <is>
+          <t>9 labs + 10 CQ answers</t>
+        </is>
       </c>
       <c r="K2" s="28" t="inlineStr">
         <is>
-          <t>Labs 1–9 (Chapters 1–9)</t>
+          <t>Labs 1–9 (Chapters 1–9); one constructivist question chosen by the student from each of the 10 chapters</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
         <is>
-          <t>in class, by instructor</t>
+          <t>labs: in class, by instructor; CQ answers: on the LMS, by instructor with a short rubric</t>
         </is>
       </c>
       <c r="M2" s="25" t="inlineStr">
         <is>
-          <t>Each lab is worth about 1.1% (10% / 9). The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark. Python tasks are graded by the provided unit tests and by code review.</t>
+          <t>Labs 6% in total (about 0.67% each). Constructivist-question answers 4% in total (0.4% each; 150–200 words; graded on reasoning, use of the textbook and clarity). The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark. Python tasks are graded by the provided unit tests and by code review.</t>
         </is>
       </c>
       <c r="N2" s="71" t="inlineStr">
@@ -7935,8 +7561,8 @@
       </c>
       <c r="K6" s="28" t="inlineStr">
         <is>
-          <t>- cover Chapters 6–10 (DSC Ch. 7, 12–19) and the Research Corner papers
-- topics: empirical studies (indexes, join algorithms, isolation levels), algorithm implementation and evaluation (FD algorithms, serializability, relational algebra), or reproducing a result from a paper</t>
+          <t>- cover Chapters 6–10 (DSC Ch. 7, 12–19)
+- topics: empirical studies (indexes, join algorithms, isolation levels), algorithm implementation and evaluation (FD algorithms, serializability, relational algebra), or reproducing at small scale a result from a published paper found by the group</t>
         </is>
       </c>
       <c r="L6" s="19" t="inlineStr">

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -1583,7 +1583,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="125" customFormat="1" customHeight="1" s="10">
+    <row r="12" ht="150" customFormat="1" customHeight="1" s="10">
       <c r="A12" s="78" t="n">
         <v>11</v>
       </c>
@@ -1596,12 +1596,12 @@
       <c r="C12" s="17" t="inlineStr">
         <is>
           <t>This course aims to help students:
-- understand the basic concepts of database systems and the relational model;
+- understand the formal foundations of the relational model: relations as sets, and keys and constraints as logical statements;
 - design databases with the Entity-Relationship model and convert them into relational schemas;
-- write queries in relational algebra, relational calculus and SQL;
-- use functional dependencies to evaluate and normalize a database design;
-- explain how a DBMS stores data, uses indexes and processes queries;
-- explain how transactions, concurrency control and recovery keep data correct;
+- write queries in relational algebra, relational calculus and SQL, and reason about what each language can express;
+- apply functional-dependency theory and its algorithms to normalize a design, and prove that a decomposition is correct;
+- analyze the cost and complexity of storage, indexing and query-processing algorithms;
+- explain the system internals that keep data correct: transactions, concurrency control and recovery;
 - answer research-style questions and carry out small experiments on database topics.</t>
         </is>
       </c>

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C3" s="124" t="inlineStr">
         <is>
-          <t>UNDERGRADUATE PROGRAM – Bachelor of Computer Science, specialization in Artificial Intelligence and Data Science (BCS_AD), cohort K22A onward – Talented-student (honors) classes</t>
+          <t>UNDERGRADUATE PROGRAM – Bachelor of Computer Science.</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C11" s="60" t="inlineStr">
         <is>
-          <t>None (semester 1). Taken together with MAD102 Discrete Mathematics and PFP191 Programming Fundamentals with Python.</t>
+          <t>None (semester 1).</t>
         </is>
       </c>
     </row>
@@ -1596,13 +1596,13 @@
       <c r="C12" s="17" t="inlineStr">
         <is>
           <t>This course aims to help students:
-- understand the formal foundations of the relational model: relations as sets, and keys and constraints as logical statements;
-- design databases with the Entity-Relationship model and convert them into relational schemas;
-- write queries in relational algebra, relational calculus and SQL, and reason about what each language can express;
-- apply functional-dependency theory and its algorithms to normalize a design, and prove that a decomposition is correct;
-- analyze the cost and complexity of storage, indexing and query-processing algorithms;
-- explain the system internals that keep data correct: transactions, concurrency control and recovery;
-- answer research-style questions and carry out small experiments on database topics.</t>
+- Understand the formal foundations of the relational model: relations as sets, and keys and constraints as logical statements;
+- Design databases with the Entity-Relationship model and convert them into relational schemas;
+- Write queries in relational algebra, relational calculus and SQL, and reason about what each language can express;
+- Apply functional-dependency theory and its algorithms to normalize a design, and prove that a decomposition is correct;
+- Analyze the cost and complexity of storage, indexing and query-processing algorithms;
+- Explain the system internals that keep data correct: transactions, concurrency control and recovery;
+- Answer research-style questions and carry out small experiments on database topics.</t>
         </is>
       </c>
     </row>
@@ -1620,10 +1620,11 @@
         <is>
           <t>- Students must attend at least 80% of contact slots in order to be accepted to the final examination.
 - Read the assigned textbook sections BEFORE each theory session.
-- For each chapter, choose ONE of its three constructivist questions and submit a short written answer (150–200 words) on the LMS within one week of the discussion session. The answers are graded as part of the research score (4% in total).
-- Complete all 9 labs, including the 'Investigate' part and the Python implementation tasks, and submit them on time.
-- Complete Assignment 1 (individual technical report) and Assignment 2 (group mini research project: short paper, reproducible code and presentation).
-- Complete the guided self-study readings listed in the schedule (abstract topics such as relational calculus, statistics estimation and recovery algorithms); they are assessed in the progress tests and the final exam.
+- For each chapter, choose ONE of its three constructivist questions and submit a short written answer on the LMS within one week of the discussion session. The answers are graded as part of the lab and constructivist-question score (4% in total).
+- Complete all 5 labs, including the 'Investigate' part, and submit them on time.
+- Complete the group project (one assignment for the whole course): a database designed through the course and a small study answering research questions about it, delivered as an academic report, reproducible SQL scripts and a presentation.
+- Complete the guided self-study readings listed in the schedule (abstract topics such as relational calculus, bag semantics of SQL, statistics estimation and recovery algorithms); they are assessed in the progress tests and the final exam.
+- Python (accessing SQL Server from Python; Python versions of the course algorithms) is optional self-study. It is not taught in class and is not required in the labs.
 - Keep all code, scripts and measurements in a version-controlled repository so that results are reproducible.
 - Disclose any use of generative AI tools in submitted work; undisclosed use is treated as a breach of academic integrity.
 - Use laptop in class only for learning purpose.
@@ -1642,13 +1643,12 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>- Microsoft SQL Server 2022 (Developer/Express) or SQL Server in Docker
-- SQL Server Management Studio (SSMS) or Azure Data Studio
-- Python 3 with pyodbc, pandas and pytest; Visual Studio Code or PyCharm
-- RelaX relational algebra calculator (online)
+          <t>- Microsoft SQL Server (Developer/Express)
+- SQL Server Management Studio (SSMS)
 - draw.io (diagrams.net) for ER diagrams
-- Git / GitHub for reproducible code and experiments
-- LaTeX (Overleaf) with the IEEE conference template for Assignment 2</t>
+- RelaX relational algebra calculator (online, optional)
+- Git / GitHub for reproducible code and experiments (optional)
+- Python 3 with pyodbc and pandas; Visual Studio Code or PyCharm (optional, self-study only)</t>
         </is>
       </c>
     </row>
@@ -1663,19 +1663,16 @@
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>1) On-going Assessment
-- 9 labs + 10 CQ answers:              10%
-- 2 Progress tests:                        20%
-- Assignment 1 (technical report):   10%
-- Assignment 2 (research project):  20%
-- 1 Practical Exam (PE):                 10%
-2) 1 Final Exam:                            30%
+          <t>1) On-going Assessment:                 50%
+- 5 labs + 10 CQ answers:              10%
+- Progress test 1:                          5%
+- Progress test 2:                          5%
+- 1 Assignment (group project):      30%
+2) 1 Final Exam:                            50%
 3) Final Result                             100%
 Completion Criteria:
 1) Every on-going assessment component &gt; 0
-2) Practical Exam &gt; 0
-3) Final Exam Score &gt;= 4 &amp; Final Result &gt;= 5
-Rationale: the course serves talented students on an academic track, so 40% of the grade rewards research work (labs, constructivist questions, report, research project), 60% rewards individual mastery of theory and skills (progress tests, practical exam, final exam), and the final exam includes at least 30% analysis-level items.</t>
+2) Final Exam Score &gt;= 5 &amp; Final Result &gt;= 5</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2259,7 @@
       </c>
       <c r="C5" s="104" t="inlineStr">
         <is>
-          <t>Use SQL to define, populate, modify and query relational databases (joins, aggregation, subqueries, views, access from Python) and explain query results through SQL semantics (bag semantics, three-valued logic).</t>
+          <t>Use SQL to define, populate, modify and query relational databases (joins, aggregation, subqueries, views, parameterized queries) and explain query results through SQL semantics (three-valued logic; bag semantics through guided self-study).</t>
         </is>
       </c>
       <c r="D5" s="103" t="n"/>
@@ -2295,7 +2292,7 @@
       </c>
       <c r="C6" s="104" t="inlineStr">
         <is>
-          <t>Analyze and improve relational schemas with functional dependency theory: compute closures, candidate keys and minimal covers, prove basic properties, decompose to 3NF/BCNF with lossless-join and dependency-preservation guarantees, and implement these algorithms in Python.</t>
+          <t>Analyze and improve relational schemas with functional dependency theory: compute closures, candidate keys and minimal covers, prove basic properties, decompose to 3NF/BCNF with lossless-join and dependency-preservation guarantees.</t>
         </is>
       </c>
       <c r="D6" s="103" t="n"/>
@@ -2394,7 +2391,7 @@
       </c>
       <c r="C9" s="104" t="inlineStr">
         <is>
-          <t>Conduct a small, reproducible research study on a database topic: review primary literature, formulate a research question or hypothesis, design and carry out an experiment or implementation, and report the results in an academic paper and presentation.</t>
+          <t>Conduct a small, reproducible research study on a database topic: review primary literature, formulate a research question or hypothesis, design and carry out an experiment or implementation, and report the results in an academic report and presentation.</t>
         </is>
       </c>
       <c r="D9" s="103" t="n"/>
@@ -3110,7 +3107,7 @@
       </c>
       <c r="D10" s="137" t="inlineStr">
         <is>
-          <t>Which algebraic laws that hold for sets fail for bags? Why did SQL choose bag semantics anyway?</t>
+          <t>COUNT(*) and COUNT(attribute) can return different values on the same table. Why, and what does this show about how aggregates treat NULL?</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4189,7 @@
       <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Discussion of the Chapter 1 constructivist questions
-Lab 1: install SQL Server; load the sample university database</t>
+Tool set-up (not graded): install SQL Server and SSMS; load the sample university database</t>
         </is>
       </c>
       <c r="C4" s="32" t="inlineStr">
@@ -4214,25 +4211,25 @@
       <c r="F4" s="33" t="inlineStr">
         <is>
           <t>- Slides: Chapter 1
-- Lab 1 handout
+- Set-up guide
 - Textbook: DSC Appendix A, pp. 1287–1298</t>
         </is>
       </c>
       <c r="G4" s="33" t="inlineStr">
         <is>
           <t>- Slides: Chapter 1
-- Lab 1 handout</t>
+- Set-up guide</t>
         </is>
       </c>
       <c r="H4" s="31" t="inlineStr">
         <is>
-          <t>Discuss the Chapter 1 constructivist questions; choose one and submit a 150–200-word answer within one week
-Do Lab 1</t>
+          <t>Discuss the Chapter 1 constructivist questions; choose one and submit an answer within one week
+Install the tools and load the sample database</t>
         </is>
       </c>
       <c r="I4" s="74" t="inlineStr">
         <is>
-          <t>Lead the discussion; guide Lab 1</t>
+          <t>Lead the discussion; help students with the set-up</t>
         </is>
       </c>
       <c r="J4" s="115" t="n"/>
@@ -4400,7 +4397,7 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>Lab 2: relational algebra exercises; Python mini relational-algebra evaluator</t>
+          <t>Assignment (group project) introduction: project brief, teams of 3–4, milestones and rubric; how to state a research question, design a small experiment and keep it reproducible</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -4410,34 +4407,32 @@
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>CLO3</t>
+          <t>CLO8</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F8" s="31" t="inlineStr">
         <is>
-          <t>- Lab 2 handout
-- Python starter code (ra.py)
-- Textbook: DSC §2.6, pp. 48–57; Exercises, pp. 60–62</t>
+          <t>- Assignment brief and rubric</t>
         </is>
       </c>
       <c r="G8" s="31" t="inlineStr">
         <is>
-          <t>- Lab 2 handout and sample solution</t>
+          <t>- Assignment brief, rubric and topic list</t>
         </is>
       </c>
       <c r="H8" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 2; submit before the end of the session</t>
+          <t>Form teams; choose an application domain; read the brief</t>
         </is>
       </c>
       <c r="I8" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 2; review and grade submissions</t>
+          <t>Present the assignment; approve teams and domains</t>
         </is>
       </c>
       <c r="J8" s="115" t="n"/>
@@ -4449,7 +4444,7 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>Guided exercises: algebra and calculus proofs; review of the relational-calculus self-study worksheet</t>
+          <t>Guided exercises: relational algebra queries (checked with RelaX); algebra and calculus proofs; review of the relational-calculus self-study worksheet</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -4470,18 +4465,20 @@
       <c r="F9" s="33" t="inlineStr">
         <is>
           <t>- Slides: Chapter 2
-- Relational-calculus worksheet (DSC online Ch. 27)</t>
+- Exercise sheet
+- Relational-calculus worksheet (DSC online Ch. 27)
+- Textbook: DSC Ch. 2 Exercises, pp. 60–62</t>
         </is>
       </c>
       <c r="G9" s="33" t="inlineStr">
         <is>
-          <t>- Worksheet solutions</t>
+          <t>- Exercise and worksheet solutions</t>
         </is>
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>Submit the self-study worksheet; solve the proof exercises
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+          <t>Submit the self-study worksheet; solve the algebra and proof exercises
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I9" s="74" t="inlineStr">
@@ -4666,7 +4663,7 @@
       <c r="B13" s="32" t="inlineStr">
         <is>
           <t>3.9 Modification of the database
-Semantics of SQL: bag semantics and translation to relational algebra</t>
+Translating SQL queries into relational algebra</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -4700,7 +4697,8 @@
       <c r="H13" s="31" t="inlineStr">
         <is>
           <t>Read DSC Ch. 3, §3.9, pp. 108–113 before class
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Self-study: Bag (multiset) semantics of SQL: duplicates, ALL vs. DISTINCT, and which algebraic laws fail for bags (DSC Ch. 3, §3.3–3.5 and §3.7, with a worksheet)
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I13" s="74" t="inlineStr">
@@ -4721,7 +4719,7 @@
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>Lab 3 (part 1): single-table queries, joins, NULL behaviour</t>
+          <t>Lab 1 (part 1): single-table queries, joins, NULL behaviour</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -4741,23 +4739,23 @@
       </c>
       <c r="F14" s="33" t="inlineStr">
         <is>
-          <t>- Lab 3 handout
+          <t>- Lab 1 handout
 - Textbook: DSC Ch. 3 Exercises, pp. 115–123</t>
         </is>
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>- Lab 3 handout and sample solution</t>
+          <t>- Lab 1 handout and sample solution</t>
         </is>
       </c>
       <c r="H14" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 3; submit before the end of the session</t>
+          <t>Do Lab 1; submit before the end of the session</t>
         </is>
       </c>
       <c r="I14" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 3; review and grade submissions</t>
+          <t>Guide Lab 1; review and grade submissions</t>
         </is>
       </c>
       <c r="J14" s="115" t="n"/>
@@ -4769,7 +4767,7 @@
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Lab 3 (part 2): aggregation, subqueries, set operations; equivalent formulations of the same query</t>
+          <t>Lab 1 (part 2): aggregation, subqueries, set operations; equivalent formulations of the same query</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -4789,23 +4787,23 @@
       </c>
       <c r="F15" s="33" t="inlineStr">
         <is>
-          <t>- Lab 3 handout
+          <t>- Lab 1 handout
 - Textbook: DSC Ch. 3 Exercises, pp. 115–123</t>
         </is>
       </c>
       <c r="G15" s="31" t="inlineStr">
         <is>
-          <t>- Lab 3 handout and sample solution</t>
+          <t>- Lab 1 handout and sample solution</t>
         </is>
       </c>
       <c r="H15" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 3; submit before the end of the session</t>
+          <t>Do Lab 1; submit before the end of the session</t>
         </is>
       </c>
       <c r="I15" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 3; review and grade submissions</t>
+          <t>Guide Lab 1; review and grade submissions</t>
         </is>
       </c>
       <c r="J15" s="115" t="n"/>
@@ -4981,8 +4979,8 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>5.1 Accessing SQL from a programming language (Python)
-SQL injection and parameterized queries</t>
+          <t>5.1 Accessing SQL from a programming language: concepts (API, cursors, prepared statements)
+SQL injection and parameterized queries in T-SQL</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -5016,8 +5014,8 @@
       <c r="H19" s="31" t="inlineStr">
         <is>
           <t>Read DSC §5.1, pp. 183–197 before class
-Self-study: DSC §9.8 Application security, pp. 437–446; optional: §5.2–5.3 functions, procedures, triggers, pp. 198–212
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Self-study: DSC §9.8 Application security, pp. 437–446; Python access to SQL Server (pyodbc, pandas), optional; §5.2–5.3 functions, procedures, triggers, pp. 198–212, optional
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I19" s="74" t="inlineStr">
@@ -5034,7 +5032,7 @@
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>Lab 4: DDL, integrity constraints, views, and SQL from Python</t>
+          <t>Lab 2: DDL, integrity constraints, views and parameterized queries</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -5054,23 +5052,23 @@
       </c>
       <c r="F20" s="33" t="inlineStr">
         <is>
-          <t>- Lab 4 handout
+          <t>- Lab 2 handout
 - Textbook: DSC Ch. 4 Exercises, pp. 176–179; §5.1</t>
         </is>
       </c>
       <c r="G20" s="33" t="inlineStr">
         <is>
-          <t>- Lab 4 handout and sample solution</t>
+          <t>- Lab 2 handout and sample solution</t>
         </is>
       </c>
       <c r="H20" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 4; submit before the end of the session</t>
+          <t>Do Lab 2; submit before the end of the session</t>
         </is>
       </c>
       <c r="I20" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 4; review and grade submissions</t>
+          <t>Guide Lab 2; review and grade submissions</t>
         </is>
       </c>
       <c r="J20" s="115" t="n"/>
@@ -5321,7 +5319,7 @@
         <is>
           <t>Read DSC Ch. 6, §6.9, pp. 279–284 before class
 Self-study: DSC §6.10–6.11 Alternative notations (crow's foot, UML) and other aspects of design, pp. 285–291
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I25" s="74" t="inlineStr">
@@ -5338,8 +5336,7 @@
       </c>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t>Lab 5: E-R design and reduction to relational schemas
-Assignment 1 released</t>
+          <t>Lab 3: E-R design, reduction to relational schemas and implementation in SQL Server</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -5359,25 +5356,23 @@
       </c>
       <c r="F26" s="33" t="inlineStr">
         <is>
-          <t>- Lab 5 handout
-- Assignment 1 brief
+          <t>- Lab 3 handout
 - Textbook: DSC Ch. 6 Exercises, pp. 294–299</t>
         </is>
       </c>
       <c r="G26" s="33" t="inlineStr">
         <is>
-          <t>- Lab 5 sample solution
-- Assignment 1 brief and rubric</t>
+          <t>- Lab 3 handout and sample solution</t>
         </is>
       </c>
       <c r="H26" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 5; read the Assignment 1 brief</t>
+          <t>Do Lab 3; submit before the end of the session</t>
         </is>
       </c>
       <c r="I26" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 5; present Assignment 1</t>
+          <t>Guide Lab 3; review and grade submissions</t>
         </is>
       </c>
       <c r="J26" s="115" t="n"/>
@@ -5676,7 +5671,7 @@
         <is>
           <t>Read DSC Ch. 7, §7.6, §7.8, pp. 336–340, 342 before class
 Self-study: DSC §7.7 More normal forms, p. 341; §7.9 Database-design process, pp. 343–346
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I32" s="74" t="inlineStr">
@@ -5693,7 +5688,7 @@
       </c>
       <c r="B33" s="32" t="inlineStr">
         <is>
-          <t>Lab 6: FD theory on paper; Python FD toolkit (closure, keys, canonical cover, BCNF, lossless-join test)</t>
+          <t>Guided exercises: FD theory on paper (attribute closure, candidate keys, canonical cover, BCNF and 3NF decomposition, lossless-join test)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -5713,24 +5708,23 @@
       </c>
       <c r="F33" s="31" t="inlineStr">
         <is>
-          <t>- Lab 6 handout
-- Python starter code (fd.py)
+          <t>- Slides: Chapter 6
 - Textbook: DSC Ch. 7 Exercises, pp. 353–359</t>
         </is>
       </c>
       <c r="G33" s="31" t="inlineStr">
         <is>
-          <t>- Lab 6 handout and sample solution</t>
+          <t>- Exercise solutions</t>
         </is>
       </c>
       <c r="H33" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 6; submit before the end of the session</t>
+          <t>Solve the exercises; check each decomposition for lossless join and dependency preservation</t>
         </is>
       </c>
       <c r="I33" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 6; review and grade submissions</t>
+          <t>Guide the exercises; discuss solutions</t>
         </is>
       </c>
       <c r="J33" s="115" t="n"/>
@@ -5742,7 +5736,7 @@
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Assignment 1: submission and oral defense</t>
+          <t>Assignment milestone 1: design review (E-R model, normalized schema with constraints, research questions)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -5752,7 +5746,7 @@
       </c>
       <c r="D34" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO3, CLO8</t>
+          <t>CLO2, CLO5, CLO8</t>
         </is>
       </c>
       <c r="E34" s="32" t="inlineStr">
@@ -5762,22 +5756,22 @@
       </c>
       <c r="F34" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 1 brief and rubric</t>
+          <t>- Assignment brief and rubric</t>
         </is>
       </c>
       <c r="G34" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 1 rubric</t>
+          <t>- Assignment rubric</t>
         </is>
       </c>
       <c r="H34" s="31" t="inlineStr">
         <is>
-          <t>Submit the report; defend it orally (5 minutes)</t>
+          <t>Submit the design document; present it (5 minutes per team)</t>
         </is>
       </c>
       <c r="I34" s="74" t="inlineStr">
         <is>
-          <t>Assess reports and oral defenses</t>
+          <t>Assess the designs; give feedback</t>
         </is>
       </c>
       <c r="J34" s="115" t="n"/>
@@ -6080,7 +6074,7 @@
       <c r="H40" s="31" t="inlineStr">
         <is>
           <t>Solve the exercises; compare hand-computed costs with the formulas
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I40" s="74" t="inlineStr">
@@ -6097,7 +6091,7 @@
       </c>
       <c r="B41" s="32" t="inlineStr">
         <is>
-          <t>Lab 7: indexing experiments on a large table; execution plans and logical reads (Investigate)</t>
+          <t>Lab 4 (part 1): indexing experiments on a large table; logical reads with and without indexes (Investigate)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -6117,23 +6111,23 @@
       </c>
       <c r="F41" s="31" t="inlineStr">
         <is>
-          <t>- Lab 7 handout
+          <t>- Lab 4 handout
 - Textbook: DSC Ch. 14 Exercises, pp. 679–682</t>
         </is>
       </c>
       <c r="G41" s="31" t="inlineStr">
         <is>
-          <t>- Lab 7 handout and sample solution</t>
+          <t>- Lab 4 handout and sample solution</t>
         </is>
       </c>
       <c r="H41" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 7; submit before the end of the session</t>
+          <t>Do Lab 4; submit before the end of the session</t>
         </is>
       </c>
       <c r="I41" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 7; review and grade submissions</t>
+          <t>Guide Lab 4; review and grade submissions</t>
         </is>
       </c>
       <c r="J41" s="115" t="n"/>
@@ -6385,7 +6379,7 @@
         <is>
           <t>Read DSC Ch. 16, §16.4, pp. 766–777 before class
 Self-study: DSC §16.3 Estimating statistics of expression results, pp. 757–765
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I46" s="74" t="inlineStr">
@@ -6402,8 +6396,7 @@
       </c>
       <c r="B47" s="32" t="inlineStr">
         <is>
-          <t>Lab 8: reading execution plans; comparing join algorithms and equivalent queries (Investigate)
-Assignment 2 released (research topics)</t>
+          <t>Lab 4 (part 2): reading execution plans; comparing join algorithms and equivalent queries (Investigate)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -6423,24 +6416,23 @@
       </c>
       <c r="F47" s="31" t="inlineStr">
         <is>
-          <t>- Lab 8 handout
-- Assignment 2 brief
+          <t>- Lab 4 handout
 - Textbook: DSC Ch. 15–16 Exercises, pp. 736–739, 789–793</t>
         </is>
       </c>
       <c r="G47" s="31" t="inlineStr">
         <is>
-          <t>- Lab 8 handout and sample solution</t>
+          <t>- Lab 4 handout and sample solution</t>
         </is>
       </c>
       <c r="H47" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 8; submit before the end of the session</t>
+          <t>Do Lab 4; submit before the end of the session</t>
         </is>
       </c>
       <c r="I47" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 8; review and grade submissions</t>
+          <t>Guide Lab 4; review and grade submissions</t>
         </is>
       </c>
       <c r="J47" s="115" t="n"/>
@@ -6747,7 +6739,7 @@
         <is>
           <t>Read DSC Ch. 18, §18.8, pp. 872–879 before class
 Self-study: DSC §18.9 Weak levels of consistency in practice, pp. 880–882
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I53" s="74" t="inlineStr">
@@ -6764,7 +6756,7 @@
       </c>
       <c r="B54" s="32" t="inlineStr">
         <is>
-          <t>Lab 9: concurrency experiments with two sessions (isolation levels, deadlocks); Python serializability tester</t>
+          <t>Lab 5: concurrency experiments with two sessions (isolation levels, dirty reads, phantoms, deadlocks); serializability of the observed schedules by precedence graph</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -6784,24 +6776,23 @@
       </c>
       <c r="F54" s="31" t="inlineStr">
         <is>
-          <t>- Lab 9 handout
-- Python starter code (schedule.py)
+          <t>- Lab 5 handout
 - Textbook: DSC Ch. 17–18 Exercises, pp. 831–833, 899–903</t>
         </is>
       </c>
       <c r="G54" s="31" t="inlineStr">
         <is>
-          <t>- Lab 9 handout and sample solution</t>
+          <t>- Lab 5 handout and sample solution</t>
         </is>
       </c>
       <c r="H54" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 9; submit before the end of the session</t>
+          <t>Do Lab 5; submit before the end of the session</t>
         </is>
       </c>
       <c r="I54" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 9; review and grade submissions</t>
+          <t>Guide Lab 5; review and grade submissions</t>
         </is>
       </c>
       <c r="J54" s="115" t="n"/>
@@ -6849,7 +6840,7 @@
         <is>
           <t>Read DSC Ch. 19, §19.1, §19.3, pp. 907, 912–921 before class
 Self-study: DSC §19.2 Storage, pp. 908–911; §19.4 Recovery algorithm, pp. 922–925; §19.5–19.6, pp. 926–930; optional §19.9 ARIES, pp. 941–946
-Discuss this chapter's constructivist questions; choose one and submit a 150–200-word answer within one week</t>
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I55" s="74" t="inlineStr">
@@ -6866,7 +6857,7 @@
       </c>
       <c r="B56" s="32" t="inlineStr">
         <is>
-          <t>Assignment 2: research progress meeting (question, method, preliminary results)</t>
+          <t>Assignment milestone 2: progress meeting (experiment method, preliminary results)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -6876,7 +6867,7 @@
       </c>
       <c r="D56" s="32" t="inlineStr">
         <is>
-          <t>CLO8</t>
+          <t>CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E56" s="32" t="inlineStr">
@@ -6886,12 +6877,12 @@
       </c>
       <c r="F56" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 brief and rubric</t>
+          <t>- Assignment brief and rubric</t>
         </is>
       </c>
       <c r="G56" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 rubric</t>
+          <t>- Assignment rubric</t>
         </is>
       </c>
       <c r="H56" s="31" t="inlineStr">
@@ -6901,7 +6892,7 @@
       </c>
       <c r="I56" s="74" t="inlineStr">
         <is>
-          <t>Give feedback on each group's method</t>
+          <t>Give feedback on each team's method</t>
         </is>
       </c>
       <c r="J56" s="115" t="n"/>
@@ -6913,7 +6904,7 @@
       </c>
       <c r="B57" s="32" t="inlineStr">
         <is>
-          <t>Assignment 2: paper presentations (part 1)</t>
+          <t>Assignment: final presentations (part 1)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -6923,7 +6914,7 @@
       </c>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t>CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO2, CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
@@ -6933,22 +6924,22 @@
       </c>
       <c r="F57" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 brief</t>
+          <t>- Assignment brief</t>
         </is>
       </c>
       <c r="G57" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 rubric</t>
+          <t>- Assignment rubric</t>
         </is>
       </c>
       <c r="H57" s="31" t="inlineStr">
         <is>
-          <t>Present the paper (10 minutes + 5 minutes Q&amp;A)</t>
+          <t>Present the project (10 minutes + 5 minutes Q&amp;A)</t>
         </is>
       </c>
       <c r="I57" s="74" t="inlineStr">
         <is>
-          <t>Assess presentations and papers</t>
+          <t>Assess presentations and reports</t>
         </is>
       </c>
       <c r="J57" s="115" t="n"/>
@@ -6960,7 +6951,7 @@
       </c>
       <c r="B58" s="32" t="inlineStr">
         <is>
-          <t>Assignment 2: paper presentations (part 2)</t>
+          <t>Assignment: final presentations (part 2)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -6970,7 +6961,7 @@
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO2, CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
@@ -6980,22 +6971,22 @@
       </c>
       <c r="F58" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 brief</t>
+          <t>- Assignment brief</t>
         </is>
       </c>
       <c r="G58" s="31" t="inlineStr">
         <is>
-          <t>- Assignment 2 rubric</t>
+          <t>- Assignment rubric</t>
         </is>
       </c>
       <c r="H58" s="31" t="inlineStr">
         <is>
-          <t>Present the paper; submit the final paper and code</t>
+          <t>Present the project; submit the final report and SQL scripts</t>
         </is>
       </c>
       <c r="I58" s="74" t="inlineStr">
         <is>
-          <t>Assess presentations and papers</t>
+          <t>Assess presentations and reports</t>
         </is>
       </c>
       <c r="J58" s="115" t="n"/>
@@ -7103,7 +7094,7 @@
       </c>
       <c r="B61" s="32" t="inlineStr">
         <is>
-          <t>Practical exam preparation: SQL practice on the computer</t>
+          <t>Final-exam practice: analysis-level questions (proofs, algorithm traces, cost estimates, schedules)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -7113,7 +7104,7 @@
       </c>
       <c r="D61" s="32" t="inlineStr">
         <is>
-          <t>CLO4</t>
+          <t>CLO1, CLO2, CLO3, CLO4, CLO5, CLO6, CLO7</t>
         </is>
       </c>
       <c r="E61" s="32" t="inlineStr">
@@ -7123,22 +7114,22 @@
       </c>
       <c r="F61" s="31" t="inlineStr">
         <is>
-          <t>- Practice problems (DDL and queries)</t>
+          <t>- Practice question set</t>
         </is>
       </c>
       <c r="G61" s="31" t="inlineStr">
         <is>
-          <t>- Practice problems and solutions</t>
+          <t>- Practice questions and solutions</t>
         </is>
       </c>
       <c r="H61" s="31" t="inlineStr">
         <is>
-          <t>Practise SQL under exam conditions</t>
+          <t>Answer the practice questions under exam conditions</t>
         </is>
       </c>
       <c r="I61" s="74" t="inlineStr">
         <is>
-          <t>Guide the practice; clarify the exam rules</t>
+          <t>Discuss the answers; clarify the exam rules</t>
         </is>
       </c>
       <c r="J61" s="115" t="n"/>
@@ -7166,7 +7157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="13.2"/>
   <cols>
     <col width="6.109375" customWidth="1" min="1" max="1"/>
@@ -7275,7 +7266,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="69" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F2" s="69" t="n">
         <v>0.0001</v>
@@ -7292,17 +7283,17 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>Lab exercises, Python implementations with tests, 'Investigate' mini-reports; short written answers to constructivist questions</t>
+          <t>Lab exercises in SQL Server, 'Investigate' mini-reports; short written answers to constructivist questions</t>
         </is>
       </c>
       <c r="J2" s="27" t="inlineStr">
         <is>
-          <t>9 labs + 10 CQ answers</t>
+          <t>5 labs + 10 CQ answers</t>
         </is>
       </c>
       <c r="K2" s="28" t="inlineStr">
         <is>
-          <t>Labs 1–9 (Chapters 1–9); one constructivist question chosen by the student from each of the 10 chapters</t>
+          <t>Labs 1–5 (Chapters 3–9: SQL queries; DDL, constraints and views; E-R design; indexing and query plans; concurrency); one constructivist question chosen by the student from each of the 10 chapters</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
@@ -7312,7 +7303,7 @@
       </c>
       <c r="M2" s="25" t="inlineStr">
         <is>
-          <t>Labs 6% in total (about 0.67% each). Constructivist-question answers 4% in total (0.4% each; 150–200 words; graded on reasoning, use of the textbook and clarity). The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark. Python tasks are graded by the provided unit tests and by code review.</t>
+          <t>Labs 6% in total (1.2% each). Constructivist-question answers 4% in total (0.4% each; graded on reasoning, use of the textbook and clarity). The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark.</t>
         </is>
       </c>
       <c r="N2" s="71" t="inlineStr">
@@ -7336,7 +7327,7 @@
         </is>
       </c>
       <c r="D3" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E3" s="69" t="n">
         <v>1</v>
@@ -7366,8 +7357,8 @@
       </c>
       <c r="K3" s="28" t="inlineStr">
         <is>
-          <t>- cover Chapters 1–4 (DSC Ch. 1–4, §5.1, §5.4) and the self-study of relational calculus (DSC online Ch. 27)
-- written items: one relational algebra/calculus proof or query, one SQL semantics question (NULL, bags)</t>
+          <t>- cover Chapters 1–4 (DSC Ch. 1–4, §5.1, §5.4) and their self-study readings (relational calculus, bag semantics)
+- written items: one relational algebra/calculus proof or query, one SQL semantics question (NULL, three-valued logic)</t>
         </is>
       </c>
       <c r="L3" s="19" t="inlineStr">
@@ -7403,7 +7394,7 @@
         </is>
       </c>
       <c r="D4" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" s="69" t="n">
         <v>1</v>
@@ -7461,7 +7452,7 @@
       </c>
       <c r="B5" s="71" t="inlineStr">
         <is>
-          <t>Assignment 1</t>
+          <t>Assignment (group project)</t>
         </is>
       </c>
       <c r="C5" s="69" t="inlineStr">
@@ -7470,7 +7461,7 @@
         </is>
       </c>
       <c r="D5" s="70" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" s="69" t="n">
         <v>1</v>
@@ -7480,17 +7471,17 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>Take-home, 3 weeks + 5' oral defense</t>
+          <t>Take-home, whole semester; 2 milestones + 15' final presentation</t>
         </is>
       </c>
       <c r="H5" s="72" t="inlineStr">
         <is>
-          <t>CLO2, CLO3, CLO8</t>
+          <t>CLO2, CLO3, CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
-          <t>Individual technical report (4–6 pages) + oral defense</t>
+          <t>Group project (3–4 students): academic report, reproducible SQL scripts and data, presentation</t>
         </is>
       </c>
       <c r="J5" s="27" t="n">
@@ -7498,18 +7489,18 @@
       </c>
       <c r="K5" s="28" t="inlineStr">
         <is>
-          <t>- cover Chapters 2–6 (DSC Ch. 2–4, 6–7)
-- design and theory report: ER model with justified alternatives, formal relational schema, constraints as logic, algebra/calculus/SQL queries with correctness arguments, one guided experiment</t>
+          <t>- cover Chapters 2–10
+- each team designs one database for its own domain (E-R model, normalized schema with constraints, SQL queries with correctness arguments) and then answers research questions about it through experiments (indexes and query plans, join algorithms, isolation levels) or through constructivist questions linked to the design</t>
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>take-home; released in session 25, submitted and defended in session 33; graded by instructor with rubric</t>
+          <t>take-home; introduced in session 7; milestone 1 (design review) in session 33; milestone 2 (progress meeting) in session 55; final presentations in sessions 56–57; graded by instructor with rubric</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
         <is>
-          <t>Instructor has responsibility to review the assignment for students after graded. Plagiarism or undisclosed AI-generated content leads to a score of 0.</t>
+          <t>Milestone 1 design review 25%, final report 40% (question, method, results, discussion), reproducibility of scripts and data 10%, presentation and Q&amp;A 20%, peer evaluation 5%. Individual marks may differ within a team based on contribution logs. Plagiarism or undisclosed AI-generated content leads to a score of 0. Instructor has responsibility to review the assignment for students after graded.</t>
         </is>
       </c>
       <c r="N5" s="71" t="inlineStr">
@@ -7524,199 +7515,85 @@
       </c>
       <c r="B6" s="71" t="inlineStr">
         <is>
-          <t>Assignment 2</t>
+          <t>Final exam</t>
         </is>
       </c>
       <c r="C6" s="69" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>final exam</t>
         </is>
       </c>
       <c r="D6" s="70" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E6" s="69" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="69" t="n">
-        <v>0.0001</v>
+        <v>5</v>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>Take-home, 4 weeks + 15' presentation</t>
+          <t>60'</t>
         </is>
       </c>
       <c r="H6" s="72" t="inlineStr">
         <is>
-          <t>CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO1, CLO2, CLO3, CLO4, CLO5, CLO6, CLO7</t>
         </is>
       </c>
       <c r="I6" s="25" t="inlineStr">
-        <is>
-          <t>Group mini research project (2–3 students): short paper (IEEE format, 4–6 pages), reproducible code, presentation</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="28" t="inlineStr">
-        <is>
-          <t>- cover Chapters 6–10 (DSC Ch. 7, 12–19)
-- topics: empirical studies (indexes, join algorithms, isolation levels), algorithm implementation and evaluation (FD algorithms, serializability, relational algebra), or reproducing at small scale a result from a published paper found by the group</t>
-        </is>
-      </c>
-      <c r="L6" s="19" t="inlineStr">
-        <is>
-          <t>take-home; released in session 46; progress meeting in session 55; presentations in sessions 56–57; graded by instructor with rubric</t>
-        </is>
-      </c>
-      <c r="M6" s="25" t="inlineStr">
-        <is>
-          <t>Paper 50% (question, method, results, discussion, related work), reproducibility of code and data 20%, presentation and Q&amp;A 20%, peer evaluation 10%. Individual marks may differ within a group based on contribution logs.</t>
-        </is>
-      </c>
-      <c r="N6" s="71" t="inlineStr">
-        <is>
-          <t>Assignment</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="66" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="71" t="inlineStr">
-        <is>
-          <t>Practical exam</t>
-        </is>
-      </c>
-      <c r="C7" s="69" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="D7" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="69" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>60'</t>
-        </is>
-      </c>
-      <c r="H7" s="72" t="inlineStr">
-        <is>
-          <t>CLO4</t>
-        </is>
-      </c>
-      <c r="I7" s="25" t="inlineStr">
-        <is>
-          <t>Practical questions on computer</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="25" t="inlineStr">
-        <is>
-          <t>- cover Chapters 3–5 (DSC Ch. 3, 4, 6)
-- create a schema with constraints from a specification; write SQL queries (joins, aggregation, subqueries, views)</t>
-        </is>
-      </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>by exam board, using computer</t>
-        </is>
-      </c>
-      <c r="M7" s="25" t="inlineStr">
-        <is>
-          <t>The exam questions must be updated or different at least 70% to the previous ones.</t>
-        </is>
-      </c>
-      <c r="N7" s="71" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="66" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="71" t="inlineStr">
-        <is>
-          <t>Final exam</t>
-        </is>
-      </c>
-      <c r="C8" s="69" t="inlineStr">
-        <is>
-          <t>final exam</t>
-        </is>
-      </c>
-      <c r="D8" s="70" t="n">
-        <v>30</v>
-      </c>
-      <c r="E8" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>60'</t>
-        </is>
-      </c>
-      <c r="H8" s="72" t="inlineStr">
-        <is>
-          <t>CLO1, CLO2, CLO3, CLO4, CLO5, CLO6, CLO7</t>
-        </is>
-      </c>
-      <c r="I8" s="25" t="inlineStr">
         <is>
           <t>Multiple choices
 Marked by Computer</t>
         </is>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J6" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t>concepts, proofs, algorithms and analysis; all chapters, including the self-study readings (about 20% of items); at least 30% of items at the Analyze level or above</t>
         </is>
       </c>
-      <c r="L8" s="19" t="inlineStr">
+      <c r="L6" s="19" t="inlineStr">
         <is>
           <t>by exam board, using computer</t>
         </is>
       </c>
-      <c r="M8" s="25" t="inlineStr">
+      <c r="M6" s="25" t="inlineStr">
         <is>
           <t>The exam questions must be updated or different at least 70% to the previous ones.</t>
         </is>
       </c>
-      <c r="N8" s="71" t="inlineStr">
+      <c r="N6" s="71" t="inlineStr">
         <is>
           <t>Final exam</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="138" t="inlineStr">
+    <row r="7" ht="79.2" customHeight="1">
+      <c r="A7" s="24" t="n"/>
+      <c r="B7" s="138" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D9" s="70">
-        <f>SUM(D2:D8)</f>
+      <c r="C7" s="46" t="n"/>
+      <c r="D7" s="70">
+        <f>SUM(D2:D6)</f>
         <v/>
       </c>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="45" t="n"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="43" t="n"/>
+      <c r="I7" s="25" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="19" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="52" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -1599,8 +1599,9 @@
 - Understand the formal foundations of the relational model: relations as sets, and keys and constraints as logical statements;
 - Design databases with the Entity-Relationship model and convert them into relational schemas;
 - Write queries in relational algebra, relational calculus and SQL, and reason about what each language can express;
+- Program the database server in T-SQL (functions, stored procedures, triggers and cursors), and compare row-by-row with set-based processing;
 - Apply functional-dependency theory and its algorithms to normalize a design, and prove that a decomposition is correct;
-- Analyze the cost and complexity of storage, indexing and query-processing algorithms;
+- Analyze the cost of storage, indexing and query-processing algorithms;
 - Explain the system internals that keep data correct: transactions, concurrency control and recovery;
 - Answer research-style questions and carry out small experiments on database topics.</t>
         </is>
@@ -2259,7 +2260,7 @@
       </c>
       <c r="C5" s="104" t="inlineStr">
         <is>
-          <t>Use SQL to define, populate, modify and query relational databases (joins, aggregation, subqueries, views, parameterized queries) and explain query results through SQL semantics (three-valued logic; bag semantics through guided self-study).</t>
+          <t>Use SQL to define, populate, modify and query relational databases (joins, aggregation, subqueries, views, parameterized queries), program the database server in T-SQL (user-defined functions, stored procedures, triggers, cursors), and explain query results through SQL semantics (three-valued logic; bag semantics through guided self-study).</t>
         </is>
       </c>
       <c r="D5" s="103" t="n"/>
@@ -3170,7 +3171,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="135" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="136" t="inlineStr">
         <is>
@@ -3179,7 +3180,7 @@
       </c>
       <c r="D14" s="137" t="inlineStr">
         <is>
-          <t>Why is a grade an attribute of the enrollment relationship and not of STUDENT or SECTION? What goes wrong if it is placed on either entity?</t>
+          <t>A business rule can often be enforced by a CHECK constraint, a trigger or a stored procedure. Which would you choose, and why does the declarative option usually win when it is possible?</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3189,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="135" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="136" t="inlineStr">
         <is>
@@ -3197,7 +3198,7 @@
       </c>
       <c r="D15" s="137" t="inlineStr">
         <is>
-          <t>Is a ternary relationship always equivalent to three binary relationships? Construct a counterexample.</t>
+          <t>A cursor processes one row at a time, while SQL is set-based. Why is the set-based version usually much faster, and when is a cursor still justified? Design an experiment that measures the difference.</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3207,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="135" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="136" t="inlineStr">
         <is>
@@ -3215,7 +3216,7 @@
       </c>
       <c r="D16" s="137" t="inlineStr">
         <is>
-          <t>Give a business rule of the university database that cannot be drawn in an E-R diagram. How should a designer record and enforce it?</t>
+          <t>A trigger can fire another trigger, or itself. What can go wrong with cascading triggers, and how could you argue that a given set of triggers always terminates?</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3225,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="135" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="136" t="inlineStr">
         <is>
@@ -3233,7 +3234,7 @@
       </c>
       <c r="D17" s="137" t="inlineStr">
         <is>
-          <t>Every normal form can be seen as removing one kind of redundancy. What single idea unifies them?</t>
+          <t>Why is a grade an attribute of the enrollment relationship and not of STUDENT or SECTION? What goes wrong if it is placed on either entity?</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3243,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="135" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C18" s="136" t="inlineStr">
         <is>
@@ -3251,7 +3252,7 @@
       </c>
       <c r="D18" s="137" t="inlineStr">
         <is>
-          <t>BCNF decomposition may lose a dependency. When would you accept 3NF instead, and what do you gain?</t>
+          <t>Is a ternary relationship always equivalent to three binary relationships? Construct a counterexample.</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3261,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="135" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="136" t="inlineStr">
         <is>
@@ -3269,7 +3270,7 @@
       </c>
       <c r="D19" s="137" t="inlineStr">
         <is>
-          <t>Testing whether an attribute is prime is NP-complete. What does this mean for automatic schema design tools?</t>
+          <t>Give a business rule of the university database that cannot be drawn in an E-R diagram. How should a designer record and enforce it?</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3279,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="135" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="136" t="inlineStr">
         <is>
@@ -3287,7 +3288,7 @@
       </c>
       <c r="D20" s="137" t="inlineStr">
         <is>
-          <t>Why is a B+-tree node the size of a disk block instead of holding a single key as in a binary search tree?</t>
+          <t>Every normal form can be seen as removing one kind of redundancy. What single idea unifies them?</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3297,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="135" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="136" t="inlineStr">
         <is>
@@ -3305,7 +3306,7 @@
       </c>
       <c r="D21" s="137" t="inlineStr">
         <is>
-          <t>When can a full table scan be cheaper than using an index? Design an experiment that shows it.</t>
+          <t>BCNF decomposition may lose a dependency. When would you accept 3NF instead, and what do you gain?</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3315,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="135" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" s="136" t="inlineStr">
         <is>
@@ -3323,7 +3324,7 @@
       </c>
       <c r="D22" s="137" t="inlineStr">
         <is>
-          <t>Could a machine-learning model replace an index? What would you need to measure to decide?</t>
+          <t>Testing whether an attribute is prime is NP-complete. What does this mean for automatic schema design tools?</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3333,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="135" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="136" t="inlineStr">
         <is>
@@ -3341,7 +3342,7 @@
       </c>
       <c r="D23" s="137" t="inlineStr">
         <is>
-          <t>The optimizer relies on estimates. What happens when the estimates are wrong, and where do the errors come from?</t>
+          <t>Why is a B+-tree node the size of a disk block instead of holding a single key as in a binary search tree?</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3351,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="135" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="136" t="inlineStr">
         <is>
@@ -3359,7 +3360,7 @@
       </c>
       <c r="D24" s="137" t="inlineStr">
         <is>
-          <t>The same query can often be written with a join, a subquery or a set operation. Should the choice affect performance? Why or why not?</t>
+          <t>When can a full table scan be cheaper than using an index? Design an experiment that shows it.</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3369,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="135" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" s="136" t="inlineStr">
         <is>
@@ -3377,7 +3378,7 @@
       </c>
       <c r="D25" s="137" t="inlineStr">
         <is>
-          <t>Why does the number of possible join orders grow so quickly, and how does dynamic programming keep the search manageable?</t>
+          <t>Could a machine-learning model replace an index? What would you need to measure to decide?</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3387,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="135" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C26" s="136" t="inlineStr">
         <is>
@@ -3395,7 +3396,7 @@
       </c>
       <c r="D26" s="137" t="inlineStr">
         <is>
-          <t>Why is serializability the accepted correctness criterion for concurrent transactions? What weaker criteria do real systems use, and why?</t>
+          <t>The optimizer relies on estimates. What happens when the estimates are wrong, and where do the errors come from?</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3405,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="135" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C27" s="136" t="inlineStr">
         <is>
@@ -3413,7 +3414,7 @@
       </c>
       <c r="D27" s="137" t="inlineStr">
         <is>
-          <t>Why does two-phase locking guarantee serializability? Explain the idea of the lock point.</t>
+          <t>The same query can often be written with a join, a subquery or a set operation. Should the choice affect performance? Why or why not?</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3423,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="135" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C28" s="136" t="inlineStr">
         <is>
@@ -3431,7 +3432,7 @@
       </c>
       <c r="D28" s="137" t="inlineStr">
         <is>
-          <t>Snapshot isolation prevents dirty reads, non-repeatable reads and phantoms. Why is it still not serializable?</t>
+          <t>Why does the number of possible join orders grow so quickly, and why can an optimizer not simply try them all?</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3450,7 @@
       </c>
       <c r="D29" s="137" t="inlineStr">
         <is>
-          <t>Why must a log record reach stable storage before the data page it describes (write-ahead logging)?</t>
+          <t>Why is serializability the accepted correctness criterion for concurrent transactions? What weaker criteria do real systems use, and why?</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3468,7 @@
       </c>
       <c r="D30" s="137" t="inlineStr">
         <is>
-          <t>What would a DBMS lose, in performance and in safety, if it forced every modified page to disk at commit?</t>
+          <t>Why does two-phase locking guarantee serializability? Explain the idea of the lock point.</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3486,7 @@
       </c>
       <c r="D31" s="137" t="inlineStr">
         <is>
-          <t>Why is recovery hard to test in a lab, and how could you still gain evidence that a recovery algorithm is correct?</t>
+          <t>Why must a log record reach stable storage before the data page it describes (write-ahead logging)?</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5015,7 @@
       <c r="H19" s="31" t="inlineStr">
         <is>
           <t>Read DSC §5.1, pp. 183–197 before class
-Self-study: DSC §9.8 Application security, pp. 437–446; Python access to SQL Server (pyodbc, pandas), optional; §5.2–5.3 functions, procedures, triggers, pp. 198–212, optional
+Self-study: DSC §9.8 Application security, pp. 437–446; Python access to SQL Server (pyodbc, pandas), optional
 Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
@@ -5080,8 +5081,7 @@
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>Progress test 1 (Chapters 1–4)
-Review exercises</t>
+          <t>5.2 Functions and procedures (1): T-SQL batches, variables and control flow (IF, WHILE); scalar and table-valued user-defined functions</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -5091,539 +5091,539 @@
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>CLO1, CLO2, CLO3, CLO4</t>
+          <t>CLO4</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F21" s="33" t="inlineStr">
         <is>
-          <t>- Slides: Chapters 1–4
-- DSC Ch. 1–4</t>
+          <t>- Slides: Chapter 5
+- Textbook: DSC §5.2 (within pp. 198–212); T-SQL reference: control-of-flow language, CREATE FUNCTION</t>
         </is>
       </c>
       <c r="G21" s="31" t="inlineStr">
         <is>
-          <t>- Progress test 1</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 5
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H21" s="31" t="inlineStr">
         <is>
-          <t>Review Chapters 1–4; take Progress test 1</t>
+          <t>Read DSC §5.2 (within pp. 198–212); T-SQL reference: control-of-flow language, CREATE FUNCTION before class</t>
         </is>
       </c>
       <c r="I21" s="74" t="inlineStr">
         <is>
-          <t>Run and grade Progress test 1; review the answers</t>
+          <t>Teach Chapter 5</t>
         </is>
       </c>
       <c r="J21" s="115" t="n"/>
       <c r="K21" s="115" t="n"/>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="42" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>5.2 Functions and procedures (2): stored procedures with input and output parameters; error handling with TRY...CATCH; transactions inside a procedure (preview of Chapter 10)</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>CLO4</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 5
+- Textbook: DSC §5.2 (within pp. 198–212); T-SQL reference: CREATE PROCEDURE, TRY...CATCH</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 5
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC §5.2 (within pp. 198–212); T-SQL reference: CREATE PROCEDURE, TRY...CATCH before class
+Self-study: Dynamic SQL with sp_executesql and its injection risk (T-SQL reference; links back to session 18)</t>
+        </is>
+      </c>
+      <c r="I22" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 5</t>
+        </is>
+      </c>
+      <c r="J22" s="115" t="n"/>
+      <c r="K22" s="115" t="n"/>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="42" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>5.3 Triggers: AFTER and INSTEAD OF triggers; the inserted and deleted tables; enforcing business rules that keys and CHECK constraints cannot express; when not to use triggers</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>CLO2, CLO4</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 5
+- Textbook: DSC §5.3 (within pp. 198–212); T-SQL reference: CREATE TRIGGER</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 5
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC §5.3 (within pp. 198–212); T-SQL reference: CREATE TRIGGER before class</t>
+        </is>
+      </c>
+      <c r="I23" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 5</t>
+        </is>
+      </c>
+      <c r="J23" s="115" t="n"/>
+      <c r="K23" s="115" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="42" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Cursors: from the cursor concept of §5.1 to T-SQL cursors (DECLARE, OPEN, FETCH, CLOSE); row-by-row versus set-based processing, and why set-based SQL is usually faster</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>CLO4</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 5
+- Textbook: DSC §5.1 (cursors, revisited) and §5.2 (loops over query results); T-SQL reference: DECLARE CURSOR, FETCH</t>
+        </is>
+      </c>
+      <c r="G24" s="33" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 5
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H24" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC §5.1 (cursors, revisited) and §5.2 (loops over query results); T-SQL reference: DECLARE CURSOR, FETCH before class
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
+        </is>
+      </c>
+      <c r="I24" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
+        </is>
+      </c>
+      <c r="J24" s="115" t="n"/>
+      <c r="K24" s="115" t="n"/>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="42" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>Lab 3 (part 1): user-defined functions and stored procedures with parameters and error handling on the university database</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>CLO4</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>- Lab 3 handout
+- Textbook: DSC Ch. 5 Exercises on §5.2; T-SQL reference</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 3 handout and sample solution</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="inlineStr">
+        <is>
+          <t>Do Lab 3; submit before the end of the session</t>
+        </is>
+      </c>
+      <c r="I25" s="74" t="inlineStr">
+        <is>
+          <t>Guide Lab 3; review and grade submissions</t>
+        </is>
+      </c>
+      <c r="J25" s="115" t="n"/>
+      <c r="K25" s="115" t="n"/>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Lab 3 (part 2): triggers for business rules and audit logs; a cursor solution versus a set-based solution of the same task (Investigate)</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>CLO2, CLO4, CLO8</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>- Lab 3 handout
+- Textbook: DSC Ch. 5 Exercises on §5.2–5.3</t>
+        </is>
+      </c>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>- Lab 3 handout and sample solution</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr">
+        <is>
+          <t>Do Lab 3; submit before the end of the session</t>
+        </is>
+      </c>
+      <c r="I26" s="74" t="inlineStr">
+        <is>
+          <t>Guide Lab 3; review and grade submissions</t>
+        </is>
+      </c>
+      <c r="J26" s="115" t="n"/>
+      <c r="K26" s="115" t="n"/>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="42" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>Progress test 1 (Chapters 1–5)
+Review exercises</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>CLO1, CLO2, CLO3, CLO4</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapters 1–5
+- DSC Ch. 1–4, Ch. 5 §5.1–5.4</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="inlineStr">
+        <is>
+          <t>- Progress test 1</t>
+        </is>
+      </c>
+      <c r="H27" s="31" t="inlineStr">
+        <is>
+          <t>Review Chapters 1–5; take Progress test 1</t>
+        </is>
+      </c>
+      <c r="I27" s="74" t="inlineStr">
+        <is>
+          <t>Run and grade Progress test 1; review the answers</t>
+        </is>
+      </c>
+      <c r="J27" s="115" t="n"/>
+      <c r="K27" s="115" t="n"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="42" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>6.1 Overview of the design process
 6.2 The Entity-Relationship model
 6.3 Complex attributes</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>CLO2</t>
         </is>
       </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F22" s="33" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 5
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 6
 - Textbook: DSC Ch. 6, §6.1–6.3, pp. 241–251</t>
         </is>
       </c>
-      <c r="G22" s="33" t="inlineStr">
+      <c r="G28" s="33" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 5
+- Slides: Chapter 6
 - Textbook [DSC]</t>
         </is>
       </c>
-      <c r="H22" s="31" t="inlineStr">
+      <c r="H28" s="31" t="inlineStr">
         <is>
           <t>Read DSC Ch. 6, §6.1–6.3, pp. 241–251 before class</t>
         </is>
       </c>
-      <c r="I22" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 5</t>
-        </is>
-      </c>
-      <c r="J22" s="115" t="n"/>
-      <c r="K22" s="115" t="n"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="42" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="I28" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 6</t>
+        </is>
+      </c>
+      <c r="J28" s="115" t="n"/>
+      <c r="K28" s="115" t="n"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="42" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>6.4 Mapping cardinalities
 6.5 Primary key
 6.6 Removing redundant attributes in entity sets</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C29" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>CLO2</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F23" s="33" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 5
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 6
 - Textbook: DSC Ch. 6, §6.4–6.6, pp. 252–263</t>
         </is>
       </c>
-      <c r="G23" s="31" t="inlineStr">
+      <c r="G29" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 5
+- Slides: Chapter 6
 - Textbook [DSC]</t>
         </is>
       </c>
-      <c r="H23" s="31" t="inlineStr">
+      <c r="H29" s="31" t="inlineStr">
         <is>
           <t>Read DSC Ch. 6, §6.4–6.6, pp. 252–263 before class</t>
         </is>
       </c>
-      <c r="I23" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 5</t>
-        </is>
-      </c>
-      <c r="J23" s="115" t="n"/>
-      <c r="K23" s="115" t="n"/>
-    </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="42" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="I29" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 6</t>
+        </is>
+      </c>
+      <c r="J29" s="115" t="n"/>
+      <c r="K29" s="115" t="n"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="42" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>6.7 Reducing E-R diagrams to relational schemas</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C30" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>CLO2</t>
         </is>
       </c>
-      <c r="E24" s="32" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 5
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 6
 - Textbook: DSC Ch. 6, §6.7, pp. 264–270</t>
         </is>
       </c>
-      <c r="G24" s="33" t="inlineStr">
+      <c r="G30" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 5
+- Slides: Chapter 6
 - Textbook [DSC]</t>
         </is>
       </c>
-      <c r="H24" s="31" t="inlineStr">
+      <c r="H30" s="31" t="inlineStr">
         <is>
           <t>Read DSC Ch. 6, §6.7, pp. 264–270 before class
 Self-study: DSC §6.8 Extended E-R features, pp. 271–278</t>
         </is>
       </c>
-      <c r="I24" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 5</t>
-        </is>
-      </c>
-      <c r="J24" s="115" t="n"/>
-      <c r="K24" s="115" t="n"/>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="42" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="I30" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 6</t>
+        </is>
+      </c>
+      <c r="J30" s="115" t="n"/>
+      <c r="K30" s="115" t="n"/>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="42" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>6.9 Entity-relationship design issues; limits of the E-R model</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>CLO2</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F25" s="33" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 5
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 6
 - Textbook: DSC Ch. 6, §6.9, pp. 279–284</t>
         </is>
       </c>
-      <c r="G25" s="31" t="inlineStr">
+      <c r="G31" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 5
+- Slides: Chapter 6
 - Textbook [DSC]</t>
         </is>
       </c>
-      <c r="H25" s="31" t="inlineStr">
+      <c r="H31" s="31" t="inlineStr">
         <is>
           <t>Read DSC Ch. 6, §6.9, pp. 279–284 before class
 Self-study: DSC §6.10–6.11 Alternative notations (crow's foot, UML) and other aspects of design, pp. 285–291
 Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
-      <c r="I25" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
-        </is>
-      </c>
-      <c r="J25" s="115" t="n"/>
-      <c r="K25" s="115" t="n"/>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="42" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="32" t="inlineStr">
-        <is>
-          <t>Lab 3: E-R design, reduction to relational schemas and implementation in SQL Server</t>
-        </is>
-      </c>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="inlineStr">
-        <is>
-          <t>CLO2</t>
-        </is>
-      </c>
-      <c r="E26" s="32" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F26" s="33" t="inlineStr">
-        <is>
-          <t>- Lab 3 handout
-- Textbook: DSC Ch. 6 Exercises, pp. 294–299</t>
-        </is>
-      </c>
-      <c r="G26" s="33" t="inlineStr">
-        <is>
-          <t>- Lab 3 handout and sample solution</t>
-        </is>
-      </c>
-      <c r="H26" s="31" t="inlineStr">
-        <is>
-          <t>Do Lab 3; submit before the end of the session</t>
-        </is>
-      </c>
-      <c r="I26" s="74" t="inlineStr">
-        <is>
-          <t>Guide Lab 3; review and grade submissions</t>
-        </is>
-      </c>
-      <c r="J26" s="115" t="n"/>
-      <c r="K26" s="115" t="n"/>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="42" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>7.1 Features of good relational designs: redundancy and anomalies
-7.2 Decomposition using functional dependencies</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>CLO5</t>
-        </is>
-      </c>
-      <c r="E27" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F27" s="33" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 6
-- Textbook: DSC Ch. 7, §7.1–7.2, pp. 303–312</t>
-        </is>
-      </c>
-      <c r="G27" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 6
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H27" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 7, §7.1–7.2, pp. 303–312 before class</t>
-        </is>
-      </c>
-      <c r="I27" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 6</t>
-        </is>
-      </c>
-      <c r="J27" s="115" t="n"/>
-      <c r="K27" s="115" t="n"/>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="42" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="32" t="inlineStr">
-        <is>
-          <t>7.3 Normal forms: BCNF and 3NF</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
-        <is>
-          <t>CLO5</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F28" s="33" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 6
-- Textbook: DSC Ch. 7, §7.3, pp. 313–319</t>
-        </is>
-      </c>
-      <c r="G28" s="33" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 6
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H28" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 7, §7.3, pp. 313–319 before class</t>
-        </is>
-      </c>
-      <c r="I28" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 6</t>
-        </is>
-      </c>
-      <c r="J28" s="115" t="n"/>
-      <c r="K28" s="115" t="n"/>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="42" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>7.4 Functional-dependency theory: closure of a set of FDs, Armstrong's axioms, attribute closure</t>
-        </is>
-      </c>
-      <c r="C29" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
-        <is>
-          <t>CLO5</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F29" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 6
-- Textbook: DSC Ch. 7, §7.4, pp. 320–329</t>
-        </is>
-      </c>
-      <c r="G29" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 6
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H29" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class</t>
-        </is>
-      </c>
-      <c r="I29" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 6</t>
-        </is>
-      </c>
-      <c r="J29" s="115" t="n"/>
-      <c r="K29" s="115" t="n"/>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="42" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="32" t="inlineStr">
-        <is>
-          <t>7.4 Functional-dependency theory (cont.): canonical cover, lossless decomposition, dependency preservation; proofs of soundness</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="inlineStr">
-        <is>
-          <t>CLO5</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F30" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 6
-- Textbook: DSC Ch. 7, §7.4, pp. 320–329</t>
-        </is>
-      </c>
-      <c r="G30" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 6
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H30" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class</t>
-        </is>
-      </c>
-      <c r="I30" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 6</t>
-        </is>
-      </c>
-      <c r="J30" s="115" t="n"/>
-      <c r="K30" s="115" t="n"/>
-    </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="42" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>7.5 Algorithms for decomposition: BCNF decomposition and 3NF synthesis</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
-        <is>
-          <t>CLO5</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F31" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 6
-- Textbook: DSC Ch. 7, §7.5, pp. 330–335</t>
-        </is>
-      </c>
-      <c r="G31" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 6
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H31" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 7, §7.5, pp. 330–335 before class</t>
-        </is>
-      </c>
       <c r="I31" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 6</t>
+          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J31" s="115" t="n"/>
@@ -5635,363 +5635,359 @@
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
+          <t>Lab 4: E-R design, reduction to relational schemas and implementation in SQL Server</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>CLO2</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 4 handout
+- Textbook: DSC Ch. 6 Exercises, pp. 294–299</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 4 handout and sample solution</t>
+        </is>
+      </c>
+      <c r="H32" s="31" t="inlineStr">
+        <is>
+          <t>Do Lab 4; submit before the end of the session</t>
+        </is>
+      </c>
+      <c r="I32" s="74" t="inlineStr">
+        <is>
+          <t>Guide Lab 4; review and grade submissions</t>
+        </is>
+      </c>
+      <c r="J32" s="115" t="n"/>
+      <c r="K32" s="115" t="n"/>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="42" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>7.1 Features of good relational designs: redundancy and anomalies
+7.2 Decomposition using functional dependencies</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>CLO5</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 7, §7.1–7.2, pp. 303–312</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 7
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H33" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 7, §7.1–7.2, pp. 303–312 before class</t>
+        </is>
+      </c>
+      <c r="I33" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 7</t>
+        </is>
+      </c>
+      <c r="J33" s="115" t="n"/>
+      <c r="K33" s="115" t="n"/>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="42" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>7.3 Normal forms: BCNF and 3NF</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>CLO5</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 7, §7.3, pp. 313–319</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 7
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H34" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 7, §7.3, pp. 313–319 before class</t>
+        </is>
+      </c>
+      <c r="I34" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 7</t>
+        </is>
+      </c>
+      <c r="J34" s="115" t="n"/>
+      <c r="K34" s="115" t="n"/>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="42" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>7.4 Functional-dependency theory: closure of a set of FDs, Armstrong's axioms, attribute closure</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>CLO5</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 7, §7.4, pp. 320–329</t>
+        </is>
+      </c>
+      <c r="G35" s="31" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 7
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H35" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class</t>
+        </is>
+      </c>
+      <c r="I35" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 7</t>
+        </is>
+      </c>
+      <c r="J35" s="115" t="n"/>
+      <c r="K35" s="115" t="n"/>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="42" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>7.4 Functional-dependency theory (cont.): canonical cover, lossless decomposition, dependency preservation; proofs of soundness</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>CLO5</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 7, §7.4, pp. 320–329</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 7
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H36" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 7, §7.4, pp. 320–329 before class</t>
+        </is>
+      </c>
+      <c r="I36" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 7</t>
+        </is>
+      </c>
+      <c r="J36" s="115" t="n"/>
+      <c r="K36" s="115" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="42" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>7.5 Algorithms for decomposition: BCNF decomposition and 3NF synthesis</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>CLO5</t>
+        </is>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
+- Textbook: DSC Ch. 7, §7.5, pp. 330–335</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 7
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H37" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 7, §7.5, pp. 330–335 before class</t>
+        </is>
+      </c>
+      <c r="I37" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 7</t>
+        </is>
+      </c>
+      <c r="J37" s="115" t="n"/>
+      <c r="K37" s="115" t="n"/>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
           <t>7.6 Decomposition using multivalued dependencies (4NF, overview)
 7.8 Atomic domains and first normal form</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>CLO5</t>
         </is>
       </c>
-      <c r="E32" s="32" t="inlineStr">
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F32" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 6
+      <c r="F38" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 7
 - Textbook: DSC Ch. 7, §7.6, §7.8, pp. 336–340, 342</t>
         </is>
       </c>
-      <c r="G32" s="31" t="inlineStr">
+      <c r="G38" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 6
+- Slides: Chapter 7
 - Textbook [DSC]</t>
         </is>
       </c>
-      <c r="H32" s="31" t="inlineStr">
+      <c r="H38" s="31" t="inlineStr">
         <is>
           <t>Read DSC Ch. 7, §7.6, §7.8, pp. 336–340, 342 before class
 Self-study: DSC §7.7 More normal forms, p. 341; §7.9 Database-design process, pp. 343–346
 Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
-      <c r="I32" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 6; lead the discussion of the constructivist questions</t>
-        </is>
-      </c>
-      <c r="J32" s="115" t="n"/>
-      <c r="K32" s="115" t="n"/>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="42" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
-        <is>
-          <t>Guided exercises: FD theory on paper (attribute closure, candidate keys, canonical cover, BCNF and 3NF decomposition, lossless-join test)</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D33" s="32" t="inlineStr">
-        <is>
-          <t>CLO5</t>
-        </is>
-      </c>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 6
-- Textbook: DSC Ch. 7 Exercises, pp. 353–359</t>
-        </is>
-      </c>
-      <c r="G33" s="31" t="inlineStr">
-        <is>
-          <t>- Exercise solutions</t>
-        </is>
-      </c>
-      <c r="H33" s="31" t="inlineStr">
-        <is>
-          <t>Solve the exercises; check each decomposition for lossless join and dependency preservation</t>
-        </is>
-      </c>
-      <c r="I33" s="74" t="inlineStr">
-        <is>
-          <t>Guide the exercises; discuss solutions</t>
-        </is>
-      </c>
-      <c r="J33" s="115" t="n"/>
-      <c r="K33" s="115" t="n"/>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="42" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="32" t="inlineStr">
-        <is>
-          <t>Assignment milestone 1: design review (E-R model, normalized schema with constraints, research questions)</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="inlineStr">
-        <is>
-          <t>CLO2, CLO5, CLO8</t>
-        </is>
-      </c>
-      <c r="E34" s="32" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F34" s="31" t="inlineStr">
-        <is>
-          <t>- Assignment brief and rubric</t>
-        </is>
-      </c>
-      <c r="G34" s="31" t="inlineStr">
-        <is>
-          <t>- Assignment rubric</t>
-        </is>
-      </c>
-      <c r="H34" s="31" t="inlineStr">
-        <is>
-          <t>Submit the design document; present it (5 minutes per team)</t>
-        </is>
-      </c>
-      <c r="I34" s="74" t="inlineStr">
-        <is>
-          <t>Assess the designs; give feedback</t>
-        </is>
-      </c>
-      <c r="J34" s="115" t="n"/>
-      <c r="K34" s="115" t="n"/>
-    </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="42" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
-        <is>
-          <t>Progress test 2 (Chapters 5–6)
-Review exercises</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="inlineStr">
-        <is>
-          <t>CLO2, CLO5</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F35" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapters 5–6
-- DSC Ch. 6–7</t>
-        </is>
-      </c>
-      <c r="G35" s="31" t="inlineStr">
-        <is>
-          <t>- Progress test 2</t>
-        </is>
-      </c>
-      <c r="H35" s="31" t="inlineStr">
-        <is>
-          <t>Review Chapters 5–6; take Progress test 2</t>
-        </is>
-      </c>
-      <c r="I35" s="74" t="inlineStr">
-        <is>
-          <t>Run and grade Progress test 2; review the answers</t>
-        </is>
-      </c>
-      <c r="J35" s="115" t="n"/>
-      <c r="K35" s="115" t="n"/>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="42" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="32" t="inlineStr">
-        <is>
-          <t>13.1 Database storage architecture
-13.2 File organization
-13.3 Organization of records in files</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D36" s="32" t="inlineStr">
-        <is>
-          <t>CLO6</t>
-        </is>
-      </c>
-      <c r="E36" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F36" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 7
-- Textbook: DSC Ch. 13, §13.1–13.3, pp. 587–601</t>
-        </is>
-      </c>
-      <c r="G36" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 7
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H36" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 13, §13.1–13.3, pp. 587–601 before class
-Self-study: DSC §12.1 Physical storage media, pp. 559–561; §12.6 Disk-block access, pp. 577–579</t>
-        </is>
-      </c>
-      <c r="I36" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 7</t>
-        </is>
-      </c>
-      <c r="J36" s="115" t="n"/>
-      <c r="K36" s="115" t="n"/>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="42" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="32" t="inlineStr">
-        <is>
-          <t>13.5 Database buffer
-14.1 Indexing: basic concepts
-14.2 Ordered indices</t>
-        </is>
-      </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="inlineStr">
-        <is>
-          <t>CLO6</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 7
-- Textbook: DSC §13.5, pp. 604–610; Ch. 14, §14.1–14.2, pp. 623–633</t>
-        </is>
-      </c>
-      <c r="G37" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 7
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H37" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC §13.5, pp. 604–610; Ch. 14, §14.1–14.2, pp. 623–633 before class
-Self-study: DSC §13.4 Data-dictionary storage, pp. 602–603</t>
-        </is>
-      </c>
-      <c r="I37" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 7</t>
-        </is>
-      </c>
-      <c r="J37" s="115" t="n"/>
-      <c r="K37" s="115" t="n"/>
-    </row>
-    <row r="38" ht="45" customHeight="1">
-      <c r="A38" s="42" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="32" t="inlineStr">
-        <is>
-          <t>14.3 B+-tree index files: structure, search, insertion, deletion; height analysis</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="inlineStr">
-        <is>
-          <t>CLO6</t>
-        </is>
-      </c>
-      <c r="E38" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F38" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 7
-- Textbook: DSC Ch. 14, §14.3, pp. 634–649</t>
-        </is>
-      </c>
-      <c r="G38" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 7
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H38" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 14, §14.3, pp. 634–649 before class
-Self-study: DSC §14.4 B+-tree extensions, pp. 650–657</t>
-        </is>
-      </c>
       <c r="I38" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 7</t>
+          <t>Teach Chapter 7; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J38" s="115" t="n"/>
       <c r="K38" s="115" t="n"/>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="42" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="32" t="inlineStr">
         <is>
-          <t>14.5 Hash indices
-14.6 Multiple-key access
-14.7 Creation of indices</t>
+          <t>Guided exercises: FD theory on paper (attribute closure, candidate keys, canonical cover, BCNF and 3NF decomposition, lossless-join test)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -6001,36 +5997,33 @@
       </c>
       <c r="D39" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO5</t>
         </is>
       </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F39" s="31" t="inlineStr">
         <is>
           <t>- Slides: Chapter 7
-- Textbook: DSC Ch. 14, §14.5–14.7, pp. 658–664</t>
+- Textbook: DSC Ch. 7 Exercises, pp. 353–359</t>
         </is>
       </c>
       <c r="G39" s="31" t="inlineStr">
         <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 7
-- Textbook [DSC]</t>
+          <t>- Exercise solutions</t>
         </is>
       </c>
       <c r="H39" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 14, §14.5–14.7, pp. 658–664 before class
-Self-study: Optional: §13.6 Column-oriented storage, pp. 611–614; §14.8 Write-optimized index structures (LSM), pp. 665–669</t>
+          <t>Solve the exercises; check each decomposition for lossless join and dependency preservation</t>
         </is>
       </c>
       <c r="I39" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 7</t>
+          <t>Guide the exercises; discuss solutions</t>
         </is>
       </c>
       <c r="J39" s="115" t="n"/>
@@ -6042,7 +6035,7 @@
       </c>
       <c r="B40" s="32" t="inlineStr">
         <is>
-          <t>Guided exercises: B+-tree insertion and deletion by hand; hashing; I/O cost of index lookups versus table scans</t>
+          <t>Assignment milestone 1: design review (E-R model, normalized schema with constraints, research questions)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -6052,7 +6045,7 @@
       </c>
       <c r="D40" s="32" t="inlineStr">
         <is>
-          <t>CLO6</t>
+          <t>CLO2, CLO5, CLO8</t>
         </is>
       </c>
       <c r="E40" s="32" t="inlineStr">
@@ -6062,24 +6055,22 @@
       </c>
       <c r="F40" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapter 7
-- Textbook: DSC Ch. 14 Exercises, pp. 679–682</t>
+          <t>- Assignment brief and rubric</t>
         </is>
       </c>
       <c r="G40" s="31" t="inlineStr">
         <is>
-          <t>- Exercise solutions</t>
+          <t>- Assignment rubric</t>
         </is>
       </c>
       <c r="H40" s="31" t="inlineStr">
         <is>
-          <t>Solve the exercises; compare hand-computed costs with the formulas
-Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
+          <t>Submit the design document; present it (5 minutes per team)</t>
         </is>
       </c>
       <c r="I40" s="74" t="inlineStr">
         <is>
-          <t>Guide the exercises; discuss solutions; lead the discussion of the constructivist questions</t>
+          <t>Assess the designs; give feedback</t>
         </is>
       </c>
       <c r="J40" s="115" t="n"/>
@@ -6091,7 +6082,8 @@
       </c>
       <c r="B41" s="32" t="inlineStr">
         <is>
-          <t>Lab 4 (part 1): indexing experiments on a large table; logical reads with and without indexes (Investigate)</t>
+          <t>Progress test 2 (Chapters 6–7)
+Review exercises</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -6101,7 +6093,7 @@
       </c>
       <c r="D41" s="32" t="inlineStr">
         <is>
-          <t>CLO6, CLO8</t>
+          <t>CLO2, CLO5</t>
         </is>
       </c>
       <c r="E41" s="32" t="inlineStr">
@@ -6111,37 +6103,38 @@
       </c>
       <c r="F41" s="31" t="inlineStr">
         <is>
-          <t>- Lab 4 handout
-- Textbook: DSC Ch. 14 Exercises, pp. 679–682</t>
+          <t>- Slides: Chapters 6–7
+- DSC Ch. 6–7</t>
         </is>
       </c>
       <c r="G41" s="31" t="inlineStr">
         <is>
-          <t>- Lab 4 handout and sample solution</t>
+          <t>- Progress test 2</t>
         </is>
       </c>
       <c r="H41" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 4; submit before the end of the session</t>
+          <t>Review Chapters 6–7; take Progress test 2</t>
         </is>
       </c>
       <c r="I41" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 4; review and grade submissions</t>
+          <t>Run and grade Progress test 2; review the answers</t>
         </is>
       </c>
       <c r="J41" s="115" t="n"/>
       <c r="K41" s="115" t="n"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="75" customHeight="1">
       <c r="A42" s="42" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="32" t="inlineStr">
         <is>
-          <t>15.1 Overview of query processing
-15.2 Measures of query cost
-15.3 Selection operation</t>
+          <t>13.1 Database storage architecture
+13.2 File organization
+13.3 Organization of records in files
+13.5 Database buffer</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -6162,7 +6155,7 @@
       <c r="F42" s="31" t="inlineStr">
         <is>
           <t>- Slides: Chapter 8
-- Textbook: DSC Ch. 15, §15.1–15.3, pp. 689–700</t>
+- Textbook: DSC Ch. 13, §13.1–13.3, pp. 587–601; §13.5, pp. 604–610</t>
         </is>
       </c>
       <c r="G42" s="31" t="inlineStr">
@@ -6174,7 +6167,8 @@
       </c>
       <c r="H42" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 15, §15.1–15.3, pp. 689–700 before class</t>
+          <t>Read DSC Ch. 13, §13.1–13.3, pp. 587–601; §13.5, pp. 604–610 before class
+Self-study: DSC §12.1 Physical storage media, pp. 559–561; §12.6 Disk-block access, pp. 577–579; §13.4 Data-dictionary storage, pp. 602–603</t>
         </is>
       </c>
       <c r="I42" s="74" t="inlineStr">
@@ -6185,14 +6179,15 @@
       <c r="J42" s="115" t="n"/>
       <c r="K42" s="115" t="n"/>
     </row>
-    <row r="43" ht="45" customHeight="1">
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="42" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>15.4 Sorting (external merge sort)
-15.5 Join operation: nested-loop and block nested-loop joins</t>
+          <t>14.1 Indexing: basic concepts
+14.2 Ordered indices
+14.3 B+-tree index files: structure, search, height analysis</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -6213,7 +6208,7 @@
       <c r="F43" s="31" t="inlineStr">
         <is>
           <t>- Slides: Chapter 8
-- Textbook: DSC Ch. 15, §15.4, pp. 701–703; §15.5, pp. 704–718</t>
+- Textbook: DSC Ch. 14, §14.1–14.2, pp. 623–633; §14.3 (structure and queries), pp. 634–649</t>
         </is>
       </c>
       <c r="G43" s="31" t="inlineStr">
@@ -6225,7 +6220,7 @@
       </c>
       <c r="H43" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 15, §15.4, pp. 701–703; §15.5, pp. 704–718 before class</t>
+          <t>Read DSC Ch. 14, §14.1–14.2, pp. 623–633; §14.3 (structure and queries), pp. 634–649 before class</t>
         </is>
       </c>
       <c r="I43" s="74" t="inlineStr">
@@ -6236,13 +6231,15 @@
       <c r="J43" s="115" t="n"/>
       <c r="K43" s="115" t="n"/>
     </row>
-    <row r="44" ht="45" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="42" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="32" t="inlineStr">
         <is>
-          <t>15.5 Join operation (cont.): indexed nested-loop, merge join, hash join; cost comparison</t>
+          <t>14.3 B+-tree index files (cont.): insertion; deletion (main idea)
+14.5 Hash indices
+14.7 Creation of indices</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -6263,7 +6260,7 @@
       <c r="F44" s="31" t="inlineStr">
         <is>
           <t>- Slides: Chapter 8
-- Textbook: DSC Ch. 15, §15.5, pp. 704–718</t>
+- Textbook: DSC Ch. 14, §14.3 (updates), pp. 634–649; §14.5–14.7, pp. 658–664</t>
         </is>
       </c>
       <c r="G44" s="31" t="inlineStr">
@@ -6275,8 +6272,8 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 15, §15.5, pp. 704–718 before class
-Self-study: DSC §15.6 Other operations, pp. 719–723; §15.7 Evaluation of expressions (pipelining), pp. 724–730</t>
+          <t>Read DSC Ch. 14, §14.3 (updates), pp. 634–649; §14.5–14.7, pp. 658–664 before class
+Self-study: DSC §14.4 B+-tree extensions, pp. 650–657; §14.6 Multiple-key access; optional: §13.6 Column-oriented storage, pp. 611–614; §14.8 Write-optimized index structures (LSM), pp. 665–669</t>
         </is>
       </c>
       <c r="I44" s="74" t="inlineStr">
@@ -6293,8 +6290,7 @@
       </c>
       <c r="B45" s="32" t="inlineStr">
         <is>
-          <t>16.1 Overview of query optimization
-16.2 Transformation of relational expressions: equivalence rules</t>
+          <t>Guided exercises: B+-tree insertion by hand; hashing; I/O cost of index lookups versus table scans</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -6309,42 +6305,44 @@
       </c>
       <c r="E45" s="32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F45" s="31" t="inlineStr">
         <is>
           <t>- Slides: Chapter 8
-- Textbook: DSC Ch. 16, §16.1–16.2, pp. 743–756</t>
+- Textbook: DSC Ch. 14 Exercises, pp. 679–682</t>
         </is>
       </c>
       <c r="G45" s="31" t="inlineStr">
         <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 8
-- Textbook [DSC]</t>
+          <t>- Exercise solutions</t>
         </is>
       </c>
       <c r="H45" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 16, §16.1–16.2, pp. 743–756 before class</t>
+          <t>Solve the exercises; compare hand-computed costs with the formulas
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
         </is>
       </c>
       <c r="I45" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 8</t>
+          <t>Guide the exercises; discuss solutions; lead the discussion of the constructivist questions</t>
         </is>
       </c>
       <c r="J45" s="115" t="n"/>
       <c r="K45" s="115" t="n"/>
     </row>
-    <row r="46" ht="45" customHeight="1">
+    <row r="46" ht="75" customHeight="1">
       <c r="A46" s="42" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="32" t="inlineStr">
         <is>
-          <t>16.4 Choice of evaluation plans: cost-based join ordering (dynamic programming)</t>
+          <t>15.1 Overview of query processing
+15.2 Measures of query cost
+15.3 Selection operation
+15.4 Sorting (external merge sort, main idea)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -6364,27 +6362,25 @@
       </c>
       <c r="F46" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapter 8
-- Textbook: DSC Ch. 16, §16.4, pp. 766–777</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 15, §15.1–15.4, pp. 689–703</t>
         </is>
       </c>
       <c r="G46" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 8
+- Slides: Chapter 9
 - Textbook [DSC]</t>
         </is>
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 16, §16.4, pp. 766–777 before class
-Self-study: DSC §16.3 Estimating statistics of expression results, pp. 757–765
-Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
+          <t>Read DSC Ch. 15, §15.1–15.4, pp. 689–703 before class</t>
         </is>
       </c>
       <c r="I46" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 8; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 9</t>
         </is>
       </c>
       <c r="J46" s="115" t="n"/>
@@ -6396,7 +6392,7 @@
       </c>
       <c r="B47" s="32" t="inlineStr">
         <is>
-          <t>Lab 4 (part 2): reading execution plans; comparing join algorithms and equivalent queries (Investigate)</t>
+          <t>15.5 Join operation: nested-loop, block nested-loop, indexed nested-loop, merge join and hash join; cost comparison</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -6406,190 +6402,192 @@
       </c>
       <c r="D47" s="32" t="inlineStr">
         <is>
-          <t>CLO6, CLO8</t>
+          <t>CLO6</t>
         </is>
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="F47" s="31" t="inlineStr">
         <is>
-          <t>- Lab 4 handout
-- Textbook: DSC Ch. 15–16 Exercises, pp. 736–739, 789–793</t>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 15, §15.5, pp. 704–718</t>
         </is>
       </c>
       <c r="G47" s="31" t="inlineStr">
         <is>
-          <t>- Lab 4 handout and sample solution</t>
+          <t>- Syllabus IDB201
+- Slides: Chapter 9
+- Textbook [DSC]</t>
         </is>
       </c>
       <c r="H47" s="31" t="inlineStr">
         <is>
-          <t>Do Lab 4; submit before the end of the session</t>
+          <t>Read DSC Ch. 15, §15.5, pp. 704–718 before class
+Self-study: DSC §15.6 Other operations, pp. 719–723; §15.7 Evaluation of expressions (pipelining), pp. 724–730</t>
         </is>
       </c>
       <c r="I47" s="74" t="inlineStr">
         <is>
-          <t>Guide Lab 4; review and grade submissions</t>
+          <t>Teach Chapter 9</t>
         </is>
       </c>
       <c r="J47" s="115" t="n"/>
       <c r="K47" s="115" t="n"/>
     </row>
-    <row r="48" ht="75" customHeight="1">
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="42" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>16.1 Overview of query optimization
+16.2 Transformation of relational expressions: equivalence rules
+Reading execution plans in SQL Server</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>CLO6</t>
+        </is>
+      </c>
+      <c r="E48" s="32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 9
+- Textbook: DSC Ch. 16, §16.1–16.2, pp. 743–756</t>
+        </is>
+      </c>
+      <c r="G48" s="31" t="inlineStr">
+        <is>
+          <t>- Syllabus IDB201
+- Slides: Chapter 9
+- Textbook [DSC]</t>
+        </is>
+      </c>
+      <c r="H48" s="31" t="inlineStr">
+        <is>
+          <t>Read DSC Ch. 16, §16.1–16.2, pp. 743–756 before class
+Self-study: DSC §16.3 Estimating statistics of expression results, pp. 757–765; optional: §16.4 Choice of evaluation plans (cost-based join ordering by dynamic programming), pp. 766–777
+Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
+        </is>
+      </c>
+      <c r="I48" s="74" t="inlineStr">
+        <is>
+          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
+        </is>
+      </c>
+      <c r="J48" s="115" t="n"/>
+      <c r="K48" s="115" t="n"/>
+    </row>
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="42" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>Lab 5 (part 1): indexes and execution plans on a large table; logical reads with and without indexes; comparing join algorithms in plans (Investigate)</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>Offline</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
+        <is>
+          <t>CLO6, CLO8</t>
+        </is>
+      </c>
+      <c r="E49" s="32" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 5 handout
+- Textbook: DSC Ch. 14–16 Exercises, pp. 679–682, 736–739, 789–793</t>
+        </is>
+      </c>
+      <c r="G49" s="31" t="inlineStr">
+        <is>
+          <t>- Lab 5 handout and sample solution</t>
+        </is>
+      </c>
+      <c r="H49" s="31" t="inlineStr">
+        <is>
+          <t>Do Lab 5; submit before the end of the session</t>
+        </is>
+      </c>
+      <c r="I49" s="74" t="inlineStr">
+        <is>
+          <t>Guide Lab 5; review and grade submissions</t>
+        </is>
+      </c>
+      <c r="J49" s="115" t="n"/>
+      <c r="K49" s="115" t="n"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="42" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
         <is>
           <t>17.1 Transaction concept
 17.2 A simple transaction model
 17.3 Storage structure
-17.4 Transaction atomicity and durability</t>
-        </is>
-      </c>
-      <c r="C48" s="32" t="inlineStr">
+17.4 Transaction atomicity and durability
+17.10 Transactions as SQL statements</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
         <is>
           <t>Offline</t>
         </is>
       </c>
-      <c r="D48" s="32" t="inlineStr">
+      <c r="D50" s="32" t="inlineStr">
         <is>
           <t>CLO7</t>
         </is>
       </c>
-      <c r="E48" s="32" t="inlineStr">
+      <c r="E50" s="32" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F48" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 9
-- Textbook: DSC Ch. 17, §17.1–17.4, pp. 799–806</t>
-        </is>
-      </c>
-      <c r="G48" s="31" t="inlineStr">
+      <c r="F50" s="31" t="inlineStr">
+        <is>
+          <t>- Slides: Chapter 10
+- Textbook: DSC Ch. 17, §17.1–17.4, pp. 799–806; §17.10</t>
+        </is>
+      </c>
+      <c r="G50" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 9
+- Slides: Chapter 10
 - Textbook [DSC]</t>
         </is>
       </c>
-      <c r="H48" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 17, §17.1–17.4, pp. 799–806 before class</t>
-        </is>
-      </c>
-      <c r="I48" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 9</t>
-        </is>
-      </c>
-      <c r="J48" s="115" t="n"/>
-      <c r="K48" s="115" t="n"/>
-    </row>
-    <row r="49" ht="45" customHeight="1">
-      <c r="A49" s="42" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="32" t="inlineStr">
-        <is>
-          <t>17.5 Transaction isolation
-17.6 Serializability: conflict serializability and precedence graphs</t>
-        </is>
-      </c>
-      <c r="C49" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="inlineStr">
-        <is>
-          <t>CLO7</t>
-        </is>
-      </c>
-      <c r="E49" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F49" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 9
-- Textbook: DSC Ch. 17, §17.5–17.6, pp. 807–818</t>
-        </is>
-      </c>
-      <c r="G49" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 9
-- Textbook [DSC]</t>
-        </is>
-      </c>
-      <c r="H49" s="31" t="inlineStr">
-        <is>
-          <t>Read DSC Ch. 17, §17.5–17.6, pp. 807–818 before class</t>
-        </is>
-      </c>
-      <c r="I49" s="74" t="inlineStr">
-        <is>
-          <t>Teach Chapter 9</t>
-        </is>
-      </c>
-      <c r="J49" s="115" t="n"/>
-      <c r="K49" s="115" t="n"/>
-    </row>
-    <row r="50" ht="75" customHeight="1">
-      <c r="A50" s="42" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="32" t="inlineStr">
-        <is>
-          <t>17.7 Transaction isolation and atomicity: recoverable and cascadeless schedules
-17.8 Transaction isolation levels
-17.9 Implementation of isolation levels
-17.10 Transactions as SQL statements</t>
-        </is>
-      </c>
-      <c r="C50" s="32" t="inlineStr">
-        <is>
-          <t>Offline</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="inlineStr">
-        <is>
-          <t>CLO7</t>
-        </is>
-      </c>
-      <c r="E50" s="32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F50" s="31" t="inlineStr">
-        <is>
-          <t>- Slides: Chapter 9
-- Textbook: DSC Ch. 17, §17.7–17.10, pp. 819–827</t>
-        </is>
-      </c>
-      <c r="G50" s="31" t="inlineStr">
-        <is>
-          <t>- Syllabus IDB201
-- Slides: Chapter 9
-- Textbook [DSC]</t>
-        </is>
-      </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 17, §17.7–17.10, pp. 819–827 before class</t>
+          <t>Read DSC Ch. 17, §17.1–17.4, pp. 799–806; §17.10 before class</t>
         </is>
       </c>
       <c r="I50" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9</t>
+          <t>Teach Chapter 10</t>
         </is>
       </c>
       <c r="J50" s="115" t="n"/>
@@ -6601,7 +6599,8 @@
       </c>
       <c r="B51" s="32" t="inlineStr">
         <is>
-          <t>18.1 Lock-based protocols: two-phase locking and why it guarantees serializability</t>
+          <t>17.5 Transaction isolation
+17.6 Serializability: conflict serializability and precedence graphs</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -6621,39 +6620,40 @@
       </c>
       <c r="F51" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapter 9
-- Textbook: DSC Ch. 18, §18.1, pp. 835–848</t>
+          <t>- Slides: Chapter 10
+- Textbook: DSC Ch. 17, §17.5–17.6, pp. 807–818</t>
         </is>
       </c>
       <c r="G51" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 9
+- Slides: Chapter 10
 - Textbook [DSC]</t>
         </is>
       </c>
       <c r="H51" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 18, §18.1, pp. 835–848 before class
-Self-study: DSC §18.3 Multiple granularity, pp. 853–856</t>
+          <t>Read DSC Ch. 17, §17.5–17.6, pp. 807–818 before class</t>
         </is>
       </c>
       <c r="I51" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9</t>
+          <t>Teach Chapter 10</t>
         </is>
       </c>
       <c r="J51" s="115" t="n"/>
       <c r="K51" s="115" t="n"/>
     </row>
-    <row r="52" ht="45" customHeight="1">
+    <row r="52" ht="75" customHeight="1">
       <c r="A52" s="42" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="32" t="inlineStr">
         <is>
-          <t>18.2 Deadlock handling
-18.4 Insert operations, delete operations and predicate reads (phantoms)</t>
+          <t>17.7 Recoverable and cascadeless schedules
+17.8 Transaction isolation levels
+17.9 Implementation of isolation levels
+18.1 Lock-based protocols: two-phase locking (main idea, lock point)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -6673,38 +6673,40 @@
       </c>
       <c r="F52" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapter 9
-- Textbook: DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860</t>
+          <t>- Slides: Chapter 10
+- Textbook: DSC Ch. 17, §17.7–17.9, pp. 819–827; Ch. 18, §18.1, pp. 835–848</t>
         </is>
       </c>
       <c r="G52" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 9
+- Slides: Chapter 10
 - Textbook [DSC]</t>
         </is>
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860 before class
-Self-study: DSC §18.5 Timestamp-based protocols, pp. 861–865; §18.7 Multiversion schemes, pp. 869–871</t>
+          <t>Read DSC Ch. 17, §17.7–17.9, pp. 819–827; Ch. 18, §18.1, pp. 835–848 before class
+Self-study: DSC §18.3 Multiple granularity, pp. 853–856</t>
         </is>
       </c>
       <c r="I52" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9</t>
+          <t>Teach Chapter 10</t>
         </is>
       </c>
       <c r="J52" s="115" t="n"/>
       <c r="K52" s="115" t="n"/>
     </row>
-    <row r="53" ht="45" customHeight="1">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="42" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="32" t="inlineStr">
         <is>
-          <t>18.8 Snapshot isolation and write skew</t>
+          <t>18.2 Deadlock handling
+18.4 Insert operations, delete operations and predicate reads (phantoms)
+18.8 Snapshot isolation (overview)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -6724,27 +6726,26 @@
       </c>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapter 9
-- Textbook: DSC Ch. 18, §18.8, pp. 872–879</t>
+          <t>- Slides: Chapter 10
+- Textbook: DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860; §18.8, pp. 872–879</t>
         </is>
       </c>
       <c r="G53" s="31" t="inlineStr">
         <is>
           <t>- Syllabus IDB201
-- Slides: Chapter 9
+- Slides: Chapter 10
 - Textbook [DSC]</t>
         </is>
       </c>
       <c r="H53" s="31" t="inlineStr">
         <is>
-          <t>Read DSC Ch. 18, §18.8, pp. 872–879 before class
-Self-study: DSC §18.9 Weak levels of consistency in practice, pp. 880–882
-Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
+          <t>Read DSC Ch. 18, §18.2, pp. 849–852; §18.4, pp. 857–860; §18.8, pp. 872–879 before class
+Self-study: DSC §18.5 Timestamp-based protocols, pp. 861–865; §18.7 Multiversion schemes, pp. 869–871; §18.9 Weak levels of consistency in practice, pp. 880–882</t>
         </is>
       </c>
       <c r="I53" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 9; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 10</t>
         </is>
       </c>
       <c r="J53" s="115" t="n"/>
@@ -6756,7 +6757,7 @@
       </c>
       <c r="B54" s="32" t="inlineStr">
         <is>
-          <t>Lab 5: concurrency experiments with two sessions (isolation levels, dirty reads, phantoms, deadlocks); serializability of the observed schedules by precedence graph</t>
+          <t>Lab 5 (part 2): concurrency experiments with two sessions (isolation levels, dirty reads, phantoms, deadlocks); serializability of the observed schedules by precedence graph</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -6766,7 +6767,7 @@
       </c>
       <c r="D54" s="32" t="inlineStr">
         <is>
-          <t>CLO7</t>
+          <t>CLO7, CLO8</t>
         </is>
       </c>
       <c r="E54" s="32" t="inlineStr">
@@ -6914,7 +6915,7 @@
       </c>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO2, CLO4, CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
@@ -6961,7 +6962,7 @@
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>CLO2, CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO2, CLO4, CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
@@ -6998,7 +6999,7 @@
       </c>
       <c r="B59" s="32" t="inlineStr">
         <is>
-          <t>Course review (part 1): Chapters 1–6, including the self-study readings</t>
+          <t>Course review (part 1): Chapters 1–7, including the self-study readings</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -7018,7 +7019,7 @@
       </c>
       <c r="F59" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapters 1–6
+          <t>- Slides: Chapters 1–7
 - Self-study reading list</t>
         </is>
       </c>
@@ -7029,7 +7030,7 @@
       </c>
       <c r="H59" s="31" t="inlineStr">
         <is>
-          <t>Review Chapters 1–6 and the self-study readings</t>
+          <t>Review Chapters 1–7 and the self-study readings</t>
         </is>
       </c>
       <c r="I59" s="74" t="inlineStr">
@@ -7046,7 +7047,7 @@
       </c>
       <c r="B60" s="32" t="inlineStr">
         <is>
-          <t>Course review (part 2): Chapters 7–10, including the self-study of recovery</t>
+          <t>Course review (part 2): Chapters 8–10, including the self-study of recovery</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -7066,7 +7067,7 @@
       </c>
       <c r="F60" s="31" t="inlineStr">
         <is>
-          <t>- Slides: Chapters 7–10
+          <t>- Slides: Chapters 8–10
 - Self-study reading list</t>
         </is>
       </c>
@@ -7077,7 +7078,7 @@
       </c>
       <c r="H60" s="31" t="inlineStr">
         <is>
-          <t>Review Chapters 7–10 and the self-study readings</t>
+          <t>Review Chapters 8–10 and the self-study readings</t>
         </is>
       </c>
       <c r="I60" s="74" t="inlineStr">
@@ -7293,7 +7294,7 @@
       </c>
       <c r="K2" s="28" t="inlineStr">
         <is>
-          <t>Labs 1–5 (Chapters 3–9: SQL queries; DDL, constraints and views; E-R design; indexing and query plans; concurrency); one constructivist question chosen by the student from each of the 10 chapters</t>
+          <t>Labs 1–5 (Chapters 3–10: SQL queries; DDL, constraints and views; T-SQL functions, procedures, triggers and cursors; E-R design; indexing, query plans and concurrency); one constructivist question chosen by the student from each of the 10 chapters</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
@@ -7357,8 +7358,8 @@
       </c>
       <c r="K3" s="28" t="inlineStr">
         <is>
-          <t>- cover Chapters 1–4 (DSC Ch. 1–4, §5.1, §5.4) and their self-study readings (relational calculus, bag semantics)
-- written items: one relational algebra/calculus proof or query, one SQL semantics question (NULL, three-valued logic)</t>
+          <t>- cover Chapters 1–5 (DSC Ch. 1–4, §5.1–5.4) and their self-study readings (relational calculus, bag semantics)
+- written items: one relational algebra/calculus proof or query, one SQL semantics or T-SQL reasoning question (NULL and three-valued logic, or the effect of a trigger)</t>
         </is>
       </c>
       <c r="L3" s="19" t="inlineStr">
@@ -7424,7 +7425,7 @@
       </c>
       <c r="K4" s="28" t="inlineStr">
         <is>
-          <t>- cover Chapters 5–6 (DSC Ch. 6–7) and their self-study sections
+          <t>- cover Chapters 6–7 (DSC Ch. 6–7) and their self-study sections
 - written items: one E-R design and reduction task, one FD proof or normalization task</t>
         </is>
       </c>
@@ -7476,7 +7477,7 @@
       </c>
       <c r="H5" s="72" t="inlineStr">
         <is>
-          <t>CLO2, CLO3, CLO5, CLO6, CLO7, CLO8</t>
+          <t>CLO2, CLO3, CLO4, CLO5, CLO6, CLO7, CLO8</t>
         </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
@@ -7490,12 +7491,12 @@
       <c r="K5" s="28" t="inlineStr">
         <is>
           <t>- cover Chapters 2–10
-- each team designs one database for its own domain (E-R model, normalized schema with constraints, SQL queries with correctness arguments) and then answers research questions about it through experiments (indexes and query plans, join algorithms, isolation levels) or through constructivist questions linked to the design</t>
+- each team designs one database for its own domain (E-R model, normalized schema with constraints, SQL queries with correctness arguments, T-SQL procedures and triggers for its business rules) and then answers research questions about it through experiments (triggers versus constraints, cursors versus set-based SQL, indexes and query plans, isolation levels) or through constructivist questions linked to the design</t>
         </is>
       </c>
       <c r="L5" s="19" t="inlineStr">
         <is>
-          <t>take-home; introduced in session 7; milestone 1 (design review) in session 33; milestone 2 (progress meeting) in session 55; final presentations in sessions 56–57; graded by instructor with rubric</t>
+          <t>take-home; introduced in session 7; milestone 1 (design review) in session 39; milestone 2 (progress meeting) in session 55; final presentations in sessions 56–57; graded by instructor with rubric</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -1621,7 +1621,7 @@
         <is>
           <t>- Students must attend at least 80% of contact slots in order to be accepted to the final examination.
 - Read the assigned textbook sections BEFORE each theory session.
-- For each chapter, choose ONE of its three constructivist questions and submit a short written answer on the LMS within one week of the discussion session. The answers are graded as part of the lab and constructivist-question score (4% in total).
+- For each chapter with constructivist questions (all chapters except C5, T-SQL programming), choose ONE of its three constructivist questions and submit a short written answer on the LMS within one week of the discussion session. The answers are graded as part of the lab and constructivist-question score (4% in total).
 - Complete all 5 labs, including the 'Investigate' part, and submit them on time.
 - Complete the group project (one assignment for the whole course): a database designed through the course and a small study answering research questions about it, delivered as an academic report, reproducible SQL scripts and a presentation.
 - Complete the guided self-study readings listed in the schedule (abstract topics such as relational calculus, bag semantics of SQL, statistics estimation and recovery algorithms); they are assessed in the progress tests and the final exam.
@@ -1665,7 +1665,7 @@
       <c r="C15" s="21" t="inlineStr">
         <is>
           <t>1) On-going Assessment:                 50%
-- 5 labs + 10 CQ answers:              10%
+- 5 labs + 9 CQ answers:                10%
 - Progress test 1:                          5%
 - Progress test 2:                          5%
 - 1 Assignment (group project):      30%
@@ -3171,7 +3171,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="135" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C14" s="136" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D14" s="137" t="inlineStr">
         <is>
-          <t>A business rule can often be enforced by a CHECK constraint, a trigger or a stored procedure. Which would you choose, and why does the declarative option usually win when it is possible?</t>
+          <t>Why is a grade an attribute of the enrollment relationship and not of STUDENT or SECTION? What goes wrong if it is placed on either entity?</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="135" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C15" s="136" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D15" s="137" t="inlineStr">
         <is>
-          <t>A cursor processes one row at a time, while SQL is set-based. Why is the set-based version usually much faster, and when is a cursor still justified? Design an experiment that measures the difference.</t>
+          <t>Is a ternary relationship always equivalent to three binary relationships? Construct a counterexample.</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="135" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C16" s="136" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="D16" s="137" t="inlineStr">
         <is>
-          <t>A trigger can fire another trigger, or itself. What can go wrong with cascading triggers, and how could you argue that a given set of triggers always terminates?</t>
+          <t>Give a business rule of the university database that cannot be drawn in an E-R diagram. How should a designer record and enforce it?</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="135" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C17" s="136" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D17" s="137" t="inlineStr">
         <is>
-          <t>Why is a grade an attribute of the enrollment relationship and not of STUDENT or SECTION? What goes wrong if it is placed on either entity?</t>
+          <t>Every normal form can be seen as removing one kind of redundancy. What single idea unifies them?</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="135" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C18" s="136" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D18" s="137" t="inlineStr">
         <is>
-          <t>Is a ternary relationship always equivalent to three binary relationships? Construct a counterexample.</t>
+          <t>BCNF decomposition may lose a dependency. When would you accept 3NF instead, and what do you gain?</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="135" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C19" s="136" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D19" s="137" t="inlineStr">
         <is>
-          <t>Give a business rule of the university database that cannot be drawn in an E-R diagram. How should a designer record and enforce it?</t>
+          <t>Testing whether an attribute is prime is NP-complete. What does this mean for automatic schema design tools?</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="135" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C20" s="136" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D20" s="137" t="inlineStr">
         <is>
-          <t>Every normal form can be seen as removing one kind of redundancy. What single idea unifies them?</t>
+          <t>Why is a B+-tree node the size of a disk block instead of holding a single key as in a binary search tree?</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="135" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C21" s="136" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D21" s="137" t="inlineStr">
         <is>
-          <t>BCNF decomposition may lose a dependency. When would you accept 3NF instead, and what do you gain?</t>
+          <t>When can a full table scan be cheaper than using an index? Design an experiment that shows it.</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="135" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C22" s="136" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D22" s="137" t="inlineStr">
         <is>
-          <t>Testing whether an attribute is prime is NP-complete. What does this mean for automatic schema design tools?</t>
+          <t>Could a machine-learning model replace an index? What would you need to measure to decide?</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="135" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C23" s="136" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="D23" s="137" t="inlineStr">
         <is>
-          <t>Why is a B+-tree node the size of a disk block instead of holding a single key as in a binary search tree?</t>
+          <t>The optimizer relies on estimates. What happens when the estimates are wrong, and where do the errors come from?</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="135" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C24" s="136" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="D24" s="137" t="inlineStr">
         <is>
-          <t>When can a full table scan be cheaper than using an index? Design an experiment that shows it.</t>
+          <t>The same query can often be written with a join, a subquery or a set operation. Should the choice affect performance? Why or why not?</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="135" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C25" s="136" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="D25" s="137" t="inlineStr">
         <is>
-          <t>Could a machine-learning model replace an index? What would you need to measure to decide?</t>
+          <t>Why does the number of possible join orders grow so quickly, and why can an optimizer not simply try them all?</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="135" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C26" s="136" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D26" s="137" t="inlineStr">
         <is>
-          <t>The optimizer relies on estimates. What happens when the estimates are wrong, and where do the errors come from?</t>
+          <t>Why is serializability the accepted correctness criterion for concurrent transactions? What weaker criteria do real systems use, and why?</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="135" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C27" s="136" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D27" s="137" t="inlineStr">
         <is>
-          <t>The same query can often be written with a join, a subquery or a set operation. Should the choice affect performance? Why or why not?</t>
+          <t>Why does two-phase locking guarantee serializability? Explain the idea of the lock point.</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="135" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C28" s="136" t="inlineStr">
         <is>
@@ -3432,63 +3432,24 @@
       </c>
       <c r="D28" s="137" t="inlineStr">
         <is>
-          <t>Why does the number of possible join orders grow so quickly, and why can an optimizer not simply try them all?</t>
+          <t>Why must a log record reach stable storage before the data page it describes (write-ahead logging)?</t>
         </is>
       </c>
     </row>
     <row r="29" ht="13.8" customHeight="1">
-      <c r="A29" s="134" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="135" t="n">
-        <v>54</v>
-      </c>
-      <c r="C29" s="136" t="inlineStr">
-        <is>
-          <t>CQ1</t>
-        </is>
-      </c>
-      <c r="D29" s="137" t="inlineStr">
-        <is>
-          <t>Why is serializability the accepted correctness criterion for concurrent transactions? What weaker criteria do real systems use, and why?</t>
-        </is>
-      </c>
+      <c r="B29" s="96" t="n"/>
+      <c r="C29" s="96" t="n"/>
+      <c r="D29" s="97" t="n"/>
     </row>
     <row r="30" ht="13.8" customHeight="1">
-      <c r="A30" s="134" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="135" t="n">
-        <v>54</v>
-      </c>
-      <c r="C30" s="136" t="inlineStr">
-        <is>
-          <t>CQ2</t>
-        </is>
-      </c>
-      <c r="D30" s="137" t="inlineStr">
-        <is>
-          <t>Why does two-phase locking guarantee serializability? Explain the idea of the lock point.</t>
-        </is>
-      </c>
+      <c r="B30" s="96" t="n"/>
+      <c r="C30" s="96" t="n"/>
+      <c r="D30" s="97" t="n"/>
     </row>
     <row r="31" ht="13.8" customHeight="1">
-      <c r="A31" s="134" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="135" t="n">
-        <v>54</v>
-      </c>
-      <c r="C31" s="136" t="inlineStr">
-        <is>
-          <t>CQ3</t>
-        </is>
-      </c>
-      <c r="D31" s="137" t="inlineStr">
-        <is>
-          <t>Why must a log record reach stable storage before the data page it describes (write-ahead logging)?</t>
-        </is>
-      </c>
+      <c r="B31" s="96" t="n"/>
+      <c r="C31" s="96" t="n"/>
+      <c r="D31" s="97" t="n"/>
     </row>
     <row r="32" ht="13.8" customHeight="1">
       <c r="B32" s="96" t="n"/>
@@ -5265,13 +5226,12 @@
       </c>
       <c r="H24" s="31" t="inlineStr">
         <is>
-          <t>Read DSC §5.1 (cursors, revisited) and §5.2 (loops over query results); T-SQL reference: DECLARE CURSOR, FETCH before class
-Discuss this chapter's constructivist questions; choose one and submit an answer within one week</t>
+          <t>Read DSC §5.1 (cursors, revisited) and §5.2 (loops over query results); T-SQL reference: DECLARE CURSOR, FETCH before class</t>
         </is>
       </c>
       <c r="I24" s="74" t="inlineStr">
         <is>
-          <t>Teach Chapter 5; lead the discussion of the constructivist questions</t>
+          <t>Teach Chapter 5</t>
         </is>
       </c>
       <c r="J24" s="115" t="n"/>
@@ -7267,7 +7227,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="69" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="69" t="n">
         <v>0.0001</v>
@@ -7289,12 +7249,12 @@
       </c>
       <c r="J2" s="27" t="inlineStr">
         <is>
-          <t>5 labs + 10 CQ answers</t>
+          <t>5 labs + 9 CQ answers</t>
         </is>
       </c>
       <c r="K2" s="28" t="inlineStr">
         <is>
-          <t>Labs 1–5 (Chapters 3–10: SQL queries; DDL, constraints and views; T-SQL functions, procedures, triggers and cursors; E-R design; indexing, query plans and concurrency); one constructivist question chosen by the student from each of the 10 chapters</t>
+          <t>Labs 1–5 (Chapters 3–10: SQL queries; DDL, constraints and views; T-SQL functions, procedures, triggers and cursors; E-R design; indexing, query plans and concurrency); one constructivist question chosen by the student from each of the 9 chapters that have them (all except C5, T-SQL programming)</t>
         </is>
       </c>
       <c r="L2" s="19" t="inlineStr">
@@ -7304,7 +7264,7 @@
       </c>
       <c r="M2" s="25" t="inlineStr">
         <is>
-          <t>Labs 6% in total (1.2% each). Constructivist-question answers 4% in total (0.4% each; graded on reasoning, use of the textbook and clarity). The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark.</t>
+          <t>Labs 6% in total (1.2% each). Constructivist-question answers 4% in total (shared equally among the 9 answers; graded on reasoning, use of the textbook and clarity). The 'Investigate' part (hypothesis, experiment, evidence) counts for at least 40% of each lab mark.</t>
         </is>
       </c>
       <c r="N2" s="71" t="inlineStr">

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="488">
   <si>
     <t xml:space="preserve">No</t>
   </si>
@@ -3833,9 +3833,7 @@
       </c>
       <c r="G18" s="45"/>
       <c r="H18" s="45"/>
-      <c r="I18" s="58" t="s">
-        <v>112</v>
-      </c>
+      <c r="I18" s="58"/>
       <c r="J18" s="45"/>
       <c r="K18" s="57"/>
       <c r="L18" s="45"/>

--- a/syllabus/IDB201_Syllabus.xlsx
+++ b/syllabus/IDB201_Syllabus.xlsx
@@ -385,7 +385,7 @@
     <t xml:space="preserve">CLO4</t>
   </si>
   <si>
-    <t xml:space="preserve">Use SQL to define, populate, modify and query relational databases (joins, aggregation, subqueries, views, parameterized queries), program the database server in T-SQL (user-defined functions, stored procedures, triggers, cursors), and explain query results through SQL semantics (three-valued logic; bag semantics through guided self-study).</t>
+    <t xml:space="preserve">Write SQL and T-SQL to define, query and modify relational databases, program server-side logic (functions, stored procedures, triggers, cursors), and explain query results through SQL semantics (three-valued logic, bag semantics).</t>
   </si>
   <si>
     <t xml:space="preserve">CLO5</t>
